--- a/Excel/SpiritDropConfig.xlsx
+++ b/Excel/SpiritDropConfig.xlsx
@@ -262,12 +262,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1865,7 +1865,7 @@
         <v>2035</v>
       </c>
       <c r="H38" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -2454,7 +2454,7 @@
         <v>2036</v>
       </c>
       <c r="H66" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -3128,7 +3128,7 @@
         <v>2037</v>
       </c>
       <c r="H98" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -3465,12 +3465,12 @@
         <v>2038</v>
       </c>
       <c r="H114" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H3 C4 D4 E4 F4 G4 H4 C5:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritDropConfig.xlsx
+++ b/Excel/SpiritDropConfig.xlsx
@@ -262,12 +262,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1069,7 +1069,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L224"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -3468,6 +3468,2186 @@
         <v>10</v>
       </c>
     </row>
+    <row r="116" customHeight="1" spans="3:11">
+      <c r="C116" s="1">
+        <v>201</v>
+      </c>
+      <c r="D116" s="1">
+        <v>2</v>
+      </c>
+      <c r="E116" s="1">
+        <v>9</v>
+      </c>
+      <c r="F116" s="8">
+        <v>1</v>
+      </c>
+      <c r="G116" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H116" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:11">
+      <c r="C117" s="1">
+        <v>202</v>
+      </c>
+      <c r="D117" s="1">
+        <v>2</v>
+      </c>
+      <c r="E117" s="1">
+        <v>9</v>
+      </c>
+      <c r="F117" s="8">
+        <v>2</v>
+      </c>
+      <c r="G117" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H117" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:11">
+      <c r="C118" s="1">
+        <v>203</v>
+      </c>
+      <c r="D118" s="1">
+        <v>2</v>
+      </c>
+      <c r="E118" s="1">
+        <v>9</v>
+      </c>
+      <c r="F118" s="8">
+        <v>2</v>
+      </c>
+      <c r="G118" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H118" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:11">
+      <c r="C119" s="1">
+        <v>204</v>
+      </c>
+      <c r="D119" s="1">
+        <v>2</v>
+      </c>
+      <c r="E119" s="1">
+        <v>9</v>
+      </c>
+      <c r="F119" s="8">
+        <v>3</v>
+      </c>
+      <c r="G119" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H119" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:11">
+      <c r="C120" s="1">
+        <v>205</v>
+      </c>
+      <c r="D120" s="1">
+        <v>2</v>
+      </c>
+      <c r="E120" s="1">
+        <v>9</v>
+      </c>
+      <c r="F120" s="8">
+        <v>3</v>
+      </c>
+      <c r="G120" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H120" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:11">
+      <c r="C121" s="1">
+        <v>206</v>
+      </c>
+      <c r="D121" s="1">
+        <v>2</v>
+      </c>
+      <c r="E121" s="1">
+        <v>9</v>
+      </c>
+      <c r="F121" s="8">
+        <v>3</v>
+      </c>
+      <c r="G121" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H121" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:11">
+      <c r="C122" s="1">
+        <v>207</v>
+      </c>
+      <c r="D122" s="1">
+        <v>2</v>
+      </c>
+      <c r="E122" s="1">
+        <v>9</v>
+      </c>
+      <c r="F122" s="8">
+        <v>4</v>
+      </c>
+      <c r="G122" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H122" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:11">
+      <c r="C123" s="1">
+        <v>208</v>
+      </c>
+      <c r="D123" s="1">
+        <v>2</v>
+      </c>
+      <c r="E123" s="1">
+        <v>9</v>
+      </c>
+      <c r="F123" s="8">
+        <v>4</v>
+      </c>
+      <c r="G123" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H123" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:11">
+      <c r="C124" s="1">
+        <v>209</v>
+      </c>
+      <c r="D124" s="1">
+        <v>2</v>
+      </c>
+      <c r="E124" s="1">
+        <v>9</v>
+      </c>
+      <c r="F124" s="8">
+        <v>4</v>
+      </c>
+      <c r="G124" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H124" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:11">
+      <c r="C125" s="1">
+        <v>210</v>
+      </c>
+      <c r="D125" s="1">
+        <v>2</v>
+      </c>
+      <c r="E125" s="1">
+        <v>9</v>
+      </c>
+      <c r="F125" s="8">
+        <v>4</v>
+      </c>
+      <c r="G125" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H125" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:11">
+      <c r="C126" s="1">
+        <v>211</v>
+      </c>
+      <c r="D126" s="1">
+        <v>2</v>
+      </c>
+      <c r="E126" s="10">
+        <v>10</v>
+      </c>
+      <c r="F126" s="11">
+        <v>1</v>
+      </c>
+      <c r="G126" s="11">
+        <v>2039</v>
+      </c>
+      <c r="H126" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:11">
+      <c r="C127" s="1">
+        <v>212</v>
+      </c>
+      <c r="D127" s="1">
+        <v>2</v>
+      </c>
+      <c r="E127" s="1">
+        <v>10</v>
+      </c>
+      <c r="F127" s="8">
+        <v>1</v>
+      </c>
+      <c r="G127" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H127" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:11">
+      <c r="C128" s="1">
+        <v>213</v>
+      </c>
+      <c r="D128" s="1">
+        <v>2</v>
+      </c>
+      <c r="E128" s="1">
+        <v>10</v>
+      </c>
+      <c r="F128" s="8">
+        <v>2</v>
+      </c>
+      <c r="G128" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H128" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:8">
+      <c r="C129" s="1">
+        <v>214</v>
+      </c>
+      <c r="D129" s="1">
+        <v>2</v>
+      </c>
+      <c r="E129" s="1">
+        <v>10</v>
+      </c>
+      <c r="F129" s="8">
+        <v>2</v>
+      </c>
+      <c r="G129" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H129" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:8">
+      <c r="C130" s="1">
+        <v>215</v>
+      </c>
+      <c r="D130" s="1">
+        <v>2</v>
+      </c>
+      <c r="E130" s="1">
+        <v>10</v>
+      </c>
+      <c r="F130" s="8">
+        <v>3</v>
+      </c>
+      <c r="G130" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H130" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:8">
+      <c r="C131" s="1">
+        <v>216</v>
+      </c>
+      <c r="D131" s="1">
+        <v>2</v>
+      </c>
+      <c r="E131" s="1">
+        <v>10</v>
+      </c>
+      <c r="F131" s="8">
+        <v>3</v>
+      </c>
+      <c r="G131" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H131" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:8">
+      <c r="C132" s="1">
+        <v>217</v>
+      </c>
+      <c r="D132" s="1">
+        <v>2</v>
+      </c>
+      <c r="E132" s="1">
+        <v>10</v>
+      </c>
+      <c r="F132" s="8">
+        <v>3</v>
+      </c>
+      <c r="G132" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H132" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:8">
+      <c r="C133" s="1">
+        <v>218</v>
+      </c>
+      <c r="D133" s="1">
+        <v>2</v>
+      </c>
+      <c r="E133" s="1">
+        <v>10</v>
+      </c>
+      <c r="F133" s="8">
+        <v>4</v>
+      </c>
+      <c r="G133" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H133" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:8">
+      <c r="C134" s="1">
+        <v>219</v>
+      </c>
+      <c r="D134" s="1">
+        <v>2</v>
+      </c>
+      <c r="E134" s="1">
+        <v>10</v>
+      </c>
+      <c r="F134" s="8">
+        <v>4</v>
+      </c>
+      <c r="G134" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H134" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:8">
+      <c r="C135" s="1">
+        <v>220</v>
+      </c>
+      <c r="D135" s="1">
+        <v>2</v>
+      </c>
+      <c r="E135" s="1">
+        <v>10</v>
+      </c>
+      <c r="F135" s="8">
+        <v>4</v>
+      </c>
+      <c r="G135" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H135" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:8">
+      <c r="C136" s="1">
+        <v>221</v>
+      </c>
+      <c r="D136" s="1">
+        <v>2</v>
+      </c>
+      <c r="E136" s="1">
+        <v>10</v>
+      </c>
+      <c r="F136" s="8">
+        <v>4</v>
+      </c>
+      <c r="G136" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H136" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:8">
+      <c r="C137" s="1">
+        <v>222</v>
+      </c>
+      <c r="D137" s="1">
+        <v>2</v>
+      </c>
+      <c r="E137" s="10">
+        <v>11</v>
+      </c>
+      <c r="F137" s="11">
+        <v>1</v>
+      </c>
+      <c r="G137" s="11">
+        <v>2039</v>
+      </c>
+      <c r="H137" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:8">
+      <c r="C138" s="1">
+        <v>223</v>
+      </c>
+      <c r="D138" s="1">
+        <v>2</v>
+      </c>
+      <c r="E138" s="1">
+        <v>11</v>
+      </c>
+      <c r="F138" s="8">
+        <v>1</v>
+      </c>
+      <c r="G138" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H138" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:8">
+      <c r="C139" s="1">
+        <v>224</v>
+      </c>
+      <c r="D139" s="1">
+        <v>2</v>
+      </c>
+      <c r="E139" s="1">
+        <v>11</v>
+      </c>
+      <c r="F139" s="8">
+        <v>2</v>
+      </c>
+      <c r="G139" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H139" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:8">
+      <c r="C140" s="1">
+        <v>225</v>
+      </c>
+      <c r="D140" s="1">
+        <v>2</v>
+      </c>
+      <c r="E140" s="1">
+        <v>11</v>
+      </c>
+      <c r="F140" s="8">
+        <v>2</v>
+      </c>
+      <c r="G140" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H140" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:8">
+      <c r="C141" s="1">
+        <v>226</v>
+      </c>
+      <c r="D141" s="1">
+        <v>2</v>
+      </c>
+      <c r="E141" s="1">
+        <v>11</v>
+      </c>
+      <c r="F141" s="8">
+        <v>2</v>
+      </c>
+      <c r="G141" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H141" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:8">
+      <c r="C142" s="1">
+        <v>227</v>
+      </c>
+      <c r="D142" s="1">
+        <v>2</v>
+      </c>
+      <c r="E142" s="1">
+        <v>11</v>
+      </c>
+      <c r="F142" s="8">
+        <v>3</v>
+      </c>
+      <c r="G142" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H142" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:8">
+      <c r="C143" s="1">
+        <v>228</v>
+      </c>
+      <c r="D143" s="1">
+        <v>2</v>
+      </c>
+      <c r="E143" s="1">
+        <v>11</v>
+      </c>
+      <c r="F143" s="8">
+        <v>3</v>
+      </c>
+      <c r="G143" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H143" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="3:8">
+      <c r="C144" s="1">
+        <v>229</v>
+      </c>
+      <c r="D144" s="1">
+        <v>2</v>
+      </c>
+      <c r="E144" s="1">
+        <v>11</v>
+      </c>
+      <c r="F144" s="8">
+        <v>3</v>
+      </c>
+      <c r="G144" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H144" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:8">
+      <c r="C145" s="1">
+        <v>230</v>
+      </c>
+      <c r="D145" s="1">
+        <v>2</v>
+      </c>
+      <c r="E145" s="1">
+        <v>11</v>
+      </c>
+      <c r="F145" s="8">
+        <v>4</v>
+      </c>
+      <c r="G145" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H145" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:8">
+      <c r="C146" s="1">
+        <v>231</v>
+      </c>
+      <c r="D146" s="1">
+        <v>2</v>
+      </c>
+      <c r="E146" s="1">
+        <v>11</v>
+      </c>
+      <c r="F146" s="8">
+        <v>4</v>
+      </c>
+      <c r="G146" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H146" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:8">
+      <c r="C147" s="1">
+        <v>232</v>
+      </c>
+      <c r="D147" s="1">
+        <v>2</v>
+      </c>
+      <c r="E147" s="1">
+        <v>11</v>
+      </c>
+      <c r="F147" s="8">
+        <v>4</v>
+      </c>
+      <c r="G147" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H147" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:8">
+      <c r="C148" s="1">
+        <v>233</v>
+      </c>
+      <c r="D148" s="1">
+        <v>2</v>
+      </c>
+      <c r="E148" s="1">
+        <v>11</v>
+      </c>
+      <c r="F148" s="8">
+        <v>4</v>
+      </c>
+      <c r="G148" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H148" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:8">
+      <c r="C149" s="1">
+        <v>234</v>
+      </c>
+      <c r="D149" s="1">
+        <v>2</v>
+      </c>
+      <c r="E149" s="10">
+        <v>12</v>
+      </c>
+      <c r="F149" s="11">
+        <v>1</v>
+      </c>
+      <c r="G149" s="11">
+        <v>2039</v>
+      </c>
+      <c r="H149" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:8">
+      <c r="C150" s="1">
+        <v>235</v>
+      </c>
+      <c r="D150" s="1">
+        <v>2</v>
+      </c>
+      <c r="E150" s="1">
+        <v>12</v>
+      </c>
+      <c r="F150" s="8">
+        <v>1</v>
+      </c>
+      <c r="G150" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H150" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:8">
+      <c r="C151" s="1">
+        <v>236</v>
+      </c>
+      <c r="D151" s="1">
+        <v>2</v>
+      </c>
+      <c r="E151" s="1">
+        <v>12</v>
+      </c>
+      <c r="F151" s="8">
+        <v>1</v>
+      </c>
+      <c r="G151" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H151" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:8">
+      <c r="C152" s="1">
+        <v>237</v>
+      </c>
+      <c r="D152" s="1">
+        <v>2</v>
+      </c>
+      <c r="E152" s="1">
+        <v>12</v>
+      </c>
+      <c r="F152" s="8">
+        <v>2</v>
+      </c>
+      <c r="G152" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H152" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:8">
+      <c r="C153" s="1">
+        <v>238</v>
+      </c>
+      <c r="D153" s="1">
+        <v>2</v>
+      </c>
+      <c r="E153" s="1">
+        <v>12</v>
+      </c>
+      <c r="F153" s="8">
+        <v>2</v>
+      </c>
+      <c r="G153" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H153" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:8">
+      <c r="C154" s="1">
+        <v>239</v>
+      </c>
+      <c r="D154" s="1">
+        <v>2</v>
+      </c>
+      <c r="E154" s="1">
+        <v>12</v>
+      </c>
+      <c r="F154" s="8">
+        <v>2</v>
+      </c>
+      <c r="G154" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H154" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:8">
+      <c r="C155" s="1">
+        <v>240</v>
+      </c>
+      <c r="D155" s="1">
+        <v>2</v>
+      </c>
+      <c r="E155" s="1">
+        <v>12</v>
+      </c>
+      <c r="F155" s="8">
+        <v>3</v>
+      </c>
+      <c r="G155" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H155" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:8">
+      <c r="C156" s="1">
+        <v>241</v>
+      </c>
+      <c r="D156" s="1">
+        <v>2</v>
+      </c>
+      <c r="E156" s="1">
+        <v>12</v>
+      </c>
+      <c r="F156" s="8">
+        <v>3</v>
+      </c>
+      <c r="G156" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H156" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:8">
+      <c r="C157" s="1">
+        <v>242</v>
+      </c>
+      <c r="D157" s="1">
+        <v>2</v>
+      </c>
+      <c r="E157" s="1">
+        <v>12</v>
+      </c>
+      <c r="F157" s="8">
+        <v>3</v>
+      </c>
+      <c r="G157" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H157" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="3:8">
+      <c r="C158" s="1">
+        <v>243</v>
+      </c>
+      <c r="D158" s="1">
+        <v>2</v>
+      </c>
+      <c r="E158" s="1">
+        <v>12</v>
+      </c>
+      <c r="F158" s="8">
+        <v>4</v>
+      </c>
+      <c r="G158" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H158" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="3:8">
+      <c r="C159" s="1">
+        <v>244</v>
+      </c>
+      <c r="D159" s="1">
+        <v>2</v>
+      </c>
+      <c r="E159" s="1">
+        <v>12</v>
+      </c>
+      <c r="F159" s="8">
+        <v>4</v>
+      </c>
+      <c r="G159" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H159" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:8">
+      <c r="C160" s="1">
+        <v>245</v>
+      </c>
+      <c r="D160" s="1">
+        <v>2</v>
+      </c>
+      <c r="E160" s="1">
+        <v>12</v>
+      </c>
+      <c r="F160" s="8">
+        <v>4</v>
+      </c>
+      <c r="G160" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H160" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:8">
+      <c r="C161" s="1">
+        <v>246</v>
+      </c>
+      <c r="D161" s="1">
+        <v>2</v>
+      </c>
+      <c r="E161" s="1">
+        <v>12</v>
+      </c>
+      <c r="F161" s="8">
+        <v>4</v>
+      </c>
+      <c r="G161" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H161" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:8">
+      <c r="C162" s="1">
+        <v>247</v>
+      </c>
+      <c r="D162" s="1">
+        <v>2</v>
+      </c>
+      <c r="E162" s="10">
+        <v>13</v>
+      </c>
+      <c r="F162" s="11">
+        <v>1</v>
+      </c>
+      <c r="G162" s="11">
+        <v>2039</v>
+      </c>
+      <c r="H162" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:8">
+      <c r="C163" s="1">
+        <v>248</v>
+      </c>
+      <c r="D163" s="1">
+        <v>2</v>
+      </c>
+      <c r="E163" s="1">
+        <v>13</v>
+      </c>
+      <c r="F163" s="8">
+        <v>1</v>
+      </c>
+      <c r="G163" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H163" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:8">
+      <c r="C164" s="1">
+        <v>249</v>
+      </c>
+      <c r="D164" s="1">
+        <v>2</v>
+      </c>
+      <c r="E164" s="1">
+        <v>13</v>
+      </c>
+      <c r="F164" s="8">
+        <v>1</v>
+      </c>
+      <c r="G164" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H164" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="3:8">
+      <c r="C165" s="1">
+        <v>250</v>
+      </c>
+      <c r="D165" s="1">
+        <v>2</v>
+      </c>
+      <c r="E165" s="1">
+        <v>13</v>
+      </c>
+      <c r="F165" s="8">
+        <v>2</v>
+      </c>
+      <c r="G165" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H165" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="3:8">
+      <c r="C166" s="1">
+        <v>251</v>
+      </c>
+      <c r="D166" s="1">
+        <v>2</v>
+      </c>
+      <c r="E166" s="1">
+        <v>13</v>
+      </c>
+      <c r="F166" s="8">
+        <v>2</v>
+      </c>
+      <c r="G166" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H166" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:8">
+      <c r="C167" s="1">
+        <v>252</v>
+      </c>
+      <c r="D167" s="1">
+        <v>2</v>
+      </c>
+      <c r="E167" s="1">
+        <v>13</v>
+      </c>
+      <c r="F167" s="8">
+        <v>2</v>
+      </c>
+      <c r="G167" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H167" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="3:8">
+      <c r="C168" s="1">
+        <v>253</v>
+      </c>
+      <c r="D168" s="1">
+        <v>2</v>
+      </c>
+      <c r="E168" s="1">
+        <v>13</v>
+      </c>
+      <c r="F168" s="8">
+        <v>2</v>
+      </c>
+      <c r="G168" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H168" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:8">
+      <c r="C169" s="1">
+        <v>254</v>
+      </c>
+      <c r="D169" s="1">
+        <v>2</v>
+      </c>
+      <c r="E169" s="1">
+        <v>13</v>
+      </c>
+      <c r="F169" s="8">
+        <v>3</v>
+      </c>
+      <c r="G169" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H169" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:8">
+      <c r="C170" s="1">
+        <v>255</v>
+      </c>
+      <c r="D170" s="1">
+        <v>2</v>
+      </c>
+      <c r="E170" s="1">
+        <v>13</v>
+      </c>
+      <c r="F170" s="8">
+        <v>3</v>
+      </c>
+      <c r="G170" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H170" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="3:8">
+      <c r="C171" s="1">
+        <v>256</v>
+      </c>
+      <c r="D171" s="1">
+        <v>2</v>
+      </c>
+      <c r="E171" s="1">
+        <v>13</v>
+      </c>
+      <c r="F171" s="8">
+        <v>3</v>
+      </c>
+      <c r="G171" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H171" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="3:8">
+      <c r="C172" s="1">
+        <v>257</v>
+      </c>
+      <c r="D172" s="1">
+        <v>2</v>
+      </c>
+      <c r="E172" s="1">
+        <v>13</v>
+      </c>
+      <c r="F172" s="8">
+        <v>3</v>
+      </c>
+      <c r="G172" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H172" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:8">
+      <c r="C173" s="1">
+        <v>258</v>
+      </c>
+      <c r="D173" s="1">
+        <v>2</v>
+      </c>
+      <c r="E173" s="1">
+        <v>13</v>
+      </c>
+      <c r="F173" s="8">
+        <v>4</v>
+      </c>
+      <c r="G173" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H173" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:8">
+      <c r="C174" s="1">
+        <v>259</v>
+      </c>
+      <c r="D174" s="1">
+        <v>2</v>
+      </c>
+      <c r="E174" s="1">
+        <v>13</v>
+      </c>
+      <c r="F174" s="8">
+        <v>4</v>
+      </c>
+      <c r="G174" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H174" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:8">
+      <c r="C175" s="1">
+        <v>260</v>
+      </c>
+      <c r="D175" s="1">
+        <v>2</v>
+      </c>
+      <c r="E175" s="1">
+        <v>13</v>
+      </c>
+      <c r="F175" s="8">
+        <v>4</v>
+      </c>
+      <c r="G175" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H175" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="3:8">
+      <c r="C176" s="1">
+        <v>261</v>
+      </c>
+      <c r="D176" s="1">
+        <v>2</v>
+      </c>
+      <c r="E176" s="1">
+        <v>13</v>
+      </c>
+      <c r="F176" s="8">
+        <v>4</v>
+      </c>
+      <c r="G176" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H176" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="3:8">
+      <c r="C177" s="1">
+        <v>262</v>
+      </c>
+      <c r="D177" s="1">
+        <v>2</v>
+      </c>
+      <c r="E177" s="10">
+        <v>14</v>
+      </c>
+      <c r="F177" s="11">
+        <v>1</v>
+      </c>
+      <c r="G177" s="11">
+        <v>2039</v>
+      </c>
+      <c r="H177" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="3:8">
+      <c r="C178" s="1">
+        <v>263</v>
+      </c>
+      <c r="D178" s="1">
+        <v>2</v>
+      </c>
+      <c r="E178" s="1">
+        <v>14</v>
+      </c>
+      <c r="F178" s="8">
+        <v>1</v>
+      </c>
+      <c r="G178" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H178" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="3:8">
+      <c r="C179" s="1">
+        <v>264</v>
+      </c>
+      <c r="D179" s="1">
+        <v>2</v>
+      </c>
+      <c r="E179" s="1">
+        <v>14</v>
+      </c>
+      <c r="F179" s="8">
+        <v>1</v>
+      </c>
+      <c r="G179" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H179" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="3:8">
+      <c r="C180" s="1">
+        <v>265</v>
+      </c>
+      <c r="D180" s="1">
+        <v>2</v>
+      </c>
+      <c r="E180" s="1">
+        <v>14</v>
+      </c>
+      <c r="F180" s="8">
+        <v>1</v>
+      </c>
+      <c r="G180" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H180" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="3:8">
+      <c r="C181" s="1">
+        <v>266</v>
+      </c>
+      <c r="D181" s="1">
+        <v>2</v>
+      </c>
+      <c r="E181" s="1">
+        <v>14</v>
+      </c>
+      <c r="F181" s="8">
+        <v>2</v>
+      </c>
+      <c r="G181" s="8">
+        <v>2039</v>
+      </c>
+      <c r="H181" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="3:8">
+      <c r="C182" s="1">
+        <v>267</v>
+      </c>
+      <c r="D182" s="1">
+        <v>2</v>
+      </c>
+      <c r="E182" s="1">
+        <v>14</v>
+      </c>
+      <c r="F182" s="8">
+        <v>2</v>
+      </c>
+      <c r="G182" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H182" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="3:8">
+      <c r="C183" s="1">
+        <v>268</v>
+      </c>
+      <c r="D183" s="1">
+        <v>2</v>
+      </c>
+      <c r="E183" s="1">
+        <v>14</v>
+      </c>
+      <c r="F183" s="8">
+        <v>2</v>
+      </c>
+      <c r="G183" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H183" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:8">
+      <c r="C184" s="1">
+        <v>269</v>
+      </c>
+      <c r="D184" s="1">
+        <v>2</v>
+      </c>
+      <c r="E184" s="1">
+        <v>14</v>
+      </c>
+      <c r="F184" s="8">
+        <v>2</v>
+      </c>
+      <c r="G184" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H184" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="3:8">
+      <c r="C185" s="1">
+        <v>270</v>
+      </c>
+      <c r="D185" s="1">
+        <v>2</v>
+      </c>
+      <c r="E185" s="1">
+        <v>14</v>
+      </c>
+      <c r="F185" s="8">
+        <v>3</v>
+      </c>
+      <c r="G185" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H185" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="3:8">
+      <c r="C186" s="1">
+        <v>271</v>
+      </c>
+      <c r="D186" s="1">
+        <v>2</v>
+      </c>
+      <c r="E186" s="1">
+        <v>14</v>
+      </c>
+      <c r="F186" s="8">
+        <v>3</v>
+      </c>
+      <c r="G186" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H186" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:8">
+      <c r="C187" s="1">
+        <v>272</v>
+      </c>
+      <c r="D187" s="1">
+        <v>2</v>
+      </c>
+      <c r="E187" s="1">
+        <v>14</v>
+      </c>
+      <c r="F187" s="8">
+        <v>3</v>
+      </c>
+      <c r="G187" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H187" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:8">
+      <c r="C188" s="1">
+        <v>273</v>
+      </c>
+      <c r="D188" s="1">
+        <v>2</v>
+      </c>
+      <c r="E188" s="1">
+        <v>14</v>
+      </c>
+      <c r="F188" s="8">
+        <v>3</v>
+      </c>
+      <c r="G188" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H188" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:8">
+      <c r="C189" s="1">
+        <v>274</v>
+      </c>
+      <c r="D189" s="1">
+        <v>2</v>
+      </c>
+      <c r="E189" s="1">
+        <v>14</v>
+      </c>
+      <c r="F189" s="8">
+        <v>4</v>
+      </c>
+      <c r="G189" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H189" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:8">
+      <c r="C190" s="1">
+        <v>275</v>
+      </c>
+      <c r="D190" s="1">
+        <v>2</v>
+      </c>
+      <c r="E190" s="1">
+        <v>14</v>
+      </c>
+      <c r="F190" s="8">
+        <v>4</v>
+      </c>
+      <c r="G190" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H190" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" spans="3:8">
+      <c r="C191" s="1">
+        <v>276</v>
+      </c>
+      <c r="D191" s="1">
+        <v>2</v>
+      </c>
+      <c r="E191" s="1">
+        <v>14</v>
+      </c>
+      <c r="F191" s="8">
+        <v>4</v>
+      </c>
+      <c r="G191" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H191" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" spans="3:8">
+      <c r="C192" s="1">
+        <v>277</v>
+      </c>
+      <c r="D192" s="1">
+        <v>2</v>
+      </c>
+      <c r="E192" s="1">
+        <v>14</v>
+      </c>
+      <c r="F192" s="8">
+        <v>4</v>
+      </c>
+      <c r="G192" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H192" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" spans="3:8">
+      <c r="C193" s="1">
+        <v>278</v>
+      </c>
+      <c r="D193" s="1">
+        <v>2</v>
+      </c>
+      <c r="E193" s="10">
+        <v>15</v>
+      </c>
+      <c r="F193" s="11">
+        <v>1</v>
+      </c>
+      <c r="G193" s="11">
+        <v>2039</v>
+      </c>
+      <c r="H193" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" spans="3:8">
+      <c r="C194" s="1">
+        <v>279</v>
+      </c>
+      <c r="D194" s="1">
+        <v>2</v>
+      </c>
+      <c r="E194" s="1">
+        <v>15</v>
+      </c>
+      <c r="F194" s="8">
+        <v>1</v>
+      </c>
+      <c r="G194" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H194" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" spans="3:8">
+      <c r="C195" s="1">
+        <v>280</v>
+      </c>
+      <c r="D195" s="1">
+        <v>2</v>
+      </c>
+      <c r="E195" s="1">
+        <v>15</v>
+      </c>
+      <c r="F195" s="8">
+        <v>1</v>
+      </c>
+      <c r="G195" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H195" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" spans="3:8">
+      <c r="C196" s="1">
+        <v>281</v>
+      </c>
+      <c r="D196" s="1">
+        <v>2</v>
+      </c>
+      <c r="E196" s="1">
+        <v>15</v>
+      </c>
+      <c r="F196" s="8">
+        <v>1</v>
+      </c>
+      <c r="G196" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H196" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" spans="3:8">
+      <c r="C197" s="1">
+        <v>282</v>
+      </c>
+      <c r="D197" s="1">
+        <v>2</v>
+      </c>
+      <c r="E197" s="1">
+        <v>15</v>
+      </c>
+      <c r="F197" s="8">
+        <v>2</v>
+      </c>
+      <c r="G197" s="8">
+        <v>2040</v>
+      </c>
+      <c r="H197" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" spans="3:8">
+      <c r="C198" s="1">
+        <v>283</v>
+      </c>
+      <c r="D198" s="1">
+        <v>2</v>
+      </c>
+      <c r="E198" s="1">
+        <v>15</v>
+      </c>
+      <c r="F198" s="8">
+        <v>2</v>
+      </c>
+      <c r="G198" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H198" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" spans="3:8">
+      <c r="C199" s="1">
+        <v>284</v>
+      </c>
+      <c r="D199" s="1">
+        <v>2</v>
+      </c>
+      <c r="E199" s="1">
+        <v>15</v>
+      </c>
+      <c r="F199" s="8">
+        <v>2</v>
+      </c>
+      <c r="G199" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H199" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" spans="3:8">
+      <c r="C200" s="1">
+        <v>285</v>
+      </c>
+      <c r="D200" s="1">
+        <v>2</v>
+      </c>
+      <c r="E200" s="1">
+        <v>15</v>
+      </c>
+      <c r="F200" s="8">
+        <v>2</v>
+      </c>
+      <c r="G200" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H200" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="3:8">
+      <c r="C201" s="1">
+        <v>286</v>
+      </c>
+      <c r="D201" s="1">
+        <v>2</v>
+      </c>
+      <c r="E201" s="1">
+        <v>15</v>
+      </c>
+      <c r="F201" s="8">
+        <v>3</v>
+      </c>
+      <c r="G201" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H201" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="3:8">
+      <c r="C202" s="1">
+        <v>287</v>
+      </c>
+      <c r="D202" s="1">
+        <v>2</v>
+      </c>
+      <c r="E202" s="1">
+        <v>15</v>
+      </c>
+      <c r="F202" s="8">
+        <v>3</v>
+      </c>
+      <c r="G202" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H202" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="3:8">
+      <c r="C203" s="1">
+        <v>288</v>
+      </c>
+      <c r="D203" s="1">
+        <v>2</v>
+      </c>
+      <c r="E203" s="1">
+        <v>15</v>
+      </c>
+      <c r="F203" s="8">
+        <v>3</v>
+      </c>
+      <c r="G203" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H203" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="3:8">
+      <c r="C204" s="1">
+        <v>289</v>
+      </c>
+      <c r="D204" s="1">
+        <v>2</v>
+      </c>
+      <c r="E204" s="1">
+        <v>15</v>
+      </c>
+      <c r="F204" s="8">
+        <v>3</v>
+      </c>
+      <c r="G204" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H204" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="3:8">
+      <c r="C205" s="1">
+        <v>290</v>
+      </c>
+      <c r="D205" s="1">
+        <v>2</v>
+      </c>
+      <c r="E205" s="1">
+        <v>15</v>
+      </c>
+      <c r="F205" s="8">
+        <v>4</v>
+      </c>
+      <c r="G205" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H205" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="3:8">
+      <c r="C206" s="1">
+        <v>291</v>
+      </c>
+      <c r="D206" s="1">
+        <v>2</v>
+      </c>
+      <c r="E206" s="1">
+        <v>15</v>
+      </c>
+      <c r="F206" s="8">
+        <v>4</v>
+      </c>
+      <c r="G206" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H206" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="3:8">
+      <c r="C207" s="1">
+        <v>292</v>
+      </c>
+      <c r="D207" s="1">
+        <v>2</v>
+      </c>
+      <c r="E207" s="1">
+        <v>15</v>
+      </c>
+      <c r="F207" s="8">
+        <v>4</v>
+      </c>
+      <c r="G207" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H207" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="3:8">
+      <c r="C208" s="1">
+        <v>293</v>
+      </c>
+      <c r="D208" s="1">
+        <v>2</v>
+      </c>
+      <c r="E208" s="1">
+        <v>15</v>
+      </c>
+      <c r="F208" s="8">
+        <v>4</v>
+      </c>
+      <c r="G208" s="8">
+        <v>2045</v>
+      </c>
+      <c r="H208" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="3:8">
+      <c r="C209" s="1">
+        <v>294</v>
+      </c>
+      <c r="D209" s="1">
+        <v>2</v>
+      </c>
+      <c r="E209" s="10">
+        <v>16</v>
+      </c>
+      <c r="F209" s="11">
+        <v>1</v>
+      </c>
+      <c r="G209" s="11">
+        <v>2040</v>
+      </c>
+      <c r="H209" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="3:8">
+      <c r="C210" s="1">
+        <v>295</v>
+      </c>
+      <c r="D210" s="1">
+        <v>2</v>
+      </c>
+      <c r="E210" s="1">
+        <v>16</v>
+      </c>
+      <c r="F210" s="8">
+        <v>1</v>
+      </c>
+      <c r="G210" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H210" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" spans="3:8">
+      <c r="C211" s="1">
+        <v>296</v>
+      </c>
+      <c r="D211" s="1">
+        <v>2</v>
+      </c>
+      <c r="E211" s="1">
+        <v>16</v>
+      </c>
+      <c r="F211" s="8">
+        <v>1</v>
+      </c>
+      <c r="G211" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H211" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" spans="3:8">
+      <c r="C212" s="1">
+        <v>297</v>
+      </c>
+      <c r="D212" s="1">
+        <v>2</v>
+      </c>
+      <c r="E212" s="1">
+        <v>16</v>
+      </c>
+      <c r="F212" s="8">
+        <v>1</v>
+      </c>
+      <c r="G212" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H212" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" spans="3:8">
+      <c r="C213" s="1">
+        <v>298</v>
+      </c>
+      <c r="D213" s="1">
+        <v>2</v>
+      </c>
+      <c r="E213" s="1">
+        <v>16</v>
+      </c>
+      <c r="F213" s="8">
+        <v>2</v>
+      </c>
+      <c r="G213" s="8">
+        <v>2041</v>
+      </c>
+      <c r="H213" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" spans="3:8">
+      <c r="C214" s="1">
+        <v>299</v>
+      </c>
+      <c r="D214" s="1">
+        <v>2</v>
+      </c>
+      <c r="E214" s="1">
+        <v>16</v>
+      </c>
+      <c r="F214" s="8">
+        <v>2</v>
+      </c>
+      <c r="G214" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H214" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" spans="3:8">
+      <c r="C215" s="1">
+        <v>300</v>
+      </c>
+      <c r="D215" s="1">
+        <v>2</v>
+      </c>
+      <c r="E215" s="1">
+        <v>16</v>
+      </c>
+      <c r="F215" s="8">
+        <v>2</v>
+      </c>
+      <c r="G215" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H215" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" spans="3:8">
+      <c r="C216" s="1">
+        <v>301</v>
+      </c>
+      <c r="D216" s="1">
+        <v>2</v>
+      </c>
+      <c r="E216" s="1">
+        <v>16</v>
+      </c>
+      <c r="F216" s="8">
+        <v>2</v>
+      </c>
+      <c r="G216" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H216" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="3:8">
+      <c r="C217" s="1">
+        <v>302</v>
+      </c>
+      <c r="D217" s="1">
+        <v>2</v>
+      </c>
+      <c r="E217" s="1">
+        <v>16</v>
+      </c>
+      <c r="F217" s="8">
+        <v>3</v>
+      </c>
+      <c r="G217" s="8">
+        <v>2042</v>
+      </c>
+      <c r="H217" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="3:8">
+      <c r="C218" s="1">
+        <v>303</v>
+      </c>
+      <c r="D218" s="1">
+        <v>2</v>
+      </c>
+      <c r="E218" s="1">
+        <v>16</v>
+      </c>
+      <c r="F218" s="8">
+        <v>3</v>
+      </c>
+      <c r="G218" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H218" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="3:8">
+      <c r="C219" s="1">
+        <v>304</v>
+      </c>
+      <c r="D219" s="1">
+        <v>2</v>
+      </c>
+      <c r="E219" s="1">
+        <v>16</v>
+      </c>
+      <c r="F219" s="8">
+        <v>3</v>
+      </c>
+      <c r="G219" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H219" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="3:8">
+      <c r="C220" s="1">
+        <v>305</v>
+      </c>
+      <c r="D220" s="1">
+        <v>2</v>
+      </c>
+      <c r="E220" s="1">
+        <v>16</v>
+      </c>
+      <c r="F220" s="8">
+        <v>3</v>
+      </c>
+      <c r="G220" s="8">
+        <v>2045</v>
+      </c>
+      <c r="H220" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" spans="3:8">
+      <c r="C221" s="1">
+        <v>306</v>
+      </c>
+      <c r="D221" s="1">
+        <v>2</v>
+      </c>
+      <c r="E221" s="1">
+        <v>16</v>
+      </c>
+      <c r="F221" s="8">
+        <v>4</v>
+      </c>
+      <c r="G221" s="8">
+        <v>2043</v>
+      </c>
+      <c r="H221" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" spans="3:8">
+      <c r="C222" s="1">
+        <v>307</v>
+      </c>
+      <c r="D222" s="1">
+        <v>2</v>
+      </c>
+      <c r="E222" s="1">
+        <v>16</v>
+      </c>
+      <c r="F222" s="8">
+        <v>4</v>
+      </c>
+      <c r="G222" s="8">
+        <v>2044</v>
+      </c>
+      <c r="H222" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" spans="3:8">
+      <c r="C223" s="1">
+        <v>308</v>
+      </c>
+      <c r="D223" s="1">
+        <v>2</v>
+      </c>
+      <c r="E223" s="1">
+        <v>16</v>
+      </c>
+      <c r="F223" s="8">
+        <v>4</v>
+      </c>
+      <c r="G223" s="8">
+        <v>2045</v>
+      </c>
+      <c r="H223" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" spans="3:8">
+      <c r="C224" s="1">
+        <v>309</v>
+      </c>
+      <c r="D224" s="1">
+        <v>2</v>
+      </c>
+      <c r="E224" s="1">
+        <v>16</v>
+      </c>
+      <c r="F224" s="8">
+        <v>4</v>
+      </c>
+      <c r="G224" s="8">
+        <v>2046</v>
+      </c>
+      <c r="H224" s="8">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">

--- a/Excel/SpiritDropConfig.xlsx
+++ b/Excel/SpiritDropConfig.xlsx
@@ -7,10 +7,12 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="生成配置" sheetId="2" r:id="rId1"/>
+    <sheet name="蜀国" sheetId="2" r:id="rId1"/>
+    <sheet name="吴国" sheetId="3" r:id="rId2"/>
+    <sheet name="魏国" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">生成配置!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">蜀国!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,8 +65,76 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 就是100%
+10 就是10%
+100就是1%</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 就是100%
+10 就是10%
+100就是1%</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="9">
   <si>
     <t>#</t>
   </si>
@@ -282,13 +352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,7 +736,7 @@
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -727,29 +797,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1069,26 +1140,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L224"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.58333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13.3333333333333" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3"/>
+    <col min="6" max="6" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
       <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1097,11 +1168,11 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1110,68 +1181,68 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1185,16 +1256,16 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
         <v>2031</v>
       </c>
-      <c r="H6" s="8">
-        <v>100</v>
-      </c>
-      <c r="K6" s="9"/>
+      <c r="H6" s="7">
+        <v>100</v>
+      </c>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" customHeight="1" spans="1:12">
       <c r="C7" s="1">
@@ -1206,16 +1277,16 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="8">
-        <v>2</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7">
         <v>2031</v>
       </c>
-      <c r="H7" s="8">
-        <v>100</v>
-      </c>
-      <c r="K7" s="9"/>
+      <c r="H7" s="7">
+        <v>100</v>
+      </c>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" customHeight="1" spans="1:12">
       <c r="C8" s="1">
@@ -1227,16 +1298,16 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="F8" s="7">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7">
         <v>2032</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>20</v>
       </c>
-      <c r="K8" s="9"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" customHeight="1" spans="1:12">
       <c r="C9" s="1">
@@ -1248,16 +1319,16 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
-        <v>3</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7">
         <v>2031</v>
       </c>
-      <c r="H9" s="8">
-        <v>100</v>
-      </c>
-      <c r="K9" s="9"/>
+      <c r="H9" s="7">
+        <v>100</v>
+      </c>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
       <c r="C10" s="1">
@@ -1269,16 +1340,16 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="8">
-        <v>3</v>
-      </c>
-      <c r="G10" s="8">
+      <c r="F10" s="7">
+        <v>3</v>
+      </c>
+      <c r="G10" s="7">
         <v>2032</v>
       </c>
-      <c r="H10" s="8">
-        <v>50</v>
-      </c>
-      <c r="K10" s="9"/>
+      <c r="H10" s="7">
+        <v>50</v>
+      </c>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" customHeight="1" spans="1:12">
       <c r="C11" s="1">
@@ -1290,16 +1361,16 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="8">
-        <v>3</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="F11" s="7">
+        <v>3</v>
+      </c>
+      <c r="G11" s="7">
         <v>2033</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>20</v>
       </c>
-      <c r="K11" s="9"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" customHeight="1" spans="1:12">
       <c r="C12" s="1">
@@ -1311,16 +1382,16 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="8">
-        <v>4</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="F12" s="7">
+        <v>4</v>
+      </c>
+      <c r="G12" s="7">
         <v>2031</v>
       </c>
-      <c r="H12" s="8">
-        <v>100</v>
-      </c>
-      <c r="K12" s="9"/>
+      <c r="H12" s="7">
+        <v>100</v>
+      </c>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" customHeight="1" spans="1:12">
       <c r="C13" s="1">
@@ -1332,16 +1403,16 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="8">
-        <v>4</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="F13" s="7">
+        <v>4</v>
+      </c>
+      <c r="G13" s="7">
         <v>2032</v>
       </c>
-      <c r="H13" s="8">
-        <v>50</v>
-      </c>
-      <c r="K13" s="9"/>
+      <c r="H13" s="7">
+        <v>50</v>
+      </c>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
       <c r="C14" s="1">
@@ -1353,16 +1424,16 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="8">
-        <v>4</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="F14" s="7">
+        <v>4</v>
+      </c>
+      <c r="G14" s="7">
         <v>2033</v>
       </c>
-      <c r="H14" s="8">
-        <v>50</v>
-      </c>
-      <c r="K14" s="9"/>
+      <c r="H14" s="7">
+        <v>50</v>
+      </c>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" customHeight="1" spans="1:12">
       <c r="C15" s="1">
@@ -1374,34 +1445,34 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="8">
-        <v>4</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="F15" s="7">
+        <v>4</v>
+      </c>
+      <c r="G15" s="7">
         <v>2034</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <v>20</v>
       </c>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" s="11" customFormat="1" customHeight="1" spans="1:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10">
-        <v>2</v>
-      </c>
-      <c r="F16" s="11">
-        <v>1</v>
-      </c>
-      <c r="G16" s="11">
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
         <v>2031</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1415,16 +1486,16 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="8">
-        <v>1</v>
-      </c>
-      <c r="G17" s="8">
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
         <v>2032</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>20</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="12"/>
     </row>
     <row r="18" customHeight="1" spans="3:12">
       <c r="C18" s="1">
@@ -1436,16 +1507,16 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="8">
-        <v>2</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="F18" s="7">
+        <v>2</v>
+      </c>
+      <c r="G18" s="7">
         <v>2031</v>
       </c>
-      <c r="H18" s="8">
-        <v>100</v>
-      </c>
-      <c r="K18" s="9"/>
+      <c r="H18" s="7">
+        <v>100</v>
+      </c>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" customHeight="1" spans="3:12">
       <c r="C19" s="1">
@@ -1457,16 +1528,16 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="8">
-        <v>2</v>
-      </c>
-      <c r="G19" s="8">
+      <c r="F19" s="7">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7">
         <v>2032</v>
       </c>
-      <c r="H19" s="8">
-        <v>50</v>
-      </c>
-      <c r="K19" s="9"/>
+      <c r="H19" s="7">
+        <v>50</v>
+      </c>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" customHeight="1" spans="3:12">
       <c r="C20" s="1">
@@ -1478,16 +1549,16 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="8">
-        <v>3</v>
-      </c>
-      <c r="G20" s="8">
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
         <v>2031</v>
       </c>
-      <c r="H20" s="8">
-        <v>100</v>
-      </c>
-      <c r="K20" s="9"/>
+      <c r="H20" s="7">
+        <v>100</v>
+      </c>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
@@ -1499,16 +1570,16 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="8">
-        <v>3</v>
-      </c>
-      <c r="G21" s="8">
+      <c r="F21" s="7">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
         <v>2032</v>
       </c>
-      <c r="H21" s="8">
-        <v>50</v>
-      </c>
-      <c r="K21" s="9"/>
+      <c r="H21" s="7">
+        <v>50</v>
+      </c>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" customHeight="1" spans="3:12">
       <c r="C22" s="1">
@@ -1520,17 +1591,17 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="8">
-        <v>3</v>
-      </c>
-      <c r="G22" s="8">
+      <c r="F22" s="7">
+        <v>3</v>
+      </c>
+      <c r="G22" s="7">
         <v>2033</v>
       </c>
-      <c r="H22" s="8">
-        <v>50</v>
-      </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="H22" s="7">
+        <v>50</v>
+      </c>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
     </row>
     <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
@@ -1542,17 +1613,17 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="8">
-        <v>4</v>
-      </c>
-      <c r="G23" s="8">
+      <c r="F23" s="7">
+        <v>4</v>
+      </c>
+      <c r="G23" s="7">
         <v>2031</v>
       </c>
-      <c r="H23" s="8">
-        <v>100</v>
-      </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="H23" s="7">
+        <v>100</v>
+      </c>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
     </row>
     <row r="24" customHeight="1" spans="3:12">
       <c r="C24" s="1">
@@ -1564,16 +1635,16 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="8">
-        <v>4</v>
-      </c>
-      <c r="G24" s="8">
+      <c r="F24" s="7">
+        <v>4</v>
+      </c>
+      <c r="G24" s="7">
         <v>2032</v>
       </c>
-      <c r="H24" s="8">
-        <v>100</v>
-      </c>
-      <c r="K24" s="9"/>
+      <c r="H24" s="7">
+        <v>100</v>
+      </c>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" customHeight="1" spans="3:12">
       <c r="C25" s="1">
@@ -1585,16 +1656,16 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="8">
-        <v>4</v>
-      </c>
-      <c r="G25" s="8">
+      <c r="F25" s="7">
+        <v>4</v>
+      </c>
+      <c r="G25" s="7">
         <v>2033</v>
       </c>
-      <c r="H25" s="8">
-        <v>50</v>
-      </c>
-      <c r="K25" s="9"/>
+      <c r="H25" s="7">
+        <v>50</v>
+      </c>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" customHeight="1" spans="3:12">
       <c r="C26" s="1">
@@ -1606,33 +1677,33 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="8">
-        <v>4</v>
-      </c>
-      <c r="G26" s="8">
+      <c r="F26" s="7">
+        <v>4</v>
+      </c>
+      <c r="G26" s="7">
         <v>2034</v>
       </c>
-      <c r="H26" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H26" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="11" customFormat="1" customHeight="1" spans="3:12">
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="10">
-        <v>1</v>
-      </c>
-      <c r="E27" s="10">
-        <v>3</v>
-      </c>
-      <c r="F27" s="11">
-        <v>1</v>
-      </c>
-      <c r="G27" s="11">
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
         <v>2031</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="7">
         <v>100</v>
       </c>
     </row>
@@ -1646,16 +1717,16 @@
       <c r="E28" s="1">
         <v>3</v>
       </c>
-      <c r="F28" s="8">
-        <v>1</v>
-      </c>
-      <c r="G28" s="8">
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7">
         <v>2032</v>
       </c>
-      <c r="H28" s="8">
-        <v>50</v>
-      </c>
-      <c r="K28" s="9"/>
+      <c r="H28" s="7">
+        <v>50</v>
+      </c>
+      <c r="K28" s="12"/>
     </row>
     <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
@@ -1667,16 +1738,16 @@
       <c r="E29" s="1">
         <v>3</v>
       </c>
-      <c r="F29" s="8">
-        <v>2</v>
-      </c>
-      <c r="G29" s="8">
+      <c r="F29" s="7">
+        <v>2</v>
+      </c>
+      <c r="G29" s="7">
         <v>2031</v>
       </c>
-      <c r="H29" s="8">
-        <v>100</v>
-      </c>
-      <c r="K29" s="9"/>
+      <c r="H29" s="7">
+        <v>100</v>
+      </c>
+      <c r="K29" s="12"/>
     </row>
     <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
@@ -1688,16 +1759,16 @@
       <c r="E30" s="1">
         <v>3</v>
       </c>
-      <c r="F30" s="8">
-        <v>2</v>
-      </c>
-      <c r="G30" s="8">
+      <c r="F30" s="7">
+        <v>2</v>
+      </c>
+      <c r="G30" s="7">
         <v>2032</v>
       </c>
-      <c r="H30" s="8">
-        <v>50</v>
-      </c>
-      <c r="K30" s="9"/>
+      <c r="H30" s="7">
+        <v>50</v>
+      </c>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
@@ -1709,16 +1780,16 @@
       <c r="E31" s="1">
         <v>3</v>
       </c>
-      <c r="F31" s="8">
-        <v>2</v>
-      </c>
-      <c r="G31" s="8">
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
         <v>2033</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="7">
         <v>20</v>
       </c>
-      <c r="K31" s="9"/>
+      <c r="K31" s="12"/>
     </row>
     <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
@@ -1730,16 +1801,16 @@
       <c r="E32" s="1">
         <v>3</v>
       </c>
-      <c r="F32" s="8">
-        <v>3</v>
-      </c>
-      <c r="G32" s="8">
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="7">
         <v>2032</v>
       </c>
-      <c r="H32" s="8">
-        <v>100</v>
-      </c>
-      <c r="K32" s="9"/>
+      <c r="H32" s="7">
+        <v>100</v>
+      </c>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
@@ -1751,16 +1822,16 @@
       <c r="E33" s="1">
         <v>3</v>
       </c>
-      <c r="F33" s="8">
-        <v>3</v>
-      </c>
-      <c r="G33" s="8">
+      <c r="F33" s="7">
+        <v>3</v>
+      </c>
+      <c r="G33" s="7">
         <v>2033</v>
       </c>
-      <c r="H33" s="8">
-        <v>50</v>
-      </c>
-      <c r="K33" s="9"/>
+      <c r="H33" s="7">
+        <v>50</v>
+      </c>
+      <c r="K33" s="12"/>
     </row>
     <row r="34" customHeight="1" spans="3:12">
       <c r="C34" s="1">
@@ -1772,17 +1843,17 @@
       <c r="E34" s="1">
         <v>3</v>
       </c>
-      <c r="F34" s="8">
-        <v>3</v>
-      </c>
-      <c r="G34" s="8">
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="7">
         <v>2034</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>20</v>
       </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
     </row>
     <row r="35" customHeight="1" spans="3:12">
       <c r="C35" s="1">
@@ -1794,17 +1865,17 @@
       <c r="E35" s="1">
         <v>3</v>
       </c>
-      <c r="F35" s="8">
-        <v>4</v>
-      </c>
-      <c r="G35" s="8">
+      <c r="F35" s="7">
+        <v>4</v>
+      </c>
+      <c r="G35" s="7">
         <v>2032</v>
       </c>
-      <c r="H35" s="8">
-        <v>100</v>
-      </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
+      <c r="H35" s="7">
+        <v>100</v>
+      </c>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36" customHeight="1" spans="3:12">
       <c r="C36" s="1">
@@ -1816,16 +1887,16 @@
       <c r="E36" s="1">
         <v>3</v>
       </c>
-      <c r="F36" s="8">
-        <v>4</v>
-      </c>
-      <c r="G36" s="8">
+      <c r="F36" s="7">
+        <v>4</v>
+      </c>
+      <c r="G36" s="7">
         <v>2033</v>
       </c>
-      <c r="H36" s="8">
-        <v>100</v>
-      </c>
-      <c r="K36" s="9"/>
+      <c r="H36" s="7">
+        <v>100</v>
+      </c>
+      <c r="K36" s="12"/>
     </row>
     <row r="37" customHeight="1" spans="3:12">
       <c r="C37" s="1">
@@ -1837,16 +1908,16 @@
       <c r="E37" s="1">
         <v>3</v>
       </c>
-      <c r="F37" s="8">
-        <v>4</v>
-      </c>
-      <c r="G37" s="8">
+      <c r="F37" s="7">
+        <v>4</v>
+      </c>
+      <c r="G37" s="7">
         <v>2034</v>
       </c>
-      <c r="H37" s="8">
-        <v>50</v>
-      </c>
-      <c r="K37" s="9"/>
+      <c r="H37" s="7">
+        <v>50</v>
+      </c>
+      <c r="K37" s="12"/>
     </row>
     <row r="38" customHeight="1" spans="3:12">
       <c r="C38" s="1">
@@ -1858,33 +1929,33 @@
       <c r="E38" s="1">
         <v>3</v>
       </c>
-      <c r="F38" s="8">
-        <v>4</v>
-      </c>
-      <c r="G38" s="8">
+      <c r="F38" s="7">
+        <v>4</v>
+      </c>
+      <c r="G38" s="7">
         <v>2035</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="39" s="11" customFormat="1" customHeight="1" spans="3:12">
       <c r="C39" s="1">
         <v>34</v>
       </c>
-      <c r="D39" s="10">
-        <v>1</v>
-      </c>
-      <c r="E39" s="10">
-        <v>4</v>
-      </c>
-      <c r="F39" s="11">
-        <v>1</v>
-      </c>
-      <c r="G39" s="11">
+      <c r="D39" s="8">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8">
+        <v>4</v>
+      </c>
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
         <v>2031</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="7">
         <v>100</v>
       </c>
     </row>
@@ -1898,16 +1969,16 @@
       <c r="E40" s="1">
         <v>4</v>
       </c>
-      <c r="F40" s="8">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8">
+      <c r="F40" s="7">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
         <v>2032</v>
       </c>
-      <c r="H40" s="8">
-        <v>50</v>
-      </c>
-      <c r="K40" s="9"/>
+      <c r="H40" s="7">
+        <v>50</v>
+      </c>
+      <c r="K40" s="12"/>
     </row>
     <row r="41" customHeight="1" spans="3:12">
       <c r="C41" s="1">
@@ -1919,16 +1990,16 @@
       <c r="E41" s="1">
         <v>4</v>
       </c>
-      <c r="F41" s="8">
-        <v>1</v>
-      </c>
-      <c r="G41" s="8">
+      <c r="F41" s="7">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
         <v>2033</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="7">
         <v>20</v>
       </c>
-      <c r="K41" s="9"/>
+      <c r="K41" s="12"/>
     </row>
     <row r="42" customHeight="1" spans="3:12">
       <c r="C42" s="1">
@@ -1940,16 +2011,16 @@
       <c r="E42" s="1">
         <v>4</v>
       </c>
-      <c r="F42" s="8">
-        <v>2</v>
-      </c>
-      <c r="G42" s="8">
+      <c r="F42" s="7">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7">
         <v>2031</v>
       </c>
-      <c r="H42" s="8">
-        <v>100</v>
-      </c>
-      <c r="K42" s="9"/>
+      <c r="H42" s="7">
+        <v>100</v>
+      </c>
+      <c r="K42" s="12"/>
     </row>
     <row r="43" customHeight="1" spans="3:12">
       <c r="C43" s="1">
@@ -1961,16 +2032,16 @@
       <c r="E43" s="1">
         <v>4</v>
       </c>
-      <c r="F43" s="8">
-        <v>2</v>
-      </c>
-      <c r="G43" s="8">
+      <c r="F43" s="7">
+        <v>2</v>
+      </c>
+      <c r="G43" s="7">
         <v>2032</v>
       </c>
-      <c r="H43" s="8">
-        <v>50</v>
-      </c>
-      <c r="K43" s="9"/>
+      <c r="H43" s="7">
+        <v>50</v>
+      </c>
+      <c r="K43" s="12"/>
     </row>
     <row r="44" customHeight="1" spans="3:12">
       <c r="C44" s="1">
@@ -1982,16 +2053,16 @@
       <c r="E44" s="1">
         <v>4</v>
       </c>
-      <c r="F44" s="8">
-        <v>2</v>
-      </c>
-      <c r="G44" s="8">
+      <c r="F44" s="7">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
         <v>2033</v>
       </c>
-      <c r="H44" s="8">
-        <v>50</v>
-      </c>
-      <c r="K44" s="9"/>
+      <c r="H44" s="7">
+        <v>50</v>
+      </c>
+      <c r="K44" s="12"/>
     </row>
     <row r="45" customHeight="1" spans="3:12">
       <c r="C45" s="1">
@@ -2003,16 +2074,16 @@
       <c r="E45" s="1">
         <v>4</v>
       </c>
-      <c r="F45" s="8">
-        <v>3</v>
-      </c>
-      <c r="G45" s="8">
+      <c r="F45" s="7">
+        <v>3</v>
+      </c>
+      <c r="G45" s="7">
         <v>2032</v>
       </c>
-      <c r="H45" s="8">
-        <v>100</v>
-      </c>
-      <c r="K45" s="9"/>
+      <c r="H45" s="7">
+        <v>100</v>
+      </c>
+      <c r="K45" s="12"/>
     </row>
     <row r="46" customHeight="1" spans="3:12">
       <c r="C46" s="1">
@@ -2024,16 +2095,16 @@
       <c r="E46" s="1">
         <v>4</v>
       </c>
-      <c r="F46" s="8">
-        <v>3</v>
-      </c>
-      <c r="G46" s="8">
+      <c r="F46" s="7">
+        <v>3</v>
+      </c>
+      <c r="G46" s="7">
         <v>2033</v>
       </c>
-      <c r="H46" s="8">
-        <v>50</v>
-      </c>
-      <c r="K46" s="9"/>
+      <c r="H46" s="7">
+        <v>50</v>
+      </c>
+      <c r="K46" s="12"/>
     </row>
     <row r="47" customHeight="1" spans="3:12">
       <c r="C47" s="1">
@@ -2045,17 +2116,17 @@
       <c r="E47" s="1">
         <v>4</v>
       </c>
-      <c r="F47" s="8">
-        <v>3</v>
-      </c>
-      <c r="G47" s="8">
+      <c r="F47" s="7">
+        <v>3</v>
+      </c>
+      <c r="G47" s="7">
         <v>2034</v>
       </c>
-      <c r="H47" s="8">
-        <v>50</v>
-      </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
+      <c r="H47" s="7">
+        <v>50</v>
+      </c>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
     </row>
     <row r="48" customHeight="1" spans="3:12">
       <c r="C48" s="1">
@@ -2067,17 +2138,17 @@
       <c r="E48" s="1">
         <v>4</v>
       </c>
-      <c r="F48" s="8">
-        <v>4</v>
-      </c>
-      <c r="G48" s="8">
+      <c r="F48" s="7">
+        <v>4</v>
+      </c>
+      <c r="G48" s="7">
         <v>2032</v>
       </c>
-      <c r="H48" s="8">
-        <v>100</v>
-      </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
+      <c r="H48" s="7">
+        <v>100</v>
+      </c>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
     </row>
     <row r="49" customHeight="1" spans="3:12">
       <c r="C49" s="1">
@@ -2089,16 +2160,16 @@
       <c r="E49" s="1">
         <v>4</v>
       </c>
-      <c r="F49" s="8">
-        <v>4</v>
-      </c>
-      <c r="G49" s="8">
+      <c r="F49" s="7">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7">
         <v>2033</v>
       </c>
-      <c r="H49" s="8">
-        <v>100</v>
-      </c>
-      <c r="K49" s="9"/>
+      <c r="H49" s="7">
+        <v>100</v>
+      </c>
+      <c r="K49" s="12"/>
     </row>
     <row r="50" customHeight="1" spans="3:12">
       <c r="C50" s="1">
@@ -2110,16 +2181,16 @@
       <c r="E50" s="1">
         <v>4</v>
       </c>
-      <c r="F50" s="8">
-        <v>4</v>
-      </c>
-      <c r="G50" s="8">
+      <c r="F50" s="7">
+        <v>4</v>
+      </c>
+      <c r="G50" s="7">
         <v>2034</v>
       </c>
-      <c r="H50" s="8">
-        <v>50</v>
-      </c>
-      <c r="K50" s="9"/>
+      <c r="H50" s="7">
+        <v>50</v>
+      </c>
+      <c r="K50" s="12"/>
     </row>
     <row r="51" customHeight="1" spans="3:12">
       <c r="C51" s="1">
@@ -2131,33 +2202,33 @@
       <c r="E51" s="1">
         <v>4</v>
       </c>
-      <c r="F51" s="8">
-        <v>4</v>
-      </c>
-      <c r="G51" s="8">
+      <c r="F51" s="7">
+        <v>4</v>
+      </c>
+      <c r="G51" s="7">
         <v>2035</v>
       </c>
-      <c r="H51" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H51" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="11" customFormat="1" customHeight="1" spans="3:12">
       <c r="C52" s="1">
         <v>47</v>
       </c>
-      <c r="D52" s="10">
-        <v>1</v>
-      </c>
-      <c r="E52" s="10">
+      <c r="D52" s="8">
+        <v>1</v>
+      </c>
+      <c r="E52" s="8">
         <v>5</v>
       </c>
-      <c r="F52" s="11">
-        <v>1</v>
-      </c>
-      <c r="G52" s="11">
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9">
         <v>2031</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="7">
         <v>100</v>
       </c>
     </row>
@@ -2171,16 +2242,16 @@
       <c r="E53" s="1">
         <v>5</v>
       </c>
-      <c r="F53" s="8">
-        <v>1</v>
-      </c>
-      <c r="G53" s="8">
+      <c r="F53" s="7">
+        <v>1</v>
+      </c>
+      <c r="G53" s="7">
         <v>2032</v>
       </c>
-      <c r="H53" s="8">
-        <v>50</v>
-      </c>
-      <c r="K53" s="9"/>
+      <c r="H53" s="7">
+        <v>50</v>
+      </c>
+      <c r="K53" s="12"/>
     </row>
     <row r="54" customHeight="1" spans="3:12">
       <c r="C54" s="1">
@@ -2192,16 +2263,16 @@
       <c r="E54" s="1">
         <v>5</v>
       </c>
-      <c r="F54" s="8">
-        <v>1</v>
-      </c>
-      <c r="G54" s="8">
+      <c r="F54" s="7">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7">
         <v>2033</v>
       </c>
-      <c r="H54" s="8">
-        <v>50</v>
-      </c>
-      <c r="K54" s="9"/>
+      <c r="H54" s="7">
+        <v>50</v>
+      </c>
+      <c r="K54" s="12"/>
     </row>
     <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="1">
@@ -2213,16 +2284,16 @@
       <c r="E55" s="1">
         <v>5</v>
       </c>
-      <c r="F55" s="8">
-        <v>2</v>
-      </c>
-      <c r="G55" s="8">
+      <c r="F55" s="7">
+        <v>2</v>
+      </c>
+      <c r="G55" s="7">
         <v>2031</v>
       </c>
-      <c r="H55" s="8">
-        <v>100</v>
-      </c>
-      <c r="K55" s="9"/>
+      <c r="H55" s="7">
+        <v>100</v>
+      </c>
+      <c r="K55" s="12"/>
     </row>
     <row r="56" customHeight="1" spans="3:12">
       <c r="C56" s="1">
@@ -2234,16 +2305,16 @@
       <c r="E56" s="1">
         <v>5</v>
       </c>
-      <c r="F56" s="8">
-        <v>2</v>
-      </c>
-      <c r="G56" s="8">
+      <c r="F56" s="7">
+        <v>2</v>
+      </c>
+      <c r="G56" s="7">
         <v>2032</v>
       </c>
-      <c r="H56" s="8">
-        <v>50</v>
-      </c>
-      <c r="K56" s="9"/>
+      <c r="H56" s="7">
+        <v>50</v>
+      </c>
+      <c r="K56" s="12"/>
     </row>
     <row r="57" customHeight="1" spans="3:12">
       <c r="C57" s="1">
@@ -2255,16 +2326,16 @@
       <c r="E57" s="1">
         <v>5</v>
       </c>
-      <c r="F57" s="8">
-        <v>2</v>
-      </c>
-      <c r="G57" s="8">
+      <c r="F57" s="7">
+        <v>2</v>
+      </c>
+      <c r="G57" s="7">
         <v>2033</v>
       </c>
-      <c r="H57" s="8">
-        <v>50</v>
-      </c>
-      <c r="K57" s="9"/>
+      <c r="H57" s="7">
+        <v>50</v>
+      </c>
+      <c r="K57" s="12"/>
     </row>
     <row r="58" customHeight="1" spans="3:12">
       <c r="C58" s="1">
@@ -2276,16 +2347,16 @@
       <c r="E58" s="1">
         <v>5</v>
       </c>
-      <c r="F58" s="8">
-        <v>2</v>
-      </c>
-      <c r="G58" s="8">
+      <c r="F58" s="7">
+        <v>2</v>
+      </c>
+      <c r="G58" s="7">
         <v>2034</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="7">
         <v>20</v>
       </c>
-      <c r="K58" s="9"/>
+      <c r="K58" s="12"/>
     </row>
     <row r="59" customHeight="1" spans="3:12">
       <c r="C59" s="1">
@@ -2297,16 +2368,16 @@
       <c r="E59" s="1">
         <v>5</v>
       </c>
-      <c r="F59" s="8">
-        <v>3</v>
-      </c>
-      <c r="G59" s="8">
+      <c r="F59" s="7">
+        <v>3</v>
+      </c>
+      <c r="G59" s="7">
         <v>2032</v>
       </c>
-      <c r="H59" s="8">
-        <v>100</v>
-      </c>
-      <c r="K59" s="9"/>
+      <c r="H59" s="7">
+        <v>100</v>
+      </c>
+      <c r="K59" s="12"/>
     </row>
     <row r="60" customHeight="1" spans="3:12">
       <c r="C60" s="1">
@@ -2318,16 +2389,16 @@
       <c r="E60" s="1">
         <v>5</v>
       </c>
-      <c r="F60" s="8">
-        <v>3</v>
-      </c>
-      <c r="G60" s="8">
+      <c r="F60" s="7">
+        <v>3</v>
+      </c>
+      <c r="G60" s="7">
         <v>2033</v>
       </c>
-      <c r="H60" s="8">
-        <v>50</v>
-      </c>
-      <c r="K60" s="9"/>
+      <c r="H60" s="7">
+        <v>50</v>
+      </c>
+      <c r="K60" s="12"/>
     </row>
     <row r="61" customHeight="1" spans="3:12">
       <c r="C61" s="1">
@@ -2339,17 +2410,17 @@
       <c r="E61" s="1">
         <v>5</v>
       </c>
-      <c r="F61" s="8">
-        <v>3</v>
-      </c>
-      <c r="G61" s="8">
+      <c r="F61" s="7">
+        <v>3</v>
+      </c>
+      <c r="G61" s="7">
         <v>2034</v>
       </c>
-      <c r="H61" s="8">
-        <v>50</v>
-      </c>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
+      <c r="H61" s="7">
+        <v>50</v>
+      </c>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
     </row>
     <row r="62" customHeight="1" spans="3:12">
       <c r="C62" s="1">
@@ -2361,17 +2432,17 @@
       <c r="E62" s="1">
         <v>5</v>
       </c>
-      <c r="F62" s="8">
-        <v>3</v>
-      </c>
-      <c r="G62" s="8">
+      <c r="F62" s="7">
+        <v>3</v>
+      </c>
+      <c r="G62" s="7">
         <v>2035</v>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="7">
         <v>20</v>
       </c>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
     </row>
     <row r="63" customHeight="1" spans="3:12">
       <c r="C63" s="1">
@@ -2383,17 +2454,17 @@
       <c r="E63" s="1">
         <v>5</v>
       </c>
-      <c r="F63" s="8">
-        <v>4</v>
-      </c>
-      <c r="G63" s="8">
+      <c r="F63" s="7">
+        <v>4</v>
+      </c>
+      <c r="G63" s="7">
         <v>2033</v>
       </c>
-      <c r="H63" s="8">
-        <v>100</v>
-      </c>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
+      <c r="H63" s="7">
+        <v>100</v>
+      </c>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
     </row>
     <row r="64" customHeight="1" spans="3:12">
       <c r="C64" s="1">
@@ -2405,16 +2476,16 @@
       <c r="E64" s="1">
         <v>5</v>
       </c>
-      <c r="F64" s="8">
-        <v>4</v>
-      </c>
-      <c r="G64" s="8">
+      <c r="F64" s="7">
+        <v>4</v>
+      </c>
+      <c r="G64" s="7">
         <v>2034</v>
       </c>
-      <c r="H64" s="8">
-        <v>100</v>
-      </c>
-      <c r="K64" s="9"/>
+      <c r="H64" s="7">
+        <v>100</v>
+      </c>
+      <c r="K64" s="12"/>
     </row>
     <row r="65" customHeight="1" spans="3:12">
       <c r="C65" s="1">
@@ -2426,16 +2497,16 @@
       <c r="E65" s="1">
         <v>5</v>
       </c>
-      <c r="F65" s="8">
-        <v>4</v>
-      </c>
-      <c r="G65" s="8">
+      <c r="F65" s="7">
+        <v>4</v>
+      </c>
+      <c r="G65" s="7">
         <v>2035</v>
       </c>
-      <c r="H65" s="8">
-        <v>50</v>
-      </c>
-      <c r="K65" s="9"/>
+      <c r="H65" s="7">
+        <v>50</v>
+      </c>
+      <c r="K65" s="12"/>
     </row>
     <row r="66" customHeight="1" spans="3:12">
       <c r="C66" s="1">
@@ -2447,33 +2518,33 @@
       <c r="E66" s="1">
         <v>5</v>
       </c>
-      <c r="F66" s="8">
-        <v>4</v>
-      </c>
-      <c r="G66" s="8">
+      <c r="F66" s="7">
+        <v>4</v>
+      </c>
+      <c r="G66" s="7">
         <v>2036</v>
       </c>
-      <c r="H66" s="8">
+      <c r="H66" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="67" s="11" customFormat="1" customHeight="1" spans="3:12">
       <c r="C67" s="1">
         <v>62</v>
       </c>
-      <c r="D67" s="10">
-        <v>1</v>
-      </c>
-      <c r="E67" s="10">
+      <c r="D67" s="8">
+        <v>1</v>
+      </c>
+      <c r="E67" s="8">
         <v>6</v>
       </c>
-      <c r="F67" s="11">
-        <v>1</v>
-      </c>
-      <c r="G67" s="11">
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9">
         <v>2031</v>
       </c>
-      <c r="H67" s="8">
+      <c r="H67" s="7">
         <v>100</v>
       </c>
     </row>
@@ -2487,16 +2558,16 @@
       <c r="E68" s="1">
         <v>6</v>
       </c>
-      <c r="F68" s="8">
-        <v>1</v>
-      </c>
-      <c r="G68" s="8">
+      <c r="F68" s="7">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7">
         <v>2032</v>
       </c>
-      <c r="H68" s="8">
-        <v>50</v>
-      </c>
-      <c r="K68" s="9"/>
+      <c r="H68" s="7">
+        <v>50</v>
+      </c>
+      <c r="K68" s="12"/>
     </row>
     <row r="69" customHeight="1" spans="3:12">
       <c r="C69" s="1">
@@ -2508,16 +2579,16 @@
       <c r="E69" s="1">
         <v>6</v>
       </c>
-      <c r="F69" s="8">
-        <v>1</v>
-      </c>
-      <c r="G69" s="8">
+      <c r="F69" s="7">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
         <v>2033</v>
       </c>
-      <c r="H69" s="8">
-        <v>50</v>
-      </c>
-      <c r="K69" s="9"/>
+      <c r="H69" s="7">
+        <v>50</v>
+      </c>
+      <c r="K69" s="12"/>
     </row>
     <row r="70" customHeight="1" spans="3:12">
       <c r="C70" s="1">
@@ -2529,16 +2600,16 @@
       <c r="E70" s="1">
         <v>6</v>
       </c>
-      <c r="F70" s="8">
-        <v>1</v>
-      </c>
-      <c r="G70" s="8">
+      <c r="F70" s="7">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7">
         <v>2034</v>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="7">
         <v>20</v>
       </c>
-      <c r="K70" s="9"/>
+      <c r="K70" s="12"/>
     </row>
     <row r="71" customHeight="1" spans="3:12">
       <c r="C71" s="1">
@@ -2550,16 +2621,16 @@
       <c r="E71" s="1">
         <v>6</v>
       </c>
-      <c r="F71" s="8">
-        <v>2</v>
-      </c>
-      <c r="G71" s="8">
+      <c r="F71" s="7">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7">
         <v>2031</v>
       </c>
-      <c r="H71" s="8">
-        <v>100</v>
-      </c>
-      <c r="K71" s="9"/>
+      <c r="H71" s="7">
+        <v>100</v>
+      </c>
+      <c r="K71" s="12"/>
     </row>
     <row r="72" customHeight="1" spans="3:12">
       <c r="C72" s="1">
@@ -2571,16 +2642,16 @@
       <c r="E72" s="1">
         <v>6</v>
       </c>
-      <c r="F72" s="8">
-        <v>2</v>
-      </c>
-      <c r="G72" s="8">
+      <c r="F72" s="7">
+        <v>2</v>
+      </c>
+      <c r="G72" s="7">
         <v>2032</v>
       </c>
-      <c r="H72" s="8">
-        <v>50</v>
-      </c>
-      <c r="K72" s="9"/>
+      <c r="H72" s="7">
+        <v>50</v>
+      </c>
+      <c r="K72" s="12"/>
     </row>
     <row r="73" customHeight="1" spans="3:12">
       <c r="C73" s="1">
@@ -2592,16 +2663,16 @@
       <c r="E73" s="1">
         <v>6</v>
       </c>
-      <c r="F73" s="8">
-        <v>2</v>
-      </c>
-      <c r="G73" s="8">
+      <c r="F73" s="7">
+        <v>2</v>
+      </c>
+      <c r="G73" s="7">
         <v>2033</v>
       </c>
-      <c r="H73" s="8">
-        <v>50</v>
-      </c>
-      <c r="K73" s="9"/>
+      <c r="H73" s="7">
+        <v>50</v>
+      </c>
+      <c r="K73" s="12"/>
     </row>
     <row r="74" customHeight="1" spans="3:12">
       <c r="C74" s="1">
@@ -2613,16 +2684,16 @@
       <c r="E74" s="1">
         <v>6</v>
       </c>
-      <c r="F74" s="8">
-        <v>2</v>
-      </c>
-      <c r="G74" s="8">
+      <c r="F74" s="7">
+        <v>2</v>
+      </c>
+      <c r="G74" s="7">
         <v>2034</v>
       </c>
-      <c r="H74" s="8">
-        <v>50</v>
-      </c>
-      <c r="K74" s="9"/>
+      <c r="H74" s="7">
+        <v>50</v>
+      </c>
+      <c r="K74" s="12"/>
     </row>
     <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
@@ -2634,16 +2705,16 @@
       <c r="E75" s="1">
         <v>6</v>
       </c>
-      <c r="F75" s="8">
-        <v>3</v>
-      </c>
-      <c r="G75" s="8">
+      <c r="F75" s="7">
+        <v>3</v>
+      </c>
+      <c r="G75" s="7">
         <v>2032</v>
       </c>
-      <c r="H75" s="8">
-        <v>100</v>
-      </c>
-      <c r="K75" s="9"/>
+      <c r="H75" s="7">
+        <v>100</v>
+      </c>
+      <c r="K75" s="12"/>
     </row>
     <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
@@ -2655,16 +2726,16 @@
       <c r="E76" s="1">
         <v>6</v>
       </c>
-      <c r="F76" s="8">
-        <v>3</v>
-      </c>
-      <c r="G76" s="8">
+      <c r="F76" s="7">
+        <v>3</v>
+      </c>
+      <c r="G76" s="7">
         <v>2033</v>
       </c>
-      <c r="H76" s="8">
-        <v>50</v>
-      </c>
-      <c r="K76" s="9"/>
+      <c r="H76" s="7">
+        <v>50</v>
+      </c>
+      <c r="K76" s="12"/>
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
@@ -2676,17 +2747,17 @@
       <c r="E77" s="1">
         <v>6</v>
       </c>
-      <c r="F77" s="8">
-        <v>3</v>
-      </c>
-      <c r="G77" s="8">
+      <c r="F77" s="7">
+        <v>3</v>
+      </c>
+      <c r="G77" s="7">
         <v>2034</v>
       </c>
-      <c r="H77" s="8">
-        <v>50</v>
-      </c>
-      <c r="K77" s="9"/>
-      <c r="L77" s="9"/>
+      <c r="H77" s="7">
+        <v>50</v>
+      </c>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
@@ -2698,17 +2769,17 @@
       <c r="E78" s="1">
         <v>6</v>
       </c>
-      <c r="F78" s="8">
-        <v>3</v>
-      </c>
-      <c r="G78" s="8">
+      <c r="F78" s="7">
+        <v>3</v>
+      </c>
+      <c r="G78" s="7">
         <v>2035</v>
       </c>
-      <c r="H78" s="8">
-        <v>50</v>
-      </c>
-      <c r="K78" s="9"/>
-      <c r="L78" s="9"/>
+      <c r="H78" s="7">
+        <v>50</v>
+      </c>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
@@ -2720,17 +2791,17 @@
       <c r="E79" s="1">
         <v>6</v>
       </c>
-      <c r="F79" s="8">
-        <v>4</v>
-      </c>
-      <c r="G79" s="8">
+      <c r="F79" s="7">
+        <v>4</v>
+      </c>
+      <c r="G79" s="7">
         <v>2033</v>
       </c>
-      <c r="H79" s="8">
-        <v>100</v>
-      </c>
-      <c r="K79" s="9"/>
-      <c r="L79" s="9"/>
+      <c r="H79" s="7">
+        <v>100</v>
+      </c>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
@@ -2742,16 +2813,16 @@
       <c r="E80" s="1">
         <v>6</v>
       </c>
-      <c r="F80" s="8">
-        <v>4</v>
-      </c>
-      <c r="G80" s="8">
+      <c r="F80" s="7">
+        <v>4</v>
+      </c>
+      <c r="G80" s="7">
         <v>2034</v>
       </c>
-      <c r="H80" s="8">
-        <v>100</v>
-      </c>
-      <c r="K80" s="9"/>
+      <c r="H80" s="7">
+        <v>100</v>
+      </c>
+      <c r="K80" s="12"/>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
@@ -2763,16 +2834,16 @@
       <c r="E81" s="1">
         <v>6</v>
       </c>
-      <c r="F81" s="8">
-        <v>4</v>
-      </c>
-      <c r="G81" s="8">
+      <c r="F81" s="7">
+        <v>4</v>
+      </c>
+      <c r="G81" s="7">
         <v>2035</v>
       </c>
-      <c r="H81" s="8">
-        <v>50</v>
-      </c>
-      <c r="K81" s="9"/>
+      <c r="H81" s="7">
+        <v>50</v>
+      </c>
+      <c r="K81" s="12"/>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
@@ -2784,33 +2855,33 @@
       <c r="E82" s="1">
         <v>6</v>
       </c>
-      <c r="F82" s="8">
-        <v>4</v>
-      </c>
-      <c r="G82" s="8">
+      <c r="F82" s="7">
+        <v>4</v>
+      </c>
+      <c r="G82" s="7">
         <v>2036</v>
       </c>
-      <c r="H82" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="83" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="H82" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" s="11" customFormat="1" customHeight="1" spans="3:12">
       <c r="C83" s="1">
         <v>78</v>
       </c>
-      <c r="D83" s="10">
-        <v>1</v>
-      </c>
-      <c r="E83" s="10">
+      <c r="D83" s="8">
+        <v>1</v>
+      </c>
+      <c r="E83" s="8">
         <v>7</v>
       </c>
-      <c r="F83" s="11">
-        <v>1</v>
-      </c>
-      <c r="G83" s="11">
+      <c r="F83" s="9">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9">
         <v>2031</v>
       </c>
-      <c r="H83" s="8">
+      <c r="H83" s="7">
         <v>100</v>
       </c>
     </row>
@@ -2824,16 +2895,16 @@
       <c r="E84" s="1">
         <v>7</v>
       </c>
-      <c r="F84" s="8">
-        <v>1</v>
-      </c>
-      <c r="G84" s="8">
+      <c r="F84" s="7">
+        <v>1</v>
+      </c>
+      <c r="G84" s="7">
         <v>2032</v>
       </c>
-      <c r="H84" s="8">
-        <v>50</v>
-      </c>
-      <c r="K84" s="9"/>
+      <c r="H84" s="7">
+        <v>50</v>
+      </c>
+      <c r="K84" s="12"/>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
@@ -2845,16 +2916,16 @@
       <c r="E85" s="1">
         <v>7</v>
       </c>
-      <c r="F85" s="8">
-        <v>1</v>
-      </c>
-      <c r="G85" s="8">
+      <c r="F85" s="7">
+        <v>1</v>
+      </c>
+      <c r="G85" s="7">
         <v>2033</v>
       </c>
-      <c r="H85" s="8">
-        <v>50</v>
-      </c>
-      <c r="K85" s="9"/>
+      <c r="H85" s="7">
+        <v>50</v>
+      </c>
+      <c r="K85" s="12"/>
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
@@ -2866,16 +2937,16 @@
       <c r="E86" s="1">
         <v>7</v>
       </c>
-      <c r="F86" s="8">
-        <v>1</v>
-      </c>
-      <c r="G86" s="8">
+      <c r="F86" s="7">
+        <v>1</v>
+      </c>
+      <c r="G86" s="7">
         <v>2034</v>
       </c>
-      <c r="H86" s="8">
-        <v>50</v>
-      </c>
-      <c r="K86" s="9"/>
+      <c r="H86" s="7">
+        <v>50</v>
+      </c>
+      <c r="K86" s="12"/>
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
@@ -2887,16 +2958,16 @@
       <c r="E87" s="1">
         <v>7</v>
       </c>
-      <c r="F87" s="8">
-        <v>2</v>
-      </c>
-      <c r="G87" s="8">
+      <c r="F87" s="7">
+        <v>2</v>
+      </c>
+      <c r="G87" s="7">
         <v>2032</v>
       </c>
-      <c r="H87" s="8">
-        <v>100</v>
-      </c>
-      <c r="K87" s="9"/>
+      <c r="H87" s="7">
+        <v>100</v>
+      </c>
+      <c r="K87" s="12"/>
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
@@ -2908,16 +2979,16 @@
       <c r="E88" s="1">
         <v>7</v>
       </c>
-      <c r="F88" s="8">
-        <v>2</v>
-      </c>
-      <c r="G88" s="8">
+      <c r="F88" s="7">
+        <v>2</v>
+      </c>
+      <c r="G88" s="7">
         <v>2033</v>
       </c>
-      <c r="H88" s="8">
-        <v>50</v>
-      </c>
-      <c r="K88" s="9"/>
+      <c r="H88" s="7">
+        <v>50</v>
+      </c>
+      <c r="K88" s="12"/>
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
@@ -2929,16 +3000,16 @@
       <c r="E89" s="1">
         <v>7</v>
       </c>
-      <c r="F89" s="8">
-        <v>2</v>
-      </c>
-      <c r="G89" s="8">
+      <c r="F89" s="7">
+        <v>2</v>
+      </c>
+      <c r="G89" s="7">
         <v>2034</v>
       </c>
-      <c r="H89" s="8">
-        <v>50</v>
-      </c>
-      <c r="K89" s="9"/>
+      <c r="H89" s="7">
+        <v>50</v>
+      </c>
+      <c r="K89" s="12"/>
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
@@ -2950,16 +3021,16 @@
       <c r="E90" s="1">
         <v>7</v>
       </c>
-      <c r="F90" s="8">
-        <v>2</v>
-      </c>
-      <c r="G90" s="8">
+      <c r="F90" s="7">
+        <v>2</v>
+      </c>
+      <c r="G90" s="7">
         <v>2035</v>
       </c>
-      <c r="H90" s="8">
+      <c r="H90" s="7">
         <v>20</v>
       </c>
-      <c r="K90" s="9"/>
+      <c r="K90" s="12"/>
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
@@ -2971,16 +3042,16 @@
       <c r="E91" s="1">
         <v>7</v>
       </c>
-      <c r="F91" s="8">
-        <v>3</v>
-      </c>
-      <c r="G91" s="8">
+      <c r="F91" s="7">
+        <v>3</v>
+      </c>
+      <c r="G91" s="7">
         <v>2033</v>
       </c>
-      <c r="H91" s="8">
-        <v>100</v>
-      </c>
-      <c r="K91" s="9"/>
+      <c r="H91" s="7">
+        <v>100</v>
+      </c>
+      <c r="K91" s="12"/>
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
@@ -2992,16 +3063,16 @@
       <c r="E92" s="1">
         <v>7</v>
       </c>
-      <c r="F92" s="8">
-        <v>3</v>
-      </c>
-      <c r="G92" s="8">
+      <c r="F92" s="7">
+        <v>3</v>
+      </c>
+      <c r="G92" s="7">
         <v>2034</v>
       </c>
-      <c r="H92" s="8">
-        <v>50</v>
-      </c>
-      <c r="K92" s="9"/>
+      <c r="H92" s="7">
+        <v>50</v>
+      </c>
+      <c r="K92" s="12"/>
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
@@ -3013,17 +3084,17 @@
       <c r="E93" s="1">
         <v>7</v>
       </c>
-      <c r="F93" s="8">
-        <v>3</v>
-      </c>
-      <c r="G93" s="8">
+      <c r="F93" s="7">
+        <v>3</v>
+      </c>
+      <c r="G93" s="7">
         <v>2035</v>
       </c>
-      <c r="H93" s="8">
-        <v>50</v>
-      </c>
-      <c r="K93" s="9"/>
-      <c r="L93" s="9"/>
+      <c r="H93" s="7">
+        <v>50</v>
+      </c>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
@@ -3035,17 +3106,17 @@
       <c r="E94" s="1">
         <v>7</v>
       </c>
-      <c r="F94" s="8">
-        <v>3</v>
-      </c>
-      <c r="G94" s="8">
+      <c r="F94" s="7">
+        <v>3</v>
+      </c>
+      <c r="G94" s="7">
         <v>2036</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="7">
         <v>20</v>
       </c>
-      <c r="K94" s="9"/>
-      <c r="L94" s="9"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
@@ -3057,17 +3128,17 @@
       <c r="E95" s="1">
         <v>7</v>
       </c>
-      <c r="F95" s="8">
-        <v>4</v>
-      </c>
-      <c r="G95" s="8">
+      <c r="F95" s="7">
+        <v>4</v>
+      </c>
+      <c r="G95" s="7">
         <v>2034</v>
       </c>
-      <c r="H95" s="8">
-        <v>100</v>
-      </c>
-      <c r="K95" s="9"/>
-      <c r="L95" s="9"/>
+      <c r="H95" s="7">
+        <v>100</v>
+      </c>
+      <c r="K95" s="12"/>
+      <c r="L95" s="12"/>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
@@ -3079,16 +3150,16 @@
       <c r="E96" s="1">
         <v>7</v>
       </c>
-      <c r="F96" s="8">
-        <v>4</v>
-      </c>
-      <c r="G96" s="8">
+      <c r="F96" s="7">
+        <v>4</v>
+      </c>
+      <c r="G96" s="7">
         <v>2035</v>
       </c>
-      <c r="H96" s="8">
-        <v>50</v>
-      </c>
-      <c r="K96" s="9"/>
+      <c r="H96" s="7">
+        <v>50</v>
+      </c>
+      <c r="K96" s="12"/>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
@@ -3100,16 +3171,16 @@
       <c r="E97" s="1">
         <v>7</v>
       </c>
-      <c r="F97" s="8">
-        <v>4</v>
-      </c>
-      <c r="G97" s="8">
+      <c r="F97" s="7">
+        <v>4</v>
+      </c>
+      <c r="G97" s="7">
         <v>2036</v>
       </c>
-      <c r="H97" s="8">
-        <v>50</v>
-      </c>
-      <c r="K97" s="9"/>
+      <c r="H97" s="7">
+        <v>50</v>
+      </c>
+      <c r="K97" s="12"/>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
@@ -3121,33 +3192,33 @@
       <c r="E98" s="1">
         <v>7</v>
       </c>
-      <c r="F98" s="8">
-        <v>4</v>
-      </c>
-      <c r="G98" s="8">
+      <c r="F98" s="7">
+        <v>4</v>
+      </c>
+      <c r="G98" s="7">
         <v>2037</v>
       </c>
-      <c r="H98" s="8">
+      <c r="H98" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="99" s="2" customFormat="1" customHeight="1" spans="3:12">
+    <row r="99" s="11" customFormat="1" customHeight="1" spans="3:12">
       <c r="C99" s="1">
         <v>94</v>
       </c>
-      <c r="D99" s="10">
-        <v>1</v>
-      </c>
-      <c r="E99" s="10">
+      <c r="D99" s="8">
+        <v>1</v>
+      </c>
+      <c r="E99" s="8">
         <v>8</v>
       </c>
-      <c r="F99" s="11">
-        <v>1</v>
-      </c>
-      <c r="G99" s="11">
+      <c r="F99" s="9">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9">
         <v>2032</v>
       </c>
-      <c r="H99" s="8">
+      <c r="H99" s="7">
         <v>100</v>
       </c>
     </row>
@@ -3161,16 +3232,16 @@
       <c r="E100" s="1">
         <v>8</v>
       </c>
-      <c r="F100" s="8">
-        <v>1</v>
-      </c>
-      <c r="G100" s="8">
+      <c r="F100" s="7">
+        <v>1</v>
+      </c>
+      <c r="G100" s="7">
         <v>2033</v>
       </c>
-      <c r="H100" s="8">
-        <v>50</v>
-      </c>
-      <c r="K100" s="9"/>
+      <c r="H100" s="7">
+        <v>50</v>
+      </c>
+      <c r="K100" s="12"/>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
@@ -3182,16 +3253,16 @@
       <c r="E101" s="1">
         <v>8</v>
       </c>
-      <c r="F101" s="8">
-        <v>1</v>
-      </c>
-      <c r="G101" s="8">
+      <c r="F101" s="7">
+        <v>1</v>
+      </c>
+      <c r="G101" s="7">
         <v>2034</v>
       </c>
-      <c r="H101" s="8">
+      <c r="H101" s="7">
         <v>20</v>
       </c>
-      <c r="K101" s="9"/>
+      <c r="K101" s="12"/>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
@@ -3203,16 +3274,16 @@
       <c r="E102" s="1">
         <v>8</v>
       </c>
-      <c r="F102" s="8">
-        <v>1</v>
-      </c>
-      <c r="G102" s="8">
+      <c r="F102" s="7">
+        <v>1</v>
+      </c>
+      <c r="G102" s="7">
         <v>2035</v>
       </c>
-      <c r="H102" s="8">
+      <c r="H102" s="7">
         <v>20</v>
       </c>
-      <c r="K102" s="9"/>
+      <c r="K102" s="12"/>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
@@ -3224,16 +3295,16 @@
       <c r="E103" s="1">
         <v>8</v>
       </c>
-      <c r="F103" s="8">
-        <v>2</v>
-      </c>
-      <c r="G103" s="8">
+      <c r="F103" s="7">
+        <v>2</v>
+      </c>
+      <c r="G103" s="7">
         <v>2033</v>
       </c>
-      <c r="H103" s="8">
-        <v>100</v>
-      </c>
-      <c r="K103" s="9"/>
+      <c r="H103" s="7">
+        <v>100</v>
+      </c>
+      <c r="K103" s="12"/>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
@@ -3245,16 +3316,16 @@
       <c r="E104" s="1">
         <v>8</v>
       </c>
-      <c r="F104" s="8">
-        <v>2</v>
-      </c>
-      <c r="G104" s="8">
+      <c r="F104" s="7">
+        <v>2</v>
+      </c>
+      <c r="G104" s="7">
         <v>2034</v>
       </c>
-      <c r="H104" s="8">
-        <v>50</v>
-      </c>
-      <c r="K104" s="9"/>
+      <c r="H104" s="7">
+        <v>50</v>
+      </c>
+      <c r="K104" s="12"/>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
@@ -3266,16 +3337,16 @@
       <c r="E105" s="1">
         <v>8</v>
       </c>
-      <c r="F105" s="8">
-        <v>2</v>
-      </c>
-      <c r="G105" s="8">
+      <c r="F105" s="7">
+        <v>2</v>
+      </c>
+      <c r="G105" s="7">
         <v>2035</v>
       </c>
-      <c r="H105" s="8">
+      <c r="H105" s="7">
         <v>20</v>
       </c>
-      <c r="K105" s="9"/>
+      <c r="K105" s="12"/>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
@@ -3287,16 +3358,16 @@
       <c r="E106" s="1">
         <v>8</v>
       </c>
-      <c r="F106" s="8">
-        <v>2</v>
-      </c>
-      <c r="G106" s="8">
+      <c r="F106" s="7">
+        <v>2</v>
+      </c>
+      <c r="G106" s="7">
         <v>2036</v>
       </c>
-      <c r="H106" s="8">
+      <c r="H106" s="7">
         <v>20</v>
       </c>
-      <c r="K106" s="9"/>
+      <c r="K106" s="12"/>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
@@ -3308,16 +3379,16 @@
       <c r="E107" s="1">
         <v>8</v>
       </c>
-      <c r="F107" s="8">
-        <v>3</v>
-      </c>
-      <c r="G107" s="8">
+      <c r="F107" s="7">
+        <v>3</v>
+      </c>
+      <c r="G107" s="7">
         <v>2034</v>
       </c>
-      <c r="H107" s="8">
-        <v>100</v>
-      </c>
-      <c r="K107" s="9"/>
+      <c r="H107" s="7">
+        <v>100</v>
+      </c>
+      <c r="K107" s="12"/>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
@@ -3329,16 +3400,16 @@
       <c r="E108" s="1">
         <v>8</v>
       </c>
-      <c r="F108" s="8">
-        <v>3</v>
-      </c>
-      <c r="G108" s="8">
+      <c r="F108" s="7">
+        <v>3</v>
+      </c>
+      <c r="G108" s="7">
         <v>2035</v>
       </c>
-      <c r="H108" s="8">
-        <v>50</v>
-      </c>
-      <c r="K108" s="9"/>
+      <c r="H108" s="7">
+        <v>50</v>
+      </c>
+      <c r="K108" s="12"/>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
@@ -3350,17 +3421,17 @@
       <c r="E109" s="1">
         <v>8</v>
       </c>
-      <c r="F109" s="8">
-        <v>3</v>
-      </c>
-      <c r="G109" s="8">
+      <c r="F109" s="7">
+        <v>3</v>
+      </c>
+      <c r="G109" s="7">
         <v>2036</v>
       </c>
-      <c r="H109" s="8">
+      <c r="H109" s="7">
         <v>20</v>
       </c>
-      <c r="K109" s="9"/>
-      <c r="L109" s="9"/>
+      <c r="K109" s="12"/>
+      <c r="L109" s="12"/>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
@@ -3372,17 +3443,17 @@
       <c r="E110" s="1">
         <v>8</v>
       </c>
-      <c r="F110" s="8">
-        <v>3</v>
-      </c>
-      <c r="G110" s="8">
+      <c r="F110" s="7">
+        <v>3</v>
+      </c>
+      <c r="G110" s="7">
         <v>2037</v>
       </c>
-      <c r="H110" s="8">
+      <c r="H110" s="7">
         <v>20</v>
       </c>
-      <c r="K110" s="9"/>
-      <c r="L110" s="9"/>
+      <c r="K110" s="12"/>
+      <c r="L110" s="12"/>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
@@ -3394,17 +3465,17 @@
       <c r="E111" s="1">
         <v>8</v>
       </c>
-      <c r="F111" s="8">
-        <v>4</v>
-      </c>
-      <c r="G111" s="8">
+      <c r="F111" s="7">
+        <v>4</v>
+      </c>
+      <c r="G111" s="7">
         <v>2035</v>
       </c>
-      <c r="H111" s="8">
-        <v>100</v>
-      </c>
-      <c r="K111" s="9"/>
-      <c r="L111" s="9"/>
+      <c r="H111" s="7">
+        <v>100</v>
+      </c>
+      <c r="K111" s="12"/>
+      <c r="L111" s="12"/>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
@@ -3416,16 +3487,16 @@
       <c r="E112" s="1">
         <v>8</v>
       </c>
-      <c r="F112" s="8">
-        <v>4</v>
-      </c>
-      <c r="G112" s="8">
+      <c r="F112" s="7">
+        <v>4</v>
+      </c>
+      <c r="G112" s="7">
         <v>2036</v>
       </c>
-      <c r="H112" s="8">
-        <v>50</v>
-      </c>
-      <c r="K112" s="9"/>
+      <c r="H112" s="7">
+        <v>50</v>
+      </c>
+      <c r="K112" s="12"/>
     </row>
     <row r="113" customHeight="1" spans="3:11">
       <c r="C113" s="1">
@@ -3437,16 +3508,16 @@
       <c r="E113" s="1">
         <v>8</v>
       </c>
-      <c r="F113" s="8">
-        <v>4</v>
-      </c>
-      <c r="G113" s="8">
+      <c r="F113" s="7">
+        <v>4</v>
+      </c>
+      <c r="G113" s="7">
         <v>2037</v>
       </c>
-      <c r="H113" s="8">
+      <c r="H113" s="7">
         <v>20</v>
       </c>
-      <c r="K113" s="9"/>
+      <c r="K113" s="12"/>
     </row>
     <row r="114" customHeight="1" spans="3:11">
       <c r="C114" s="1">
@@ -3458,2193 +3529,4615 @@
       <c r="E114" s="1">
         <v>8</v>
       </c>
-      <c r="F114" s="8">
-        <v>4</v>
-      </c>
-      <c r="G114" s="8">
+      <c r="F114" s="7">
+        <v>4</v>
+      </c>
+      <c r="G114" s="7">
         <v>2038</v>
       </c>
-      <c r="H114" s="8">
+      <c r="H114" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="3:11">
-      <c r="C116" s="1">
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L114"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C6" s="1">
         <v>201</v>
       </c>
-      <c r="D116" s="1">
-        <v>2</v>
-      </c>
-      <c r="E116" s="1">
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
         <v>9</v>
       </c>
-      <c r="F116" s="8">
-        <v>1</v>
-      </c>
-      <c r="G116" s="8">
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
         <v>2039</v>
       </c>
-      <c r="H116" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="3:11">
-      <c r="C117" s="1">
+      <c r="H6" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C7" s="1">
         <v>202</v>
       </c>
-      <c r="D117" s="1">
-        <v>2</v>
-      </c>
-      <c r="E117" s="1">
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
         <v>9</v>
       </c>
-      <c r="F117" s="8">
-        <v>2</v>
-      </c>
-      <c r="G117" s="8">
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7">
         <v>2039</v>
       </c>
-      <c r="H117" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="3:11">
-      <c r="C118" s="1">
+      <c r="H7" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C8" s="1">
         <v>203</v>
       </c>
-      <c r="D118" s="1">
-        <v>2</v>
-      </c>
-      <c r="E118" s="1">
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
         <v>9</v>
       </c>
-      <c r="F118" s="8">
-        <v>2</v>
-      </c>
-      <c r="G118" s="8">
+      <c r="F8" s="7">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7">
         <v>2040</v>
       </c>
-      <c r="H118" s="8">
+      <c r="H8" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="3:11">
-      <c r="C119" s="1">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C9" s="1">
         <v>204</v>
       </c>
-      <c r="D119" s="1">
-        <v>2</v>
-      </c>
-      <c r="E119" s="1">
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
         <v>9</v>
       </c>
-      <c r="F119" s="8">
-        <v>3</v>
-      </c>
-      <c r="G119" s="8">
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7">
         <v>2039</v>
       </c>
-      <c r="H119" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="3:11">
-      <c r="C120" s="1">
+      <c r="H9" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C10" s="1">
         <v>205</v>
       </c>
-      <c r="D120" s="1">
-        <v>2</v>
-      </c>
-      <c r="E120" s="1">
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
         <v>9</v>
       </c>
-      <c r="F120" s="8">
-        <v>3</v>
-      </c>
-      <c r="G120" s="8">
+      <c r="F10" s="7">
+        <v>3</v>
+      </c>
+      <c r="G10" s="7">
         <v>2040</v>
       </c>
-      <c r="H120" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="3:11">
-      <c r="C121" s="1">
+      <c r="H10" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C11" s="1">
         <v>206</v>
       </c>
-      <c r="D121" s="1">
-        <v>2</v>
-      </c>
-      <c r="E121" s="1">
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
         <v>9</v>
       </c>
-      <c r="F121" s="8">
-        <v>3</v>
-      </c>
-      <c r="G121" s="8">
+      <c r="F11" s="7">
+        <v>3</v>
+      </c>
+      <c r="G11" s="7">
         <v>2041</v>
       </c>
-      <c r="H121" s="8">
+      <c r="H11" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="3:11">
-      <c r="C122" s="1">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C12" s="1">
         <v>207</v>
       </c>
-      <c r="D122" s="1">
-        <v>2</v>
-      </c>
-      <c r="E122" s="1">
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
         <v>9</v>
       </c>
-      <c r="F122" s="8">
-        <v>4</v>
-      </c>
-      <c r="G122" s="8">
+      <c r="F12" s="7">
+        <v>4</v>
+      </c>
+      <c r="G12" s="7">
         <v>2039</v>
       </c>
-      <c r="H122" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" spans="3:11">
-      <c r="C123" s="1">
+      <c r="H12" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C13" s="1">
         <v>208</v>
       </c>
-      <c r="D123" s="1">
-        <v>2</v>
-      </c>
-      <c r="E123" s="1">
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
         <v>9</v>
       </c>
-      <c r="F123" s="8">
-        <v>4</v>
-      </c>
-      <c r="G123" s="8">
+      <c r="F13" s="7">
+        <v>4</v>
+      </c>
+      <c r="G13" s="7">
         <v>2040</v>
       </c>
-      <c r="H123" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="3:11">
-      <c r="C124" s="1">
+      <c r="H13" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C14" s="1">
         <v>209</v>
       </c>
-      <c r="D124" s="1">
-        <v>2</v>
-      </c>
-      <c r="E124" s="1">
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
         <v>9</v>
       </c>
-      <c r="F124" s="8">
-        <v>4</v>
-      </c>
-      <c r="G124" s="8">
+      <c r="F14" s="7">
+        <v>4</v>
+      </c>
+      <c r="G14" s="7">
         <v>2041</v>
       </c>
-      <c r="H124" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" spans="3:11">
-      <c r="C125" s="1">
+      <c r="H14" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C15" s="1">
         <v>210</v>
       </c>
-      <c r="D125" s="1">
-        <v>2</v>
-      </c>
-      <c r="E125" s="1">
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
         <v>9</v>
       </c>
-      <c r="F125" s="8">
-        <v>4</v>
-      </c>
-      <c r="G125" s="8">
+      <c r="F15" s="7">
+        <v>4</v>
+      </c>
+      <c r="G15" s="7">
         <v>2042</v>
       </c>
-      <c r="H125" s="8">
+      <c r="H15" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="3:11">
-      <c r="C126" s="1">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C16" s="1">
         <v>211</v>
       </c>
-      <c r="D126" s="1">
-        <v>2</v>
-      </c>
-      <c r="E126" s="10">
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8">
         <v>10</v>
       </c>
-      <c r="F126" s="11">
-        <v>1</v>
-      </c>
-      <c r="G126" s="11">
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
         <v>2039</v>
       </c>
-      <c r="H126" s="11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" spans="3:11">
-      <c r="C127" s="1">
+      <c r="H16" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
         <v>212</v>
       </c>
-      <c r="D127" s="1">
-        <v>2</v>
-      </c>
-      <c r="E127" s="1">
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
         <v>10</v>
       </c>
-      <c r="F127" s="8">
-        <v>1</v>
-      </c>
-      <c r="G127" s="8">
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
         <v>2040</v>
       </c>
-      <c r="H127" s="8">
+      <c r="H17" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="3:11">
-      <c r="C128" s="1">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C18" s="1">
         <v>213</v>
       </c>
-      <c r="D128" s="1">
-        <v>2</v>
-      </c>
-      <c r="E128" s="1">
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
         <v>10</v>
       </c>
-      <c r="F128" s="8">
-        <v>2</v>
-      </c>
-      <c r="G128" s="8">
+      <c r="F18" s="7">
+        <v>2</v>
+      </c>
+      <c r="G18" s="7">
         <v>2039</v>
       </c>
-      <c r="H128" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" spans="3:8">
-      <c r="C129" s="1">
+      <c r="H18" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C19" s="1">
         <v>214</v>
       </c>
-      <c r="D129" s="1">
-        <v>2</v>
-      </c>
-      <c r="E129" s="1">
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
         <v>10</v>
       </c>
-      <c r="F129" s="8">
-        <v>2</v>
-      </c>
-      <c r="G129" s="8">
+      <c r="F19" s="7">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7">
         <v>2040</v>
       </c>
-      <c r="H129" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="3:8">
-      <c r="C130" s="1">
+      <c r="H19" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="1">
         <v>215</v>
       </c>
-      <c r="D130" s="1">
-        <v>2</v>
-      </c>
-      <c r="E130" s="1">
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
         <v>10</v>
       </c>
-      <c r="F130" s="8">
-        <v>3</v>
-      </c>
-      <c r="G130" s="8">
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
         <v>2039</v>
       </c>
-      <c r="H130" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="3:8">
-      <c r="C131" s="1">
+      <c r="H20" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C21" s="1">
         <v>216</v>
       </c>
-      <c r="D131" s="1">
-        <v>2</v>
-      </c>
-      <c r="E131" s="1">
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
         <v>10</v>
       </c>
-      <c r="F131" s="8">
-        <v>3</v>
-      </c>
-      <c r="G131" s="8">
+      <c r="F21" s="7">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
         <v>2040</v>
       </c>
-      <c r="H131" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" spans="3:8">
-      <c r="C132" s="1">
+      <c r="H21" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C22" s="1">
         <v>217</v>
       </c>
-      <c r="D132" s="1">
-        <v>2</v>
-      </c>
-      <c r="E132" s="1">
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
         <v>10</v>
       </c>
-      <c r="F132" s="8">
-        <v>3</v>
-      </c>
-      <c r="G132" s="8">
+      <c r="F22" s="7">
+        <v>3</v>
+      </c>
+      <c r="G22" s="7">
         <v>2041</v>
       </c>
-      <c r="H132" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" spans="3:8">
-      <c r="C133" s="1">
+      <c r="H22" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C23" s="1">
         <v>218</v>
       </c>
-      <c r="D133" s="1">
-        <v>2</v>
-      </c>
-      <c r="E133" s="1">
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
         <v>10</v>
       </c>
-      <c r="F133" s="8">
-        <v>4</v>
-      </c>
-      <c r="G133" s="8">
+      <c r="F23" s="7">
+        <v>4</v>
+      </c>
+      <c r="G23" s="7">
         <v>2039</v>
       </c>
-      <c r="H133" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" spans="3:8">
-      <c r="C134" s="1">
+      <c r="H23" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C24" s="1">
         <v>219</v>
       </c>
-      <c r="D134" s="1">
-        <v>2</v>
-      </c>
-      <c r="E134" s="1">
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
         <v>10</v>
       </c>
-      <c r="F134" s="8">
-        <v>4</v>
-      </c>
-      <c r="G134" s="8">
+      <c r="F24" s="7">
+        <v>4</v>
+      </c>
+      <c r="G24" s="7">
         <v>2040</v>
       </c>
-      <c r="H134" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" spans="3:8">
-      <c r="C135" s="1">
+      <c r="H24" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C25" s="1">
         <v>220</v>
       </c>
-      <c r="D135" s="1">
-        <v>2</v>
-      </c>
-      <c r="E135" s="1">
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
         <v>10</v>
       </c>
-      <c r="F135" s="8">
-        <v>4</v>
-      </c>
-      <c r="G135" s="8">
+      <c r="F25" s="7">
+        <v>4</v>
+      </c>
+      <c r="G25" s="7">
         <v>2041</v>
       </c>
-      <c r="H135" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" spans="3:8">
-      <c r="C136" s="1">
+      <c r="H25" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C26" s="1">
         <v>221</v>
       </c>
-      <c r="D136" s="1">
-        <v>2</v>
-      </c>
-      <c r="E136" s="1">
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
         <v>10</v>
       </c>
-      <c r="F136" s="8">
-        <v>4</v>
-      </c>
-      <c r="G136" s="8">
+      <c r="F26" s="7">
+        <v>4</v>
+      </c>
+      <c r="G26" s="7">
         <v>2042</v>
       </c>
-      <c r="H136" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" spans="3:8">
-      <c r="C137" s="1">
+      <c r="H26" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
         <v>222</v>
       </c>
-      <c r="D137" s="1">
-        <v>2</v>
-      </c>
-      <c r="E137" s="10">
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="8">
         <v>11</v>
       </c>
-      <c r="F137" s="11">
-        <v>1</v>
-      </c>
-      <c r="G137" s="11">
+      <c r="F27" s="9">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
         <v>2039</v>
       </c>
-      <c r="H137" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" spans="3:8">
-      <c r="C138" s="1">
+      <c r="H27" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
         <v>223</v>
       </c>
-      <c r="D138" s="1">
-        <v>2</v>
-      </c>
-      <c r="E138" s="1">
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
         <v>11</v>
       </c>
-      <c r="F138" s="8">
-        <v>1</v>
-      </c>
-      <c r="G138" s="8">
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7">
         <v>2040</v>
       </c>
-      <c r="H138" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" spans="3:8">
-      <c r="C139" s="1">
+      <c r="H28" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
         <v>224</v>
       </c>
-      <c r="D139" s="1">
-        <v>2</v>
-      </c>
-      <c r="E139" s="1">
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
         <v>11</v>
       </c>
-      <c r="F139" s="8">
-        <v>2</v>
-      </c>
-      <c r="G139" s="8">
+      <c r="F29" s="7">
+        <v>2</v>
+      </c>
+      <c r="G29" s="7">
         <v>2039</v>
       </c>
-      <c r="H139" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" spans="3:8">
-      <c r="C140" s="1">
+      <c r="H29" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="1">
         <v>225</v>
       </c>
-      <c r="D140" s="1">
-        <v>2</v>
-      </c>
-      <c r="E140" s="1">
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
         <v>11</v>
       </c>
-      <c r="F140" s="8">
-        <v>2</v>
-      </c>
-      <c r="G140" s="8">
+      <c r="F30" s="7">
+        <v>2</v>
+      </c>
+      <c r="G30" s="7">
         <v>2040</v>
       </c>
-      <c r="H140" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" spans="3:8">
-      <c r="C141" s="1">
+      <c r="H30" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="1">
         <v>226</v>
       </c>
-      <c r="D141" s="1">
-        <v>2</v>
-      </c>
-      <c r="E141" s="1">
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
         <v>11</v>
       </c>
-      <c r="F141" s="8">
-        <v>2</v>
-      </c>
-      <c r="G141" s="8">
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
         <v>2041</v>
       </c>
-      <c r="H141" s="8">
+      <c r="H31" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="3:8">
-      <c r="C142" s="1">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C32" s="1">
         <v>227</v>
       </c>
-      <c r="D142" s="1">
-        <v>2</v>
-      </c>
-      <c r="E142" s="1">
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
         <v>11</v>
       </c>
-      <c r="F142" s="8">
-        <v>3</v>
-      </c>
-      <c r="G142" s="8">
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="7">
         <v>2040</v>
       </c>
-      <c r="H142" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" spans="3:8">
-      <c r="C143" s="1">
+      <c r="H32" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="1">
         <v>228</v>
       </c>
-      <c r="D143" s="1">
-        <v>2</v>
-      </c>
-      <c r="E143" s="1">
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
         <v>11</v>
       </c>
-      <c r="F143" s="8">
-        <v>3</v>
-      </c>
-      <c r="G143" s="8">
+      <c r="F33" s="7">
+        <v>3</v>
+      </c>
+      <c r="G33" s="7">
         <v>2041</v>
       </c>
-      <c r="H143" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" spans="3:8">
-      <c r="C144" s="1">
+      <c r="H33" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="1">
         <v>229</v>
       </c>
-      <c r="D144" s="1">
-        <v>2</v>
-      </c>
-      <c r="E144" s="1">
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
         <v>11</v>
       </c>
-      <c r="F144" s="8">
-        <v>3</v>
-      </c>
-      <c r="G144" s="8">
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="7">
         <v>2042</v>
       </c>
-      <c r="H144" s="8">
+      <c r="H34" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="3:8">
-      <c r="C145" s="1">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C35" s="1">
         <v>230</v>
       </c>
-      <c r="D145" s="1">
-        <v>2</v>
-      </c>
-      <c r="E145" s="1">
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
         <v>11</v>
       </c>
-      <c r="F145" s="8">
-        <v>4</v>
-      </c>
-      <c r="G145" s="8">
+      <c r="F35" s="7">
+        <v>4</v>
+      </c>
+      <c r="G35" s="7">
         <v>2040</v>
       </c>
-      <c r="H145" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" spans="3:8">
-      <c r="C146" s="1">
+      <c r="H35" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="1">
         <v>231</v>
       </c>
-      <c r="D146" s="1">
-        <v>2</v>
-      </c>
-      <c r="E146" s="1">
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
         <v>11</v>
       </c>
-      <c r="F146" s="8">
-        <v>4</v>
-      </c>
-      <c r="G146" s="8">
+      <c r="F36" s="7">
+        <v>4</v>
+      </c>
+      <c r="G36" s="7">
         <v>2041</v>
       </c>
-      <c r="H146" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" spans="3:8">
-      <c r="C147" s="1">
+      <c r="H36" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="1">
         <v>232</v>
       </c>
-      <c r="D147" s="1">
-        <v>2</v>
-      </c>
-      <c r="E147" s="1">
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
         <v>11</v>
       </c>
-      <c r="F147" s="8">
-        <v>4</v>
-      </c>
-      <c r="G147" s="8">
+      <c r="F37" s="7">
+        <v>4</v>
+      </c>
+      <c r="G37" s="7">
         <v>2042</v>
       </c>
-      <c r="H147" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" spans="3:8">
-      <c r="C148" s="1">
+      <c r="H37" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C38" s="1">
         <v>233</v>
       </c>
-      <c r="D148" s="1">
-        <v>2</v>
-      </c>
-      <c r="E148" s="1">
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
         <v>11</v>
       </c>
-      <c r="F148" s="8">
-        <v>4</v>
-      </c>
-      <c r="G148" s="8">
+      <c r="F38" s="7">
+        <v>4</v>
+      </c>
+      <c r="G38" s="7">
         <v>2043</v>
       </c>
-      <c r="H148" s="8">
+      <c r="H38" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="3:8">
-      <c r="C149" s="1">
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C39" s="1">
         <v>234</v>
       </c>
-      <c r="D149" s="1">
-        <v>2</v>
-      </c>
-      <c r="E149" s="10">
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="8">
         <v>12</v>
       </c>
-      <c r="F149" s="11">
-        <v>1</v>
-      </c>
-      <c r="G149" s="11">
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
         <v>2039</v>
       </c>
-      <c r="H149" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" spans="3:8">
-      <c r="C150" s="1">
+      <c r="H39" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="1">
         <v>235</v>
       </c>
-      <c r="D150" s="1">
-        <v>2</v>
-      </c>
-      <c r="E150" s="1">
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1">
         <v>12</v>
       </c>
-      <c r="F150" s="8">
-        <v>1</v>
-      </c>
-      <c r="G150" s="8">
+      <c r="F40" s="7">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
         <v>2040</v>
       </c>
-      <c r="H150" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" spans="3:8">
-      <c r="C151" s="1">
+      <c r="H40" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="1">
         <v>236</v>
       </c>
-      <c r="D151" s="1">
-        <v>2</v>
-      </c>
-      <c r="E151" s="1">
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1">
         <v>12</v>
       </c>
-      <c r="F151" s="8">
-        <v>1</v>
-      </c>
-      <c r="G151" s="8">
+      <c r="F41" s="7">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
         <v>2041</v>
       </c>
-      <c r="H151" s="8">
+      <c r="H41" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="3:8">
-      <c r="C152" s="1">
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C42" s="1">
         <v>237</v>
       </c>
-      <c r="D152" s="1">
-        <v>2</v>
-      </c>
-      <c r="E152" s="1">
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
         <v>12</v>
       </c>
-      <c r="F152" s="8">
-        <v>2</v>
-      </c>
-      <c r="G152" s="8">
+      <c r="F42" s="7">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7">
         <v>2039</v>
       </c>
-      <c r="H152" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="153" customHeight="1" spans="3:8">
-      <c r="C153" s="1">
+      <c r="H42" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C43" s="1">
         <v>238</v>
       </c>
-      <c r="D153" s="1">
-        <v>2</v>
-      </c>
-      <c r="E153" s="1">
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
         <v>12</v>
       </c>
-      <c r="F153" s="8">
-        <v>2</v>
-      </c>
-      <c r="G153" s="8">
+      <c r="F43" s="7">
+        <v>2</v>
+      </c>
+      <c r="G43" s="7">
         <v>2040</v>
       </c>
-      <c r="H153" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" spans="3:8">
-      <c r="C154" s="1">
+      <c r="H43" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C44" s="1">
         <v>239</v>
       </c>
-      <c r="D154" s="1">
-        <v>2</v>
-      </c>
-      <c r="E154" s="1">
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
         <v>12</v>
       </c>
-      <c r="F154" s="8">
-        <v>2</v>
-      </c>
-      <c r="G154" s="8">
+      <c r="F44" s="7">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
         <v>2041</v>
       </c>
-      <c r="H154" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" spans="3:8">
-      <c r="C155" s="1">
+      <c r="H44" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C45" s="1">
         <v>240</v>
       </c>
-      <c r="D155" s="1">
-        <v>2</v>
-      </c>
-      <c r="E155" s="1">
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
         <v>12</v>
       </c>
-      <c r="F155" s="8">
-        <v>3</v>
-      </c>
-      <c r="G155" s="8">
+      <c r="F45" s="7">
+        <v>3</v>
+      </c>
+      <c r="G45" s="7">
         <v>2040</v>
       </c>
-      <c r="H155" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" spans="3:8">
-      <c r="C156" s="1">
+      <c r="H45" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C46" s="1">
         <v>241</v>
       </c>
-      <c r="D156" s="1">
-        <v>2</v>
-      </c>
-      <c r="E156" s="1">
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
         <v>12</v>
       </c>
-      <c r="F156" s="8">
-        <v>3</v>
-      </c>
-      <c r="G156" s="8">
+      <c r="F46" s="7">
+        <v>3</v>
+      </c>
+      <c r="G46" s="7">
         <v>2041</v>
       </c>
-      <c r="H156" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" spans="3:8">
-      <c r="C157" s="1">
+      <c r="H46" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C47" s="1">
         <v>242</v>
       </c>
-      <c r="D157" s="1">
-        <v>2</v>
-      </c>
-      <c r="E157" s="1">
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1">
         <v>12</v>
       </c>
-      <c r="F157" s="8">
-        <v>3</v>
-      </c>
-      <c r="G157" s="8">
+      <c r="F47" s="7">
+        <v>3</v>
+      </c>
+      <c r="G47" s="7">
         <v>2042</v>
       </c>
-      <c r="H157" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" spans="3:8">
-      <c r="C158" s="1">
+      <c r="H47" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C48" s="1">
         <v>243</v>
       </c>
-      <c r="D158" s="1">
-        <v>2</v>
-      </c>
-      <c r="E158" s="1">
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
         <v>12</v>
       </c>
-      <c r="F158" s="8">
-        <v>4</v>
-      </c>
-      <c r="G158" s="8">
+      <c r="F48" s="7">
+        <v>4</v>
+      </c>
+      <c r="G48" s="7">
         <v>2040</v>
       </c>
-      <c r="H158" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" spans="3:8">
-      <c r="C159" s="1">
+      <c r="H48" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C49" s="1">
         <v>244</v>
       </c>
-      <c r="D159" s="1">
-        <v>2</v>
-      </c>
-      <c r="E159" s="1">
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1">
         <v>12</v>
       </c>
-      <c r="F159" s="8">
-        <v>4</v>
-      </c>
-      <c r="G159" s="8">
+      <c r="F49" s="7">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7">
         <v>2041</v>
       </c>
-      <c r="H159" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" spans="3:8">
-      <c r="C160" s="1">
+      <c r="H49" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C50" s="1">
         <v>245</v>
       </c>
-      <c r="D160" s="1">
-        <v>2</v>
-      </c>
-      <c r="E160" s="1">
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
         <v>12</v>
       </c>
-      <c r="F160" s="8">
-        <v>4</v>
-      </c>
-      <c r="G160" s="8">
+      <c r="F50" s="7">
+        <v>4</v>
+      </c>
+      <c r="G50" s="7">
         <v>2042</v>
       </c>
-      <c r="H160" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" spans="3:8">
-      <c r="C161" s="1">
+      <c r="H50" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="1">
         <v>246</v>
       </c>
-      <c r="D161" s="1">
-        <v>2</v>
-      </c>
-      <c r="E161" s="1">
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" s="1">
         <v>12</v>
       </c>
-      <c r="F161" s="8">
-        <v>4</v>
-      </c>
-      <c r="G161" s="8">
+      <c r="F51" s="7">
+        <v>4</v>
+      </c>
+      <c r="G51" s="7">
         <v>2043</v>
       </c>
-      <c r="H161" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" spans="3:8">
-      <c r="C162" s="1">
+      <c r="H51" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="1">
         <v>247</v>
       </c>
-      <c r="D162" s="1">
-        <v>2</v>
-      </c>
-      <c r="E162" s="10">
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="8">
         <v>13</v>
       </c>
-      <c r="F162" s="11">
-        <v>1</v>
-      </c>
-      <c r="G162" s="11">
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9">
         <v>2039</v>
       </c>
-      <c r="H162" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" spans="3:8">
-      <c r="C163" s="1">
+      <c r="H52" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C53" s="1">
         <v>248</v>
       </c>
-      <c r="D163" s="1">
-        <v>2</v>
-      </c>
-      <c r="E163" s="1">
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1">
         <v>13</v>
       </c>
-      <c r="F163" s="8">
-        <v>1</v>
-      </c>
-      <c r="G163" s="8">
+      <c r="F53" s="7">
+        <v>1</v>
+      </c>
+      <c r="G53" s="7">
         <v>2040</v>
       </c>
-      <c r="H163" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" spans="3:8">
-      <c r="C164" s="1">
+      <c r="H53" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C54" s="1">
         <v>249</v>
       </c>
-      <c r="D164" s="1">
-        <v>2</v>
-      </c>
-      <c r="E164" s="1">
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="1">
         <v>13</v>
       </c>
-      <c r="F164" s="8">
-        <v>1</v>
-      </c>
-      <c r="G164" s="8">
+      <c r="F54" s="7">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7">
         <v>2041</v>
       </c>
-      <c r="H164" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" spans="3:8">
-      <c r="C165" s="1">
+      <c r="H54" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C55" s="1">
         <v>250</v>
       </c>
-      <c r="D165" s="1">
-        <v>2</v>
-      </c>
-      <c r="E165" s="1">
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1">
         <v>13</v>
       </c>
-      <c r="F165" s="8">
-        <v>2</v>
-      </c>
-      <c r="G165" s="8">
+      <c r="F55" s="7">
+        <v>2</v>
+      </c>
+      <c r="G55" s="7">
         <v>2039</v>
       </c>
-      <c r="H165" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" spans="3:8">
-      <c r="C166" s="1">
+      <c r="H55" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C56" s="1">
         <v>251</v>
       </c>
-      <c r="D166" s="1">
-        <v>2</v>
-      </c>
-      <c r="E166" s="1">
+      <c r="D56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1">
         <v>13</v>
       </c>
-      <c r="F166" s="8">
-        <v>2</v>
-      </c>
-      <c r="G166" s="8">
+      <c r="F56" s="7">
+        <v>2</v>
+      </c>
+      <c r="G56" s="7">
         <v>2040</v>
       </c>
-      <c r="H166" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="167" customHeight="1" spans="3:8">
-      <c r="C167" s="1">
+      <c r="H56" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="1">
         <v>252</v>
       </c>
-      <c r="D167" s="1">
-        <v>2</v>
-      </c>
-      <c r="E167" s="1">
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1">
         <v>13</v>
       </c>
-      <c r="F167" s="8">
-        <v>2</v>
-      </c>
-      <c r="G167" s="8">
+      <c r="F57" s="7">
+        <v>2</v>
+      </c>
+      <c r="G57" s="7">
         <v>2041</v>
       </c>
-      <c r="H167" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="168" customHeight="1" spans="3:8">
-      <c r="C168" s="1">
+      <c r="H57" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="1">
         <v>253</v>
       </c>
-      <c r="D168" s="1">
-        <v>2</v>
-      </c>
-      <c r="E168" s="1">
+      <c r="D58" s="1">
+        <v>2</v>
+      </c>
+      <c r="E58" s="1">
         <v>13</v>
       </c>
-      <c r="F168" s="8">
-        <v>2</v>
-      </c>
-      <c r="G168" s="8">
+      <c r="F58" s="7">
+        <v>2</v>
+      </c>
+      <c r="G58" s="7">
         <v>2042</v>
       </c>
-      <c r="H168" s="8">
+      <c r="H58" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="3:8">
-      <c r="C169" s="1">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C59" s="1">
         <v>254</v>
       </c>
-      <c r="D169" s="1">
-        <v>2</v>
-      </c>
-      <c r="E169" s="1">
+      <c r="D59" s="1">
+        <v>2</v>
+      </c>
+      <c r="E59" s="1">
         <v>13</v>
       </c>
-      <c r="F169" s="8">
-        <v>3</v>
-      </c>
-      <c r="G169" s="8">
+      <c r="F59" s="7">
+        <v>3</v>
+      </c>
+      <c r="G59" s="7">
         <v>2040</v>
       </c>
-      <c r="H169" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" spans="3:8">
-      <c r="C170" s="1">
+      <c r="H59" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C60" s="1">
         <v>255</v>
       </c>
-      <c r="D170" s="1">
-        <v>2</v>
-      </c>
-      <c r="E170" s="1">
+      <c r="D60" s="1">
+        <v>2</v>
+      </c>
+      <c r="E60" s="1">
         <v>13</v>
       </c>
-      <c r="F170" s="8">
-        <v>3</v>
-      </c>
-      <c r="G170" s="8">
+      <c r="F60" s="7">
+        <v>3</v>
+      </c>
+      <c r="G60" s="7">
         <v>2041</v>
       </c>
-      <c r="H170" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="171" customHeight="1" spans="3:8">
-      <c r="C171" s="1">
+      <c r="H60" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C61" s="1">
         <v>256</v>
       </c>
-      <c r="D171" s="1">
-        <v>2</v>
-      </c>
-      <c r="E171" s="1">
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" s="1">
         <v>13</v>
       </c>
-      <c r="F171" s="8">
-        <v>3</v>
-      </c>
-      <c r="G171" s="8">
+      <c r="F61" s="7">
+        <v>3</v>
+      </c>
+      <c r="G61" s="7">
         <v>2042</v>
       </c>
-      <c r="H171" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" spans="3:8">
-      <c r="C172" s="1">
+      <c r="H61" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C62" s="1">
         <v>257</v>
       </c>
-      <c r="D172" s="1">
-        <v>2</v>
-      </c>
-      <c r="E172" s="1">
+      <c r="D62" s="1">
+        <v>2</v>
+      </c>
+      <c r="E62" s="1">
         <v>13</v>
       </c>
-      <c r="F172" s="8">
-        <v>3</v>
-      </c>
-      <c r="G172" s="8">
+      <c r="F62" s="7">
+        <v>3</v>
+      </c>
+      <c r="G62" s="7">
         <v>2043</v>
       </c>
-      <c r="H172" s="8">
+      <c r="H62" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="3:8">
-      <c r="C173" s="1">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C63" s="1">
         <v>258</v>
       </c>
-      <c r="D173" s="1">
-        <v>2</v>
-      </c>
-      <c r="E173" s="1">
+      <c r="D63" s="1">
+        <v>2</v>
+      </c>
+      <c r="E63" s="1">
         <v>13</v>
       </c>
-      <c r="F173" s="8">
-        <v>4</v>
-      </c>
-      <c r="G173" s="8">
+      <c r="F63" s="7">
+        <v>4</v>
+      </c>
+      <c r="G63" s="7">
         <v>2041</v>
       </c>
-      <c r="H173" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="174" customHeight="1" spans="3:8">
-      <c r="C174" s="1">
+      <c r="H63" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="1">
         <v>259</v>
       </c>
-      <c r="D174" s="1">
-        <v>2</v>
-      </c>
-      <c r="E174" s="1">
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="E64" s="1">
         <v>13</v>
       </c>
-      <c r="F174" s="8">
-        <v>4</v>
-      </c>
-      <c r="G174" s="8">
+      <c r="F64" s="7">
+        <v>4</v>
+      </c>
+      <c r="G64" s="7">
         <v>2042</v>
       </c>
-      <c r="H174" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="175" customHeight="1" spans="3:8">
-      <c r="C175" s="1">
+      <c r="H64" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
         <v>260</v>
       </c>
-      <c r="D175" s="1">
-        <v>2</v>
-      </c>
-      <c r="E175" s="1">
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1">
         <v>13</v>
       </c>
-      <c r="F175" s="8">
-        <v>4</v>
-      </c>
-      <c r="G175" s="8">
+      <c r="F65" s="7">
+        <v>4</v>
+      </c>
+      <c r="G65" s="7">
         <v>2043</v>
       </c>
-      <c r="H175" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="176" customHeight="1" spans="3:8">
-      <c r="C176" s="1">
+      <c r="H65" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
         <v>261</v>
       </c>
-      <c r="D176" s="1">
-        <v>2</v>
-      </c>
-      <c r="E176" s="1">
+      <c r="D66" s="1">
+        <v>2</v>
+      </c>
+      <c r="E66" s="1">
         <v>13</v>
       </c>
-      <c r="F176" s="8">
-        <v>4</v>
-      </c>
-      <c r="G176" s="8">
+      <c r="F66" s="7">
+        <v>4</v>
+      </c>
+      <c r="G66" s="7">
         <v>2044</v>
       </c>
-      <c r="H176" s="8">
+      <c r="H66" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="177" customHeight="1" spans="3:8">
-      <c r="C177" s="1">
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
         <v>262</v>
       </c>
-      <c r="D177" s="1">
-        <v>2</v>
-      </c>
-      <c r="E177" s="10">
+      <c r="D67" s="1">
+        <v>2</v>
+      </c>
+      <c r="E67" s="8">
         <v>14</v>
       </c>
-      <c r="F177" s="11">
-        <v>1</v>
-      </c>
-      <c r="G177" s="11">
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9">
         <v>2039</v>
       </c>
-      <c r="H177" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="178" customHeight="1" spans="3:8">
-      <c r="C178" s="1">
+      <c r="H67" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
         <v>263</v>
       </c>
-      <c r="D178" s="1">
-        <v>2</v>
-      </c>
-      <c r="E178" s="1">
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="E68" s="1">
         <v>14</v>
       </c>
-      <c r="F178" s="8">
-        <v>1</v>
-      </c>
-      <c r="G178" s="8">
+      <c r="F68" s="7">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7">
         <v>2040</v>
       </c>
-      <c r="H178" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="179" customHeight="1" spans="3:8">
-      <c r="C179" s="1">
+      <c r="H68" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
         <v>264</v>
       </c>
-      <c r="D179" s="1">
-        <v>2</v>
-      </c>
-      <c r="E179" s="1">
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="E69" s="1">
         <v>14</v>
       </c>
-      <c r="F179" s="8">
-        <v>1</v>
-      </c>
-      <c r="G179" s="8">
+      <c r="F69" s="7">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
         <v>2041</v>
       </c>
-      <c r="H179" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="180" customHeight="1" spans="3:8">
-      <c r="C180" s="1">
+      <c r="H69" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
         <v>265</v>
       </c>
-      <c r="D180" s="1">
-        <v>2</v>
-      </c>
-      <c r="E180" s="1">
+      <c r="D70" s="1">
+        <v>2</v>
+      </c>
+      <c r="E70" s="1">
         <v>14</v>
       </c>
-      <c r="F180" s="8">
-        <v>1</v>
-      </c>
-      <c r="G180" s="8">
+      <c r="F70" s="7">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7">
         <v>2042</v>
       </c>
-      <c r="H180" s="8">
+      <c r="H70" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="3:8">
-      <c r="C181" s="1">
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
         <v>266</v>
       </c>
-      <c r="D181" s="1">
-        <v>2</v>
-      </c>
-      <c r="E181" s="1">
+      <c r="D71" s="1">
+        <v>2</v>
+      </c>
+      <c r="E71" s="1">
         <v>14</v>
       </c>
-      <c r="F181" s="8">
-        <v>2</v>
-      </c>
-      <c r="G181" s="8">
+      <c r="F71" s="7">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7">
         <v>2039</v>
       </c>
-      <c r="H181" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" spans="3:8">
-      <c r="C182" s="1">
+      <c r="H71" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
         <v>267</v>
       </c>
-      <c r="D182" s="1">
-        <v>2</v>
-      </c>
-      <c r="E182" s="1">
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="E72" s="1">
         <v>14</v>
       </c>
-      <c r="F182" s="8">
-        <v>2</v>
-      </c>
-      <c r="G182" s="8">
+      <c r="F72" s="7">
+        <v>2</v>
+      </c>
+      <c r="G72" s="7">
         <v>2040</v>
       </c>
-      <c r="H182" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" spans="3:8">
-      <c r="C183" s="1">
+      <c r="H72" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C73" s="1">
         <v>268</v>
       </c>
-      <c r="D183" s="1">
-        <v>2</v>
-      </c>
-      <c r="E183" s="1">
+      <c r="D73" s="1">
+        <v>2</v>
+      </c>
+      <c r="E73" s="1">
         <v>14</v>
       </c>
-      <c r="F183" s="8">
-        <v>2</v>
-      </c>
-      <c r="G183" s="8">
+      <c r="F73" s="7">
+        <v>2</v>
+      </c>
+      <c r="G73" s="7">
         <v>2041</v>
       </c>
-      <c r="H183" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" spans="3:8">
-      <c r="C184" s="1">
+      <c r="H73" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C74" s="1">
         <v>269</v>
       </c>
-      <c r="D184" s="1">
-        <v>2</v>
-      </c>
-      <c r="E184" s="1">
+      <c r="D74" s="1">
+        <v>2</v>
+      </c>
+      <c r="E74" s="1">
         <v>14</v>
       </c>
-      <c r="F184" s="8">
-        <v>2</v>
-      </c>
-      <c r="G184" s="8">
+      <c r="F74" s="7">
+        <v>2</v>
+      </c>
+      <c r="G74" s="7">
         <v>2042</v>
       </c>
-      <c r="H184" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" spans="3:8">
-      <c r="C185" s="1">
+      <c r="H74" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
         <v>270</v>
       </c>
-      <c r="D185" s="1">
-        <v>2</v>
-      </c>
-      <c r="E185" s="1">
+      <c r="D75" s="1">
+        <v>2</v>
+      </c>
+      <c r="E75" s="1">
         <v>14</v>
       </c>
-      <c r="F185" s="8">
-        <v>3</v>
-      </c>
-      <c r="G185" s="8">
+      <c r="F75" s="7">
+        <v>3</v>
+      </c>
+      <c r="G75" s="7">
         <v>2040</v>
       </c>
-      <c r="H185" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" spans="3:8">
-      <c r="C186" s="1">
+      <c r="H75" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
         <v>271</v>
       </c>
-      <c r="D186" s="1">
-        <v>2</v>
-      </c>
-      <c r="E186" s="1">
+      <c r="D76" s="1">
+        <v>2</v>
+      </c>
+      <c r="E76" s="1">
         <v>14</v>
       </c>
-      <c r="F186" s="8">
-        <v>3</v>
-      </c>
-      <c r="G186" s="8">
+      <c r="F76" s="7">
+        <v>3</v>
+      </c>
+      <c r="G76" s="7">
         <v>2041</v>
       </c>
-      <c r="H186" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" spans="3:8">
-      <c r="C187" s="1">
+      <c r="H76" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
         <v>272</v>
       </c>
-      <c r="D187" s="1">
-        <v>2</v>
-      </c>
-      <c r="E187" s="1">
+      <c r="D77" s="1">
+        <v>2</v>
+      </c>
+      <c r="E77" s="1">
         <v>14</v>
       </c>
-      <c r="F187" s="8">
-        <v>3</v>
-      </c>
-      <c r="G187" s="8">
+      <c r="F77" s="7">
+        <v>3</v>
+      </c>
+      <c r="G77" s="7">
         <v>2042</v>
       </c>
-      <c r="H187" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" spans="3:8">
-      <c r="C188" s="1">
+      <c r="H77" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C78" s="1">
         <v>273</v>
       </c>
-      <c r="D188" s="1">
-        <v>2</v>
-      </c>
-      <c r="E188" s="1">
+      <c r="D78" s="1">
+        <v>2</v>
+      </c>
+      <c r="E78" s="1">
         <v>14</v>
       </c>
-      <c r="F188" s="8">
-        <v>3</v>
-      </c>
-      <c r="G188" s="8">
+      <c r="F78" s="7">
+        <v>3</v>
+      </c>
+      <c r="G78" s="7">
         <v>2043</v>
       </c>
-      <c r="H188" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" spans="3:8">
-      <c r="C189" s="1">
+      <c r="H78" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C79" s="1">
         <v>274</v>
       </c>
-      <c r="D189" s="1">
-        <v>2</v>
-      </c>
-      <c r="E189" s="1">
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+      <c r="E79" s="1">
         <v>14</v>
       </c>
-      <c r="F189" s="8">
-        <v>4</v>
-      </c>
-      <c r="G189" s="8">
+      <c r="F79" s="7">
+        <v>4</v>
+      </c>
+      <c r="G79" s="7">
         <v>2041</v>
       </c>
-      <c r="H189" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" spans="3:8">
-      <c r="C190" s="1">
+      <c r="H79" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C80" s="1">
         <v>275</v>
       </c>
-      <c r="D190" s="1">
-        <v>2</v>
-      </c>
-      <c r="E190" s="1">
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" s="1">
         <v>14</v>
       </c>
-      <c r="F190" s="8">
-        <v>4</v>
-      </c>
-      <c r="G190" s="8">
+      <c r="F80" s="7">
+        <v>4</v>
+      </c>
+      <c r="G80" s="7">
         <v>2042</v>
       </c>
-      <c r="H190" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="191" customHeight="1" spans="3:8">
-      <c r="C191" s="1">
+      <c r="H80" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C81" s="1">
         <v>276</v>
       </c>
-      <c r="D191" s="1">
-        <v>2</v>
-      </c>
-      <c r="E191" s="1">
+      <c r="D81" s="1">
+        <v>2</v>
+      </c>
+      <c r="E81" s="1">
         <v>14</v>
       </c>
-      <c r="F191" s="8">
-        <v>4</v>
-      </c>
-      <c r="G191" s="8">
+      <c r="F81" s="7">
+        <v>4</v>
+      </c>
+      <c r="G81" s="7">
         <v>2043</v>
       </c>
-      <c r="H191" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="192" customHeight="1" spans="3:8">
-      <c r="C192" s="1">
+      <c r="H81" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C82" s="1">
         <v>277</v>
       </c>
-      <c r="D192" s="1">
-        <v>2</v>
-      </c>
-      <c r="E192" s="1">
+      <c r="D82" s="1">
+        <v>2</v>
+      </c>
+      <c r="E82" s="1">
         <v>14</v>
       </c>
-      <c r="F192" s="8">
-        <v>4</v>
-      </c>
-      <c r="G192" s="8">
+      <c r="F82" s="7">
+        <v>4</v>
+      </c>
+      <c r="G82" s="7">
         <v>2044</v>
       </c>
-      <c r="H192" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="193" customHeight="1" spans="3:8">
-      <c r="C193" s="1">
+      <c r="H82" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C83" s="1">
         <v>278</v>
       </c>
-      <c r="D193" s="1">
-        <v>2</v>
-      </c>
-      <c r="E193" s="10">
+      <c r="D83" s="1">
+        <v>2</v>
+      </c>
+      <c r="E83" s="8">
         <v>15</v>
       </c>
-      <c r="F193" s="11">
-        <v>1</v>
-      </c>
-      <c r="G193" s="11">
+      <c r="F83" s="9">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9">
         <v>2039</v>
       </c>
-      <c r="H193" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="194" customHeight="1" spans="3:8">
-      <c r="C194" s="1">
+      <c r="H83" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="1">
         <v>279</v>
       </c>
-      <c r="D194" s="1">
-        <v>2</v>
-      </c>
-      <c r="E194" s="1">
+      <c r="D84" s="1">
+        <v>2</v>
+      </c>
+      <c r="E84" s="1">
         <v>15</v>
       </c>
-      <c r="F194" s="8">
-        <v>1</v>
-      </c>
-      <c r="G194" s="8">
+      <c r="F84" s="7">
+        <v>1</v>
+      </c>
+      <c r="G84" s="7">
         <v>2040</v>
       </c>
-      <c r="H194" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="195" customHeight="1" spans="3:8">
-      <c r="C195" s="1">
+      <c r="H84" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C85" s="1">
         <v>280</v>
       </c>
-      <c r="D195" s="1">
-        <v>2</v>
-      </c>
-      <c r="E195" s="1">
+      <c r="D85" s="1">
+        <v>2</v>
+      </c>
+      <c r="E85" s="1">
         <v>15</v>
       </c>
-      <c r="F195" s="8">
-        <v>1</v>
-      </c>
-      <c r="G195" s="8">
+      <c r="F85" s="7">
+        <v>1</v>
+      </c>
+      <c r="G85" s="7">
         <v>2041</v>
       </c>
-      <c r="H195" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="196" customHeight="1" spans="3:8">
-      <c r="C196" s="1">
+      <c r="H85" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C86" s="1">
         <v>281</v>
       </c>
-      <c r="D196" s="1">
-        <v>2</v>
-      </c>
-      <c r="E196" s="1">
+      <c r="D86" s="1">
+        <v>2</v>
+      </c>
+      <c r="E86" s="1">
         <v>15</v>
       </c>
-      <c r="F196" s="8">
-        <v>1</v>
-      </c>
-      <c r="G196" s="8">
+      <c r="F86" s="7">
+        <v>1</v>
+      </c>
+      <c r="G86" s="7">
         <v>2042</v>
       </c>
-      <c r="H196" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="197" customHeight="1" spans="3:8">
-      <c r="C197" s="1">
+      <c r="H86" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C87" s="1">
         <v>282</v>
       </c>
-      <c r="D197" s="1">
-        <v>2</v>
-      </c>
-      <c r="E197" s="1">
+      <c r="D87" s="1">
+        <v>2</v>
+      </c>
+      <c r="E87" s="1">
         <v>15</v>
       </c>
-      <c r="F197" s="8">
-        <v>2</v>
-      </c>
-      <c r="G197" s="8">
+      <c r="F87" s="7">
+        <v>2</v>
+      </c>
+      <c r="G87" s="7">
         <v>2040</v>
       </c>
-      <c r="H197" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="198" customHeight="1" spans="3:8">
-      <c r="C198" s="1">
+      <c r="H87" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C88" s="1">
         <v>283</v>
       </c>
-      <c r="D198" s="1">
-        <v>2</v>
-      </c>
-      <c r="E198" s="1">
+      <c r="D88" s="1">
+        <v>2</v>
+      </c>
+      <c r="E88" s="1">
         <v>15</v>
       </c>
-      <c r="F198" s="8">
-        <v>2</v>
-      </c>
-      <c r="G198" s="8">
+      <c r="F88" s="7">
+        <v>2</v>
+      </c>
+      <c r="G88" s="7">
         <v>2041</v>
       </c>
-      <c r="H198" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="199" customHeight="1" spans="3:8">
-      <c r="C199" s="1">
+      <c r="H88" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C89" s="1">
         <v>284</v>
       </c>
-      <c r="D199" s="1">
-        <v>2</v>
-      </c>
-      <c r="E199" s="1">
+      <c r="D89" s="1">
+        <v>2</v>
+      </c>
+      <c r="E89" s="1">
         <v>15</v>
       </c>
-      <c r="F199" s="8">
-        <v>2</v>
-      </c>
-      <c r="G199" s="8">
+      <c r="F89" s="7">
+        <v>2</v>
+      </c>
+      <c r="G89" s="7">
         <v>2042</v>
       </c>
-      <c r="H199" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="200" customHeight="1" spans="3:8">
-      <c r="C200" s="1">
+      <c r="H89" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C90" s="1">
         <v>285</v>
       </c>
-      <c r="D200" s="1">
-        <v>2</v>
-      </c>
-      <c r="E200" s="1">
+      <c r="D90" s="1">
+        <v>2</v>
+      </c>
+      <c r="E90" s="1">
         <v>15</v>
       </c>
-      <c r="F200" s="8">
-        <v>2</v>
-      </c>
-      <c r="G200" s="8">
+      <c r="F90" s="7">
+        <v>2</v>
+      </c>
+      <c r="G90" s="7">
         <v>2043</v>
       </c>
-      <c r="H200" s="8">
+      <c r="H90" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="201" customHeight="1" spans="3:8">
-      <c r="C201" s="1">
+    <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C91" s="1">
         <v>286</v>
       </c>
-      <c r="D201" s="1">
-        <v>2</v>
-      </c>
-      <c r="E201" s="1">
+      <c r="D91" s="1">
+        <v>2</v>
+      </c>
+      <c r="E91" s="1">
         <v>15</v>
       </c>
-      <c r="F201" s="8">
-        <v>3</v>
-      </c>
-      <c r="G201" s="8">
+      <c r="F91" s="7">
+        <v>3</v>
+      </c>
+      <c r="G91" s="7">
         <v>2041</v>
       </c>
-      <c r="H201" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" spans="3:8">
-      <c r="C202" s="1">
+      <c r="H91" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C92" s="1">
         <v>287</v>
       </c>
-      <c r="D202" s="1">
-        <v>2</v>
-      </c>
-      <c r="E202" s="1">
+      <c r="D92" s="1">
+        <v>2</v>
+      </c>
+      <c r="E92" s="1">
         <v>15</v>
       </c>
-      <c r="F202" s="8">
-        <v>3</v>
-      </c>
-      <c r="G202" s="8">
+      <c r="F92" s="7">
+        <v>3</v>
+      </c>
+      <c r="G92" s="7">
         <v>2042</v>
       </c>
-      <c r="H202" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" spans="3:8">
-      <c r="C203" s="1">
+      <c r="H92" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C93" s="1">
         <v>288</v>
       </c>
-      <c r="D203" s="1">
-        <v>2</v>
-      </c>
-      <c r="E203" s="1">
+      <c r="D93" s="1">
+        <v>2</v>
+      </c>
+      <c r="E93" s="1">
         <v>15</v>
       </c>
-      <c r="F203" s="8">
-        <v>3</v>
-      </c>
-      <c r="G203" s="8">
+      <c r="F93" s="7">
+        <v>3</v>
+      </c>
+      <c r="G93" s="7">
         <v>2043</v>
       </c>
-      <c r="H203" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" spans="3:8">
-      <c r="C204" s="1">
+      <c r="H93" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C94" s="1">
         <v>289</v>
       </c>
-      <c r="D204" s="1">
-        <v>2</v>
-      </c>
-      <c r="E204" s="1">
+      <c r="D94" s="1">
+        <v>2</v>
+      </c>
+      <c r="E94" s="1">
         <v>15</v>
       </c>
-      <c r="F204" s="8">
-        <v>3</v>
-      </c>
-      <c r="G204" s="8">
+      <c r="F94" s="7">
+        <v>3</v>
+      </c>
+      <c r="G94" s="7">
         <v>2044</v>
       </c>
-      <c r="H204" s="8">
+      <c r="H94" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="205" customHeight="1" spans="3:8">
-      <c r="C205" s="1">
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C95" s="1">
         <v>290</v>
       </c>
-      <c r="D205" s="1">
-        <v>2</v>
-      </c>
-      <c r="E205" s="1">
+      <c r="D95" s="1">
+        <v>2</v>
+      </c>
+      <c r="E95" s="1">
         <v>15</v>
       </c>
-      <c r="F205" s="8">
-        <v>4</v>
-      </c>
-      <c r="G205" s="8">
+      <c r="F95" s="7">
+        <v>4</v>
+      </c>
+      <c r="G95" s="7">
         <v>2042</v>
       </c>
-      <c r="H205" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" spans="3:8">
-      <c r="C206" s="1">
+      <c r="H95" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C96" s="1">
         <v>291</v>
       </c>
-      <c r="D206" s="1">
-        <v>2</v>
-      </c>
-      <c r="E206" s="1">
+      <c r="D96" s="1">
+        <v>2</v>
+      </c>
+      <c r="E96" s="1">
         <v>15</v>
       </c>
-      <c r="F206" s="8">
-        <v>4</v>
-      </c>
-      <c r="G206" s="8">
+      <c r="F96" s="7">
+        <v>4</v>
+      </c>
+      <c r="G96" s="7">
         <v>2043</v>
       </c>
-      <c r="H206" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" spans="3:8">
-      <c r="C207" s="1">
+      <c r="H96" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C97" s="1">
         <v>292</v>
       </c>
-      <c r="D207" s="1">
-        <v>2</v>
-      </c>
-      <c r="E207" s="1">
+      <c r="D97" s="1">
+        <v>2</v>
+      </c>
+      <c r="E97" s="1">
         <v>15</v>
       </c>
-      <c r="F207" s="8">
-        <v>4</v>
-      </c>
-      <c r="G207" s="8">
+      <c r="F97" s="7">
+        <v>4</v>
+      </c>
+      <c r="G97" s="7">
         <v>2044</v>
       </c>
-      <c r="H207" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" spans="3:8">
-      <c r="C208" s="1">
+      <c r="H97" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C98" s="1">
         <v>293</v>
       </c>
-      <c r="D208" s="1">
-        <v>2</v>
-      </c>
-      <c r="E208" s="1">
+      <c r="D98" s="1">
+        <v>2</v>
+      </c>
+      <c r="E98" s="1">
         <v>15</v>
       </c>
-      <c r="F208" s="8">
-        <v>4</v>
-      </c>
-      <c r="G208" s="8">
+      <c r="F98" s="7">
+        <v>4</v>
+      </c>
+      <c r="G98" s="7">
         <v>2045</v>
       </c>
-      <c r="H208" s="8">
+      <c r="H98" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="209" customHeight="1" spans="3:8">
-      <c r="C209" s="1">
+    <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C99" s="1">
         <v>294</v>
       </c>
-      <c r="D209" s="1">
-        <v>2</v>
-      </c>
-      <c r="E209" s="10">
+      <c r="D99" s="1">
+        <v>2</v>
+      </c>
+      <c r="E99" s="8">
         <v>16</v>
       </c>
-      <c r="F209" s="11">
-        <v>1</v>
-      </c>
-      <c r="G209" s="11">
+      <c r="F99" s="9">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9">
         <v>2040</v>
       </c>
-      <c r="H209" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" spans="3:8">
-      <c r="C210" s="1">
+      <c r="H99" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C100" s="1">
         <v>295</v>
       </c>
-      <c r="D210" s="1">
-        <v>2</v>
-      </c>
-      <c r="E210" s="1">
+      <c r="D100" s="1">
+        <v>2</v>
+      </c>
+      <c r="E100" s="1">
         <v>16</v>
       </c>
-      <c r="F210" s="8">
-        <v>1</v>
-      </c>
-      <c r="G210" s="8">
+      <c r="F100" s="7">
+        <v>1</v>
+      </c>
+      <c r="G100" s="7">
         <v>2041</v>
       </c>
-      <c r="H210" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="211" customHeight="1" spans="3:8">
-      <c r="C211" s="1">
+      <c r="H100" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C101" s="1">
         <v>296</v>
       </c>
-      <c r="D211" s="1">
-        <v>2</v>
-      </c>
-      <c r="E211" s="1">
+      <c r="D101" s="1">
+        <v>2</v>
+      </c>
+      <c r="E101" s="1">
         <v>16</v>
       </c>
-      <c r="F211" s="8">
-        <v>1</v>
-      </c>
-      <c r="G211" s="8">
+      <c r="F101" s="7">
+        <v>1</v>
+      </c>
+      <c r="G101" s="7">
         <v>2042</v>
       </c>
-      <c r="H211" s="8">
+      <c r="H101" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="212" customHeight="1" spans="3:8">
-      <c r="C212" s="1">
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C102" s="1">
         <v>297</v>
       </c>
-      <c r="D212" s="1">
-        <v>2</v>
-      </c>
-      <c r="E212" s="1">
+      <c r="D102" s="1">
+        <v>2</v>
+      </c>
+      <c r="E102" s="1">
         <v>16</v>
       </c>
-      <c r="F212" s="8">
-        <v>1</v>
-      </c>
-      <c r="G212" s="8">
+      <c r="F102" s="7">
+        <v>1</v>
+      </c>
+      <c r="G102" s="7">
         <v>2043</v>
       </c>
-      <c r="H212" s="8">
+      <c r="H102" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="213" customHeight="1" spans="3:8">
-      <c r="C213" s="1">
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C103" s="1">
         <v>298</v>
       </c>
-      <c r="D213" s="1">
-        <v>2</v>
-      </c>
-      <c r="E213" s="1">
+      <c r="D103" s="1">
+        <v>2</v>
+      </c>
+      <c r="E103" s="1">
         <v>16</v>
       </c>
-      <c r="F213" s="8">
-        <v>2</v>
-      </c>
-      <c r="G213" s="8">
+      <c r="F103" s="7">
+        <v>2</v>
+      </c>
+      <c r="G103" s="7">
         <v>2041</v>
       </c>
-      <c r="H213" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="214" customHeight="1" spans="3:8">
-      <c r="C214" s="1">
+      <c r="H103" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C104" s="1">
         <v>299</v>
       </c>
-      <c r="D214" s="1">
-        <v>2</v>
-      </c>
-      <c r="E214" s="1">
+      <c r="D104" s="1">
+        <v>2</v>
+      </c>
+      <c r="E104" s="1">
         <v>16</v>
       </c>
-      <c r="F214" s="8">
-        <v>2</v>
-      </c>
-      <c r="G214" s="8">
+      <c r="F104" s="7">
+        <v>2</v>
+      </c>
+      <c r="G104" s="7">
         <v>2042</v>
       </c>
-      <c r="H214" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="215" customHeight="1" spans="3:8">
-      <c r="C215" s="1">
+      <c r="H104" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C105" s="1">
         <v>300</v>
       </c>
-      <c r="D215" s="1">
-        <v>2</v>
-      </c>
-      <c r="E215" s="1">
+      <c r="D105" s="1">
+        <v>2</v>
+      </c>
+      <c r="E105" s="1">
         <v>16</v>
       </c>
-      <c r="F215" s="8">
-        <v>2</v>
-      </c>
-      <c r="G215" s="8">
+      <c r="F105" s="7">
+        <v>2</v>
+      </c>
+      <c r="G105" s="7">
         <v>2043</v>
       </c>
-      <c r="H215" s="8">
+      <c r="H105" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="216" customHeight="1" spans="3:8">
-      <c r="C216" s="1">
+    <row r="106" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C106" s="1">
         <v>301</v>
       </c>
-      <c r="D216" s="1">
-        <v>2</v>
-      </c>
-      <c r="E216" s="1">
+      <c r="D106" s="1">
+        <v>2</v>
+      </c>
+      <c r="E106" s="1">
         <v>16</v>
       </c>
-      <c r="F216" s="8">
-        <v>2</v>
-      </c>
-      <c r="G216" s="8">
+      <c r="F106" s="7">
+        <v>2</v>
+      </c>
+      <c r="G106" s="7">
         <v>2044</v>
       </c>
-      <c r="H216" s="8">
+      <c r="H106" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="217" customHeight="1" spans="3:8">
-      <c r="C217" s="1">
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C107" s="1">
         <v>302</v>
       </c>
-      <c r="D217" s="1">
-        <v>2</v>
-      </c>
-      <c r="E217" s="1">
+      <c r="D107" s="1">
+        <v>2</v>
+      </c>
+      <c r="E107" s="1">
         <v>16</v>
       </c>
-      <c r="F217" s="8">
-        <v>3</v>
-      </c>
-      <c r="G217" s="8">
+      <c r="F107" s="7">
+        <v>3</v>
+      </c>
+      <c r="G107" s="7">
         <v>2042</v>
       </c>
-      <c r="H217" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" spans="3:8">
-      <c r="C218" s="1">
+      <c r="H107" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C108" s="1">
         <v>303</v>
       </c>
-      <c r="D218" s="1">
-        <v>2</v>
-      </c>
-      <c r="E218" s="1">
+      <c r="D108" s="1">
+        <v>2</v>
+      </c>
+      <c r="E108" s="1">
         <v>16</v>
       </c>
-      <c r="F218" s="8">
-        <v>3</v>
-      </c>
-      <c r="G218" s="8">
+      <c r="F108" s="7">
+        <v>3</v>
+      </c>
+      <c r="G108" s="7">
         <v>2043</v>
       </c>
-      <c r="H218" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" spans="3:8">
-      <c r="C219" s="1">
+      <c r="H108" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C109" s="1">
         <v>304</v>
       </c>
-      <c r="D219" s="1">
-        <v>2</v>
-      </c>
-      <c r="E219" s="1">
+      <c r="D109" s="1">
+        <v>2</v>
+      </c>
+      <c r="E109" s="1">
         <v>16</v>
       </c>
-      <c r="F219" s="8">
-        <v>3</v>
-      </c>
-      <c r="G219" s="8">
+      <c r="F109" s="7">
+        <v>3</v>
+      </c>
+      <c r="G109" s="7">
         <v>2044</v>
       </c>
-      <c r="H219" s="8">
+      <c r="H109" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="220" customHeight="1" spans="3:8">
-      <c r="C220" s="1">
+    <row r="110" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C110" s="1">
         <v>305</v>
       </c>
-      <c r="D220" s="1">
-        <v>2</v>
-      </c>
-      <c r="E220" s="1">
+      <c r="D110" s="1">
+        <v>2</v>
+      </c>
+      <c r="E110" s="1">
         <v>16</v>
       </c>
-      <c r="F220" s="8">
-        <v>3</v>
-      </c>
-      <c r="G220" s="8">
+      <c r="F110" s="7">
+        <v>3</v>
+      </c>
+      <c r="G110" s="7">
         <v>2045</v>
       </c>
-      <c r="H220" s="8">
+      <c r="H110" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="221" customHeight="1" spans="3:8">
-      <c r="C221" s="1">
+    <row r="111" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C111" s="1">
         <v>306</v>
       </c>
-      <c r="D221" s="1">
-        <v>2</v>
-      </c>
-      <c r="E221" s="1">
+      <c r="D111" s="1">
+        <v>2</v>
+      </c>
+      <c r="E111" s="1">
         <v>16</v>
       </c>
-      <c r="F221" s="8">
-        <v>4</v>
-      </c>
-      <c r="G221" s="8">
+      <c r="F111" s="7">
+        <v>4</v>
+      </c>
+      <c r="G111" s="7">
         <v>2043</v>
       </c>
-      <c r="H221" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="222" customHeight="1" spans="3:8">
-      <c r="C222" s="1">
+      <c r="H111" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C112" s="1">
         <v>307</v>
       </c>
-      <c r="D222" s="1">
-        <v>2</v>
-      </c>
-      <c r="E222" s="1">
+      <c r="D112" s="1">
+        <v>2</v>
+      </c>
+      <c r="E112" s="1">
         <v>16</v>
       </c>
-      <c r="F222" s="8">
-        <v>4</v>
-      </c>
-      <c r="G222" s="8">
+      <c r="F112" s="7">
+        <v>4</v>
+      </c>
+      <c r="G112" s="7">
         <v>2044</v>
       </c>
-      <c r="H222" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="223" customHeight="1" spans="3:8">
-      <c r="C223" s="1">
+      <c r="H112" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C113" s="1">
         <v>308</v>
       </c>
-      <c r="D223" s="1">
-        <v>2</v>
-      </c>
-      <c r="E223" s="1">
+      <c r="D113" s="1">
+        <v>2</v>
+      </c>
+      <c r="E113" s="1">
         <v>16</v>
       </c>
-      <c r="F223" s="8">
-        <v>4</v>
-      </c>
-      <c r="G223" s="8">
+      <c r="F113" s="7">
+        <v>4</v>
+      </c>
+      <c r="G113" s="7">
         <v>2045</v>
       </c>
-      <c r="H223" s="8">
+      <c r="H113" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="224" customHeight="1" spans="3:8">
-      <c r="C224" s="1">
+    <row r="114" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C114" s="1">
         <v>309</v>
       </c>
-      <c r="D224" s="1">
-        <v>2</v>
-      </c>
-      <c r="E224" s="1">
+      <c r="D114" s="1">
+        <v>2</v>
+      </c>
+      <c r="E114" s="1">
         <v>16</v>
       </c>
-      <c r="F224" s="8">
-        <v>4</v>
-      </c>
-      <c r="G224" s="8">
+      <c r="F114" s="7">
+        <v>4</v>
+      </c>
+      <c r="G114" s="7">
         <v>2046</v>
       </c>
-      <c r="H224" s="8">
+      <c r="H114" s="7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L114"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C6" s="1">
+        <v>401</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H6" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C7" s="1">
+        <v>402</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>17</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H7" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C8" s="1">
+        <v>403</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H8" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C9" s="1">
+        <v>404</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>17</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H9" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C10" s="1">
+        <v>405</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>17</v>
+      </c>
+      <c r="F10" s="7">
+        <v>3</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H10" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C11" s="1">
+        <v>406</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C12" s="1">
+        <v>407</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>17</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H12" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C13" s="1">
+        <v>408</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>17</v>
+      </c>
+      <c r="F13" s="7">
+        <v>4</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H13" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C14" s="1">
+        <v>409</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>17</v>
+      </c>
+      <c r="F14" s="7">
+        <v>4</v>
+      </c>
+      <c r="G14" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H14" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C15" s="1">
+        <v>410</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7">
+        <v>4</v>
+      </c>
+      <c r="G15" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H15" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C16" s="1">
+        <v>411</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="8">
+        <v>18</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
+        <v>2047</v>
+      </c>
+      <c r="H16" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
+        <v>412</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H17" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C18" s="1">
+        <v>413</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7">
+        <v>2</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H18" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C19" s="1">
+        <v>414</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>18</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H19" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="1">
+        <v>415</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H20" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C21" s="1">
+        <v>416</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H21" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C22" s="1">
+        <v>417</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
+        <v>18</v>
+      </c>
+      <c r="F22" s="7">
+        <v>3</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H22" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C23" s="1">
+        <v>418</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>18</v>
+      </c>
+      <c r="F23" s="7">
+        <v>4</v>
+      </c>
+      <c r="G23" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H23" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C24" s="1">
+        <v>419</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>18</v>
+      </c>
+      <c r="F24" s="7">
+        <v>4</v>
+      </c>
+      <c r="G24" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H24" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C25" s="1">
+        <v>420</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>18</v>
+      </c>
+      <c r="F25" s="7">
+        <v>4</v>
+      </c>
+      <c r="G25" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H25" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C26" s="1">
+        <v>421</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>18</v>
+      </c>
+      <c r="F26" s="7">
+        <v>4</v>
+      </c>
+      <c r="G26" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H26" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
+        <v>422</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="10">
+        <v>19</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
+        <v>2047</v>
+      </c>
+      <c r="H27" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
+        <v>423</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="10">
+        <v>19</v>
+      </c>
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H28" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
+        <v>424</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="10">
+        <v>19</v>
+      </c>
+      <c r="F29" s="7">
+        <v>2</v>
+      </c>
+      <c r="G29" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H29" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="1">
+        <v>425</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="10">
+        <v>19</v>
+      </c>
+      <c r="F30" s="7">
+        <v>2</v>
+      </c>
+      <c r="G30" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H30" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="1">
+        <v>426</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="10">
+        <v>19</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H31" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C32" s="1">
+        <v>427</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="10">
+        <v>19</v>
+      </c>
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H32" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="1">
+        <v>428</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="10">
+        <v>19</v>
+      </c>
+      <c r="F33" s="7">
+        <v>3</v>
+      </c>
+      <c r="G33" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H33" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="1">
+        <v>429</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="10">
+        <v>19</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H34" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C35" s="1">
+        <v>430</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="10">
+        <v>19</v>
+      </c>
+      <c r="F35" s="7">
+        <v>4</v>
+      </c>
+      <c r="G35" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H35" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="1">
+        <v>431</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="10">
+        <v>19</v>
+      </c>
+      <c r="F36" s="7">
+        <v>4</v>
+      </c>
+      <c r="G36" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H36" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="1">
+        <v>432</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="10">
+        <v>19</v>
+      </c>
+      <c r="F37" s="7">
+        <v>4</v>
+      </c>
+      <c r="G37" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H37" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C38" s="1">
+        <v>433</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" s="10">
+        <v>19</v>
+      </c>
+      <c r="F38" s="7">
+        <v>4</v>
+      </c>
+      <c r="G38" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H38" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C39" s="1">
+        <v>434</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="8">
+        <v>20</v>
+      </c>
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>2047</v>
+      </c>
+      <c r="H39" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="1">
+        <v>435</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>20</v>
+      </c>
+      <c r="F40" s="7">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H40" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="1">
+        <v>436</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>20</v>
+      </c>
+      <c r="F41" s="7">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H41" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C42" s="1">
+        <v>437</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>20</v>
+      </c>
+      <c r="F42" s="7">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H42" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C43" s="1">
+        <v>438</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>20</v>
+      </c>
+      <c r="F43" s="7">
+        <v>2</v>
+      </c>
+      <c r="G43" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H43" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C44" s="1">
+        <v>439</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>20</v>
+      </c>
+      <c r="F44" s="7">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H44" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C45" s="1">
+        <v>440</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>20</v>
+      </c>
+      <c r="F45" s="7">
+        <v>3</v>
+      </c>
+      <c r="G45" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H45" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C46" s="1">
+        <v>441</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>20</v>
+      </c>
+      <c r="F46" s="7">
+        <v>3</v>
+      </c>
+      <c r="G46" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H46" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C47" s="1">
+        <v>442</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>20</v>
+      </c>
+      <c r="F47" s="7">
+        <v>3</v>
+      </c>
+      <c r="G47" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H47" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C48" s="1">
+        <v>443</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>20</v>
+      </c>
+      <c r="F48" s="7">
+        <v>4</v>
+      </c>
+      <c r="G48" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H48" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C49" s="1">
+        <v>444</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>20</v>
+      </c>
+      <c r="F49" s="7">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H49" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C50" s="1">
+        <v>445</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>20</v>
+      </c>
+      <c r="F50" s="7">
+        <v>4</v>
+      </c>
+      <c r="G50" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H50" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="1">
+        <v>446</v>
+      </c>
+      <c r="D51" s="1">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>20</v>
+      </c>
+      <c r="F51" s="7">
+        <v>4</v>
+      </c>
+      <c r="G51" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H51" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="1">
+        <v>447</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" s="8">
+        <v>21</v>
+      </c>
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9">
+        <v>2047</v>
+      </c>
+      <c r="H52" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C53" s="1">
+        <v>448</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>21</v>
+      </c>
+      <c r="F53" s="7">
+        <v>1</v>
+      </c>
+      <c r="G53" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H53" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C54" s="1">
+        <v>449</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>21</v>
+      </c>
+      <c r="F54" s="7">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H54" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C55" s="1">
+        <v>450</v>
+      </c>
+      <c r="D55" s="1">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>21</v>
+      </c>
+      <c r="F55" s="7">
+        <v>2</v>
+      </c>
+      <c r="G55" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H55" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C56" s="1">
+        <v>451</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>21</v>
+      </c>
+      <c r="F56" s="7">
+        <v>2</v>
+      </c>
+      <c r="G56" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H56" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="1">
+        <v>452</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>21</v>
+      </c>
+      <c r="F57" s="7">
+        <v>2</v>
+      </c>
+      <c r="G57" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H57" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="1">
+        <v>453</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>21</v>
+      </c>
+      <c r="F58" s="7">
+        <v>2</v>
+      </c>
+      <c r="G58" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H58" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C59" s="1">
+        <v>454</v>
+      </c>
+      <c r="D59" s="1">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>21</v>
+      </c>
+      <c r="F59" s="7">
+        <v>3</v>
+      </c>
+      <c r="G59" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H59" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C60" s="1">
+        <v>455</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>21</v>
+      </c>
+      <c r="F60" s="7">
+        <v>3</v>
+      </c>
+      <c r="G60" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H60" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C61" s="1">
+        <v>456</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>21</v>
+      </c>
+      <c r="F61" s="7">
+        <v>3</v>
+      </c>
+      <c r="G61" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H61" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C62" s="1">
+        <v>457</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>21</v>
+      </c>
+      <c r="F62" s="7">
+        <v>3</v>
+      </c>
+      <c r="G62" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H62" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C63" s="1">
+        <v>458</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>21</v>
+      </c>
+      <c r="F63" s="7">
+        <v>4</v>
+      </c>
+      <c r="G63" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H63" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="1">
+        <v>459</v>
+      </c>
+      <c r="D64" s="1">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>21</v>
+      </c>
+      <c r="F64" s="7">
+        <v>4</v>
+      </c>
+      <c r="G64" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H64" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
+        <v>460</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3</v>
+      </c>
+      <c r="E65" s="1">
+        <v>21</v>
+      </c>
+      <c r="F65" s="7">
+        <v>4</v>
+      </c>
+      <c r="G65" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H65" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
+        <v>461</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1">
+        <v>21</v>
+      </c>
+      <c r="F66" s="7">
+        <v>4</v>
+      </c>
+      <c r="G66" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H66" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
+        <v>462</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" s="8">
+        <v>22</v>
+      </c>
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9">
+        <v>2047</v>
+      </c>
+      <c r="H67" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
+        <v>463</v>
+      </c>
+      <c r="D68" s="1">
+        <v>3</v>
+      </c>
+      <c r="E68" s="1">
+        <v>22</v>
+      </c>
+      <c r="F68" s="7">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H68" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
+        <v>464</v>
+      </c>
+      <c r="D69" s="1">
+        <v>3</v>
+      </c>
+      <c r="E69" s="1">
+        <v>22</v>
+      </c>
+      <c r="F69" s="7">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H69" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
+        <v>465</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3</v>
+      </c>
+      <c r="E70" s="1">
+        <v>22</v>
+      </c>
+      <c r="F70" s="7">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H70" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
+        <v>466</v>
+      </c>
+      <c r="D71" s="1">
+        <v>3</v>
+      </c>
+      <c r="E71" s="1">
+        <v>22</v>
+      </c>
+      <c r="F71" s="7">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H71" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
+        <v>467</v>
+      </c>
+      <c r="D72" s="1">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1">
+        <v>22</v>
+      </c>
+      <c r="F72" s="7">
+        <v>2</v>
+      </c>
+      <c r="G72" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H72" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C73" s="1">
+        <v>468</v>
+      </c>
+      <c r="D73" s="1">
+        <v>3</v>
+      </c>
+      <c r="E73" s="1">
+        <v>22</v>
+      </c>
+      <c r="F73" s="7">
+        <v>2</v>
+      </c>
+      <c r="G73" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H73" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C74" s="1">
+        <v>469</v>
+      </c>
+      <c r="D74" s="1">
+        <v>3</v>
+      </c>
+      <c r="E74" s="1">
+        <v>22</v>
+      </c>
+      <c r="F74" s="7">
+        <v>2</v>
+      </c>
+      <c r="G74" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H74" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
+        <v>470</v>
+      </c>
+      <c r="D75" s="1">
+        <v>3</v>
+      </c>
+      <c r="E75" s="1">
+        <v>22</v>
+      </c>
+      <c r="F75" s="7">
+        <v>3</v>
+      </c>
+      <c r="G75" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H75" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
+        <v>471</v>
+      </c>
+      <c r="D76" s="1">
+        <v>3</v>
+      </c>
+      <c r="E76" s="1">
+        <v>22</v>
+      </c>
+      <c r="F76" s="7">
+        <v>3</v>
+      </c>
+      <c r="G76" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H76" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
+        <v>472</v>
+      </c>
+      <c r="D77" s="1">
+        <v>3</v>
+      </c>
+      <c r="E77" s="1">
+        <v>22</v>
+      </c>
+      <c r="F77" s="7">
+        <v>3</v>
+      </c>
+      <c r="G77" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H77" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C78" s="1">
+        <v>473</v>
+      </c>
+      <c r="D78" s="1">
+        <v>3</v>
+      </c>
+      <c r="E78" s="1">
+        <v>22</v>
+      </c>
+      <c r="F78" s="7">
+        <v>3</v>
+      </c>
+      <c r="G78" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H78" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C79" s="1">
+        <v>474</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3</v>
+      </c>
+      <c r="E79" s="1">
+        <v>22</v>
+      </c>
+      <c r="F79" s="7">
+        <v>4</v>
+      </c>
+      <c r="G79" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H79" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C80" s="1">
+        <v>475</v>
+      </c>
+      <c r="D80" s="1">
+        <v>3</v>
+      </c>
+      <c r="E80" s="1">
+        <v>22</v>
+      </c>
+      <c r="F80" s="7">
+        <v>4</v>
+      </c>
+      <c r="G80" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H80" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C81" s="1">
+        <v>476</v>
+      </c>
+      <c r="D81" s="1">
+        <v>3</v>
+      </c>
+      <c r="E81" s="1">
+        <v>22</v>
+      </c>
+      <c r="F81" s="7">
+        <v>4</v>
+      </c>
+      <c r="G81" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H81" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C82" s="1">
+        <v>477</v>
+      </c>
+      <c r="D82" s="1">
+        <v>3</v>
+      </c>
+      <c r="E82" s="1">
+        <v>22</v>
+      </c>
+      <c r="F82" s="7">
+        <v>4</v>
+      </c>
+      <c r="G82" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H82" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C83" s="1">
+        <v>478</v>
+      </c>
+      <c r="D83" s="1">
+        <v>3</v>
+      </c>
+      <c r="E83" s="8">
+        <v>23</v>
+      </c>
+      <c r="F83" s="9">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9">
+        <v>2047</v>
+      </c>
+      <c r="H83" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="1">
+        <v>479</v>
+      </c>
+      <c r="D84" s="1">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1">
+        <v>23</v>
+      </c>
+      <c r="F84" s="7">
+        <v>1</v>
+      </c>
+      <c r="G84" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H84" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C85" s="1">
+        <v>480</v>
+      </c>
+      <c r="D85" s="1">
+        <v>3</v>
+      </c>
+      <c r="E85" s="1">
+        <v>23</v>
+      </c>
+      <c r="F85" s="7">
+        <v>1</v>
+      </c>
+      <c r="G85" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H85" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C86" s="1">
+        <v>481</v>
+      </c>
+      <c r="D86" s="1">
+        <v>3</v>
+      </c>
+      <c r="E86" s="1">
+        <v>23</v>
+      </c>
+      <c r="F86" s="7">
+        <v>1</v>
+      </c>
+      <c r="G86" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H86" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C87" s="1">
+        <v>482</v>
+      </c>
+      <c r="D87" s="1">
+        <v>3</v>
+      </c>
+      <c r="E87" s="1">
+        <v>23</v>
+      </c>
+      <c r="F87" s="7">
+        <v>2</v>
+      </c>
+      <c r="G87" s="7">
+        <v>2048</v>
+      </c>
+      <c r="H87" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C88" s="1">
+        <v>483</v>
+      </c>
+      <c r="D88" s="1">
+        <v>3</v>
+      </c>
+      <c r="E88" s="1">
+        <v>23</v>
+      </c>
+      <c r="F88" s="7">
+        <v>2</v>
+      </c>
+      <c r="G88" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H88" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C89" s="1">
+        <v>484</v>
+      </c>
+      <c r="D89" s="1">
+        <v>3</v>
+      </c>
+      <c r="E89" s="1">
+        <v>23</v>
+      </c>
+      <c r="F89" s="7">
+        <v>2</v>
+      </c>
+      <c r="G89" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H89" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C90" s="1">
+        <v>485</v>
+      </c>
+      <c r="D90" s="1">
+        <v>3</v>
+      </c>
+      <c r="E90" s="1">
+        <v>23</v>
+      </c>
+      <c r="F90" s="7">
+        <v>2</v>
+      </c>
+      <c r="G90" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H90" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C91" s="1">
+        <v>486</v>
+      </c>
+      <c r="D91" s="1">
+        <v>3</v>
+      </c>
+      <c r="E91" s="1">
+        <v>23</v>
+      </c>
+      <c r="F91" s="7">
+        <v>3</v>
+      </c>
+      <c r="G91" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H91" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C92" s="1">
+        <v>487</v>
+      </c>
+      <c r="D92" s="1">
+        <v>3</v>
+      </c>
+      <c r="E92" s="1">
+        <v>23</v>
+      </c>
+      <c r="F92" s="7">
+        <v>3</v>
+      </c>
+      <c r="G92" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H92" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C93" s="1">
+        <v>488</v>
+      </c>
+      <c r="D93" s="1">
+        <v>3</v>
+      </c>
+      <c r="E93" s="1">
+        <v>23</v>
+      </c>
+      <c r="F93" s="7">
+        <v>3</v>
+      </c>
+      <c r="G93" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H93" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C94" s="1">
+        <v>489</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1">
+        <v>23</v>
+      </c>
+      <c r="F94" s="7">
+        <v>3</v>
+      </c>
+      <c r="G94" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H94" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C95" s="1">
+        <v>490</v>
+      </c>
+      <c r="D95" s="1">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1">
+        <v>23</v>
+      </c>
+      <c r="F95" s="7">
+        <v>4</v>
+      </c>
+      <c r="G95" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H95" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C96" s="1">
+        <v>491</v>
+      </c>
+      <c r="D96" s="1">
+        <v>3</v>
+      </c>
+      <c r="E96" s="1">
+        <v>23</v>
+      </c>
+      <c r="F96" s="7">
+        <v>4</v>
+      </c>
+      <c r="G96" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H96" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C97" s="1">
+        <v>492</v>
+      </c>
+      <c r="D97" s="1">
+        <v>3</v>
+      </c>
+      <c r="E97" s="1">
+        <v>23</v>
+      </c>
+      <c r="F97" s="7">
+        <v>4</v>
+      </c>
+      <c r="G97" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H97" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C98" s="1">
+        <v>493</v>
+      </c>
+      <c r="D98" s="1">
+        <v>3</v>
+      </c>
+      <c r="E98" s="1">
+        <v>23</v>
+      </c>
+      <c r="F98" s="7">
+        <v>4</v>
+      </c>
+      <c r="G98" s="7">
+        <v>2053</v>
+      </c>
+      <c r="H98" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C99" s="1">
+        <v>494</v>
+      </c>
+      <c r="D99" s="1">
+        <v>3</v>
+      </c>
+      <c r="E99" s="8">
+        <v>24</v>
+      </c>
+      <c r="F99" s="9">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9">
+        <v>2048</v>
+      </c>
+      <c r="H99" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C100" s="1">
+        <v>495</v>
+      </c>
+      <c r="D100" s="1">
+        <v>3</v>
+      </c>
+      <c r="E100" s="1">
+        <v>24</v>
+      </c>
+      <c r="F100" s="7">
+        <v>1</v>
+      </c>
+      <c r="G100" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H100" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C101" s="1">
+        <v>496</v>
+      </c>
+      <c r="D101" s="1">
+        <v>3</v>
+      </c>
+      <c r="E101" s="1">
+        <v>24</v>
+      </c>
+      <c r="F101" s="7">
+        <v>1</v>
+      </c>
+      <c r="G101" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H101" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C102" s="1">
+        <v>497</v>
+      </c>
+      <c r="D102" s="1">
+        <v>3</v>
+      </c>
+      <c r="E102" s="1">
+        <v>24</v>
+      </c>
+      <c r="F102" s="7">
+        <v>1</v>
+      </c>
+      <c r="G102" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H102" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C103" s="1">
+        <v>498</v>
+      </c>
+      <c r="D103" s="1">
+        <v>3</v>
+      </c>
+      <c r="E103" s="1">
+        <v>24</v>
+      </c>
+      <c r="F103" s="7">
+        <v>2</v>
+      </c>
+      <c r="G103" s="7">
+        <v>2049</v>
+      </c>
+      <c r="H103" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C104" s="1">
+        <v>499</v>
+      </c>
+      <c r="D104" s="1">
+        <v>3</v>
+      </c>
+      <c r="E104" s="1">
+        <v>24</v>
+      </c>
+      <c r="F104" s="7">
+        <v>2</v>
+      </c>
+      <c r="G104" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H104" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C105" s="1">
+        <v>500</v>
+      </c>
+      <c r="D105" s="1">
+        <v>3</v>
+      </c>
+      <c r="E105" s="1">
+        <v>24</v>
+      </c>
+      <c r="F105" s="7">
+        <v>2</v>
+      </c>
+      <c r="G105" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H105" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C106" s="1">
+        <v>501</v>
+      </c>
+      <c r="D106" s="1">
+        <v>3</v>
+      </c>
+      <c r="E106" s="1">
+        <v>24</v>
+      </c>
+      <c r="F106" s="7">
+        <v>2</v>
+      </c>
+      <c r="G106" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H106" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C107" s="1">
+        <v>502</v>
+      </c>
+      <c r="D107" s="1">
+        <v>3</v>
+      </c>
+      <c r="E107" s="1">
+        <v>24</v>
+      </c>
+      <c r="F107" s="7">
+        <v>3</v>
+      </c>
+      <c r="G107" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H107" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C108" s="1">
+        <v>503</v>
+      </c>
+      <c r="D108" s="1">
+        <v>3</v>
+      </c>
+      <c r="E108" s="1">
+        <v>24</v>
+      </c>
+      <c r="F108" s="7">
+        <v>3</v>
+      </c>
+      <c r="G108" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H108" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C109" s="1">
+        <v>504</v>
+      </c>
+      <c r="D109" s="1">
+        <v>3</v>
+      </c>
+      <c r="E109" s="1">
+        <v>24</v>
+      </c>
+      <c r="F109" s="7">
+        <v>3</v>
+      </c>
+      <c r="G109" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H109" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C110" s="1">
+        <v>505</v>
+      </c>
+      <c r="D110" s="1">
+        <v>3</v>
+      </c>
+      <c r="E110" s="1">
+        <v>24</v>
+      </c>
+      <c r="F110" s="7">
+        <v>3</v>
+      </c>
+      <c r="G110" s="7">
+        <v>2053</v>
+      </c>
+      <c r="H110" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C111" s="1">
+        <v>506</v>
+      </c>
+      <c r="D111" s="1">
+        <v>3</v>
+      </c>
+      <c r="E111" s="1">
+        <v>24</v>
+      </c>
+      <c r="F111" s="7">
+        <v>4</v>
+      </c>
+      <c r="G111" s="7">
+        <v>2051</v>
+      </c>
+      <c r="H111" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C112" s="1">
+        <v>507</v>
+      </c>
+      <c r="D112" s="1">
+        <v>3</v>
+      </c>
+      <c r="E112" s="1">
+        <v>24</v>
+      </c>
+      <c r="F112" s="7">
+        <v>4</v>
+      </c>
+      <c r="G112" s="7">
+        <v>2052</v>
+      </c>
+      <c r="H112" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C113" s="1">
+        <v>508</v>
+      </c>
+      <c r="D113" s="1">
+        <v>3</v>
+      </c>
+      <c r="E113" s="1">
+        <v>24</v>
+      </c>
+      <c r="F113" s="7">
+        <v>4</v>
+      </c>
+      <c r="G113" s="7">
+        <v>2053</v>
+      </c>
+      <c r="H113" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C114" s="1">
+        <v>509</v>
+      </c>
+      <c r="D114" s="1">
+        <v>3</v>
+      </c>
+      <c r="E114" s="1">
+        <v>24</v>
+      </c>
+      <c r="F114" s="7">
+        <v>4</v>
+      </c>
+      <c r="G114" s="7">
+        <v>2054</v>
+      </c>
+      <c r="H114" s="7">
         <v>10</v>
       </c>
     </row>

--- a/Excel/SpiritDropConfig.xlsx
+++ b/Excel/SpiritDropConfig.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="蜀国" sheetId="2" r:id="rId1"/>
     <sheet name="吴国" sheetId="3" r:id="rId2"/>
     <sheet name="魏国" sheetId="4" r:id="rId3"/>
+    <sheet name="群雄" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">蜀国!#REF!</definedName>
@@ -133,8 +139,42 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 就是100%
+10 就是10%
+100就是1%</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="9">
   <si>
     <t>#</t>
   </si>
@@ -8151,4 +8191,2305 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L114"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C6" s="1">
+        <v>601</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1">
+        <v>25</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H6" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C7" s="1">
+        <v>602</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1">
+        <v>25</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H7" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C8" s="1">
+        <v>603</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>25</v>
+      </c>
+      <c r="F8" s="7">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H8" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C9" s="1">
+        <v>604</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
+        <v>25</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H9" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C10" s="1">
+        <v>605</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1">
+        <v>25</v>
+      </c>
+      <c r="F10" s="7">
+        <v>3</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H10" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C11" s="1">
+        <v>606</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1">
+        <v>25</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3</v>
+      </c>
+      <c r="G11" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H11" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C12" s="1">
+        <v>607</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1">
+        <v>25</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H12" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C13" s="1">
+        <v>608</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1">
+        <v>25</v>
+      </c>
+      <c r="F13" s="7">
+        <v>4</v>
+      </c>
+      <c r="G13" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H13" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C14" s="1">
+        <v>609</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>25</v>
+      </c>
+      <c r="F14" s="7">
+        <v>4</v>
+      </c>
+      <c r="G14" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H14" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C15" s="1">
+        <v>610</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1">
+        <v>25</v>
+      </c>
+      <c r="F15" s="7">
+        <v>4</v>
+      </c>
+      <c r="G15" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H15" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C16" s="1">
+        <v>611</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4</v>
+      </c>
+      <c r="E16" s="8">
+        <v>26</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
+        <v>2055</v>
+      </c>
+      <c r="H16" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
+        <v>612</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1">
+        <v>26</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H17" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C18" s="1">
+        <v>613</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1">
+        <v>26</v>
+      </c>
+      <c r="F18" s="7">
+        <v>2</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H18" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C19" s="1">
+        <v>614</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>26</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H19" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="1">
+        <v>615</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>26</v>
+      </c>
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H20" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C21" s="1">
+        <v>616</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1">
+        <v>26</v>
+      </c>
+      <c r="F21" s="7">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H21" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C22" s="1">
+        <v>617</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1">
+        <v>26</v>
+      </c>
+      <c r="F22" s="7">
+        <v>3</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H22" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C23" s="1">
+        <v>618</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1">
+        <v>26</v>
+      </c>
+      <c r="F23" s="7">
+        <v>4</v>
+      </c>
+      <c r="G23" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H23" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C24" s="1">
+        <v>619</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1">
+        <v>26</v>
+      </c>
+      <c r="F24" s="7">
+        <v>4</v>
+      </c>
+      <c r="G24" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H24" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C25" s="1">
+        <v>620</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1">
+        <v>26</v>
+      </c>
+      <c r="F25" s="7">
+        <v>4</v>
+      </c>
+      <c r="G25" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H25" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C26" s="1">
+        <v>621</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1">
+        <v>26</v>
+      </c>
+      <c r="F26" s="7">
+        <v>4</v>
+      </c>
+      <c r="G26" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H26" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
+        <v>622</v>
+      </c>
+      <c r="D27" s="1">
+        <v>4</v>
+      </c>
+      <c r="E27" s="10">
+        <v>27</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
+        <v>2055</v>
+      </c>
+      <c r="H27" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
+        <v>623</v>
+      </c>
+      <c r="D28" s="1">
+        <v>4</v>
+      </c>
+      <c r="E28" s="10">
+        <v>27</v>
+      </c>
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H28" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
+        <v>624</v>
+      </c>
+      <c r="D29" s="1">
+        <v>4</v>
+      </c>
+      <c r="E29" s="10">
+        <v>27</v>
+      </c>
+      <c r="F29" s="7">
+        <v>2</v>
+      </c>
+      <c r="G29" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H29" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="1">
+        <v>625</v>
+      </c>
+      <c r="D30" s="1">
+        <v>4</v>
+      </c>
+      <c r="E30" s="10">
+        <v>27</v>
+      </c>
+      <c r="F30" s="7">
+        <v>2</v>
+      </c>
+      <c r="G30" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H30" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="1">
+        <v>626</v>
+      </c>
+      <c r="D31" s="1">
+        <v>4</v>
+      </c>
+      <c r="E31" s="10">
+        <v>27</v>
+      </c>
+      <c r="F31" s="7">
+        <v>2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H31" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C32" s="1">
+        <v>627</v>
+      </c>
+      <c r="D32" s="1">
+        <v>4</v>
+      </c>
+      <c r="E32" s="10">
+        <v>27</v>
+      </c>
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H32" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="1">
+        <v>628</v>
+      </c>
+      <c r="D33" s="1">
+        <v>4</v>
+      </c>
+      <c r="E33" s="10">
+        <v>27</v>
+      </c>
+      <c r="F33" s="7">
+        <v>3</v>
+      </c>
+      <c r="G33" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H33" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="1">
+        <v>629</v>
+      </c>
+      <c r="D34" s="1">
+        <v>4</v>
+      </c>
+      <c r="E34" s="10">
+        <v>27</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H34" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C35" s="1">
+        <v>630</v>
+      </c>
+      <c r="D35" s="1">
+        <v>4</v>
+      </c>
+      <c r="E35" s="10">
+        <v>27</v>
+      </c>
+      <c r="F35" s="7">
+        <v>4</v>
+      </c>
+      <c r="G35" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H35" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="1">
+        <v>631</v>
+      </c>
+      <c r="D36" s="1">
+        <v>4</v>
+      </c>
+      <c r="E36" s="10">
+        <v>27</v>
+      </c>
+      <c r="F36" s="7">
+        <v>4</v>
+      </c>
+      <c r="G36" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H36" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="1">
+        <v>632</v>
+      </c>
+      <c r="D37" s="1">
+        <v>4</v>
+      </c>
+      <c r="E37" s="10">
+        <v>27</v>
+      </c>
+      <c r="F37" s="7">
+        <v>4</v>
+      </c>
+      <c r="G37" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H37" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C38" s="1">
+        <v>633</v>
+      </c>
+      <c r="D38" s="1">
+        <v>4</v>
+      </c>
+      <c r="E38" s="10">
+        <v>27</v>
+      </c>
+      <c r="F38" s="7">
+        <v>4</v>
+      </c>
+      <c r="G38" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H38" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C39" s="1">
+        <v>634</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4</v>
+      </c>
+      <c r="E39" s="8">
+        <v>28</v>
+      </c>
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>2055</v>
+      </c>
+      <c r="H39" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="1">
+        <v>635</v>
+      </c>
+      <c r="D40" s="1">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1">
+        <v>28</v>
+      </c>
+      <c r="F40" s="7">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H40" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="1">
+        <v>636</v>
+      </c>
+      <c r="D41" s="1">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1">
+        <v>28</v>
+      </c>
+      <c r="F41" s="7">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H41" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C42" s="1">
+        <v>637</v>
+      </c>
+      <c r="D42" s="1">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1">
+        <v>28</v>
+      </c>
+      <c r="F42" s="7">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H42" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C43" s="1">
+        <v>638</v>
+      </c>
+      <c r="D43" s="1">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1">
+        <v>28</v>
+      </c>
+      <c r="F43" s="7">
+        <v>2</v>
+      </c>
+      <c r="G43" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H43" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C44" s="1">
+        <v>639</v>
+      </c>
+      <c r="D44" s="1">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1">
+        <v>28</v>
+      </c>
+      <c r="F44" s="7">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H44" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C45" s="1">
+        <v>640</v>
+      </c>
+      <c r="D45" s="1">
+        <v>4</v>
+      </c>
+      <c r="E45" s="1">
+        <v>28</v>
+      </c>
+      <c r="F45" s="7">
+        <v>3</v>
+      </c>
+      <c r="G45" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H45" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C46" s="1">
+        <v>641</v>
+      </c>
+      <c r="D46" s="1">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1">
+        <v>28</v>
+      </c>
+      <c r="F46" s="7">
+        <v>3</v>
+      </c>
+      <c r="G46" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H46" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C47" s="1">
+        <v>642</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1">
+        <v>28</v>
+      </c>
+      <c r="F47" s="7">
+        <v>3</v>
+      </c>
+      <c r="G47" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H47" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C48" s="1">
+        <v>643</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1">
+        <v>28</v>
+      </c>
+      <c r="F48" s="7">
+        <v>4</v>
+      </c>
+      <c r="G48" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H48" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C49" s="1">
+        <v>644</v>
+      </c>
+      <c r="D49" s="1">
+        <v>4</v>
+      </c>
+      <c r="E49" s="1">
+        <v>28</v>
+      </c>
+      <c r="F49" s="7">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H49" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C50" s="1">
+        <v>645</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1">
+        <v>28</v>
+      </c>
+      <c r="F50" s="7">
+        <v>4</v>
+      </c>
+      <c r="G50" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H50" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="1">
+        <v>646</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1">
+        <v>28</v>
+      </c>
+      <c r="F51" s="7">
+        <v>4</v>
+      </c>
+      <c r="G51" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H51" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="1">
+        <v>647</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4</v>
+      </c>
+      <c r="E52" s="8">
+        <v>29</v>
+      </c>
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9">
+        <v>2055</v>
+      </c>
+      <c r="H52" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C53" s="1">
+        <v>648</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1">
+        <v>29</v>
+      </c>
+      <c r="F53" s="7">
+        <v>1</v>
+      </c>
+      <c r="G53" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H53" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C54" s="1">
+        <v>649</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>29</v>
+      </c>
+      <c r="F54" s="7">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H54" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C55" s="1">
+        <v>650</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1">
+        <v>29</v>
+      </c>
+      <c r="F55" s="7">
+        <v>2</v>
+      </c>
+      <c r="G55" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H55" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C56" s="1">
+        <v>651</v>
+      </c>
+      <c r="D56" s="1">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1">
+        <v>29</v>
+      </c>
+      <c r="F56" s="7">
+        <v>2</v>
+      </c>
+      <c r="G56" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H56" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="1">
+        <v>652</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1">
+        <v>29</v>
+      </c>
+      <c r="F57" s="7">
+        <v>2</v>
+      </c>
+      <c r="G57" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H57" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="1">
+        <v>653</v>
+      </c>
+      <c r="D58" s="1">
+        <v>4</v>
+      </c>
+      <c r="E58" s="1">
+        <v>29</v>
+      </c>
+      <c r="F58" s="7">
+        <v>2</v>
+      </c>
+      <c r="G58" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H58" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C59" s="1">
+        <v>654</v>
+      </c>
+      <c r="D59" s="1">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1">
+        <v>29</v>
+      </c>
+      <c r="F59" s="7">
+        <v>3</v>
+      </c>
+      <c r="G59" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H59" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C60" s="1">
+        <v>655</v>
+      </c>
+      <c r="D60" s="1">
+        <v>4</v>
+      </c>
+      <c r="E60" s="1">
+        <v>29</v>
+      </c>
+      <c r="F60" s="7">
+        <v>3</v>
+      </c>
+      <c r="G60" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H60" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C61" s="1">
+        <v>656</v>
+      </c>
+      <c r="D61" s="1">
+        <v>4</v>
+      </c>
+      <c r="E61" s="1">
+        <v>29</v>
+      </c>
+      <c r="F61" s="7">
+        <v>3</v>
+      </c>
+      <c r="G61" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H61" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C62" s="1">
+        <v>657</v>
+      </c>
+      <c r="D62" s="1">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1">
+        <v>29</v>
+      </c>
+      <c r="F62" s="7">
+        <v>3</v>
+      </c>
+      <c r="G62" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H62" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C63" s="1">
+        <v>658</v>
+      </c>
+      <c r="D63" s="1">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1">
+        <v>29</v>
+      </c>
+      <c r="F63" s="7">
+        <v>4</v>
+      </c>
+      <c r="G63" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H63" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="1">
+        <v>659</v>
+      </c>
+      <c r="D64" s="1">
+        <v>4</v>
+      </c>
+      <c r="E64" s="1">
+        <v>29</v>
+      </c>
+      <c r="F64" s="7">
+        <v>4</v>
+      </c>
+      <c r="G64" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H64" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
+        <v>660</v>
+      </c>
+      <c r="D65" s="1">
+        <v>4</v>
+      </c>
+      <c r="E65" s="1">
+        <v>29</v>
+      </c>
+      <c r="F65" s="7">
+        <v>4</v>
+      </c>
+      <c r="G65" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H65" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
+        <v>661</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1">
+        <v>29</v>
+      </c>
+      <c r="F66" s="7">
+        <v>4</v>
+      </c>
+      <c r="G66" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H66" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
+        <v>662</v>
+      </c>
+      <c r="D67" s="1">
+        <v>4</v>
+      </c>
+      <c r="E67" s="8">
+        <v>30</v>
+      </c>
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9">
+        <v>2055</v>
+      </c>
+      <c r="H67" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
+        <v>663</v>
+      </c>
+      <c r="D68" s="1">
+        <v>4</v>
+      </c>
+      <c r="E68" s="1">
+        <v>30</v>
+      </c>
+      <c r="F68" s="7">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H68" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
+        <v>664</v>
+      </c>
+      <c r="D69" s="1">
+        <v>4</v>
+      </c>
+      <c r="E69" s="1">
+        <v>30</v>
+      </c>
+      <c r="F69" s="7">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H69" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
+        <v>665</v>
+      </c>
+      <c r="D70" s="1">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1">
+        <v>30</v>
+      </c>
+      <c r="F70" s="7">
+        <v>1</v>
+      </c>
+      <c r="G70" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H70" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
+        <v>666</v>
+      </c>
+      <c r="D71" s="1">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1">
+        <v>30</v>
+      </c>
+      <c r="F71" s="7">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7">
+        <v>2055</v>
+      </c>
+      <c r="H71" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
+        <v>667</v>
+      </c>
+      <c r="D72" s="1">
+        <v>4</v>
+      </c>
+      <c r="E72" s="1">
+        <v>30</v>
+      </c>
+      <c r="F72" s="7">
+        <v>2</v>
+      </c>
+      <c r="G72" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H72" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C73" s="1">
+        <v>668</v>
+      </c>
+      <c r="D73" s="1">
+        <v>4</v>
+      </c>
+      <c r="E73" s="1">
+        <v>30</v>
+      </c>
+      <c r="F73" s="7">
+        <v>2</v>
+      </c>
+      <c r="G73" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H73" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C74" s="1">
+        <v>669</v>
+      </c>
+      <c r="D74" s="1">
+        <v>4</v>
+      </c>
+      <c r="E74" s="1">
+        <v>30</v>
+      </c>
+      <c r="F74" s="7">
+        <v>2</v>
+      </c>
+      <c r="G74" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H74" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
+        <v>670</v>
+      </c>
+      <c r="D75" s="1">
+        <v>4</v>
+      </c>
+      <c r="E75" s="1">
+        <v>30</v>
+      </c>
+      <c r="F75" s="7">
+        <v>3</v>
+      </c>
+      <c r="G75" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H75" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
+        <v>671</v>
+      </c>
+      <c r="D76" s="1">
+        <v>4</v>
+      </c>
+      <c r="E76" s="1">
+        <v>30</v>
+      </c>
+      <c r="F76" s="7">
+        <v>3</v>
+      </c>
+      <c r="G76" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H76" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
+        <v>672</v>
+      </c>
+      <c r="D77" s="1">
+        <v>4</v>
+      </c>
+      <c r="E77" s="1">
+        <v>30</v>
+      </c>
+      <c r="F77" s="7">
+        <v>3</v>
+      </c>
+      <c r="G77" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H77" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C78" s="1">
+        <v>673</v>
+      </c>
+      <c r="D78" s="1">
+        <v>4</v>
+      </c>
+      <c r="E78" s="1">
+        <v>30</v>
+      </c>
+      <c r="F78" s="7">
+        <v>3</v>
+      </c>
+      <c r="G78" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H78" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C79" s="1">
+        <v>674</v>
+      </c>
+      <c r="D79" s="1">
+        <v>4</v>
+      </c>
+      <c r="E79" s="1">
+        <v>30</v>
+      </c>
+      <c r="F79" s="7">
+        <v>4</v>
+      </c>
+      <c r="G79" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H79" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C80" s="1">
+        <v>675</v>
+      </c>
+      <c r="D80" s="1">
+        <v>4</v>
+      </c>
+      <c r="E80" s="1">
+        <v>30</v>
+      </c>
+      <c r="F80" s="7">
+        <v>4</v>
+      </c>
+      <c r="G80" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H80" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C81" s="1">
+        <v>676</v>
+      </c>
+      <c r="D81" s="1">
+        <v>4</v>
+      </c>
+      <c r="E81" s="1">
+        <v>30</v>
+      </c>
+      <c r="F81" s="7">
+        <v>4</v>
+      </c>
+      <c r="G81" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H81" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C82" s="1">
+        <v>677</v>
+      </c>
+      <c r="D82" s="1">
+        <v>4</v>
+      </c>
+      <c r="E82" s="1">
+        <v>30</v>
+      </c>
+      <c r="F82" s="7">
+        <v>4</v>
+      </c>
+      <c r="G82" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H82" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C83" s="1">
+        <v>678</v>
+      </c>
+      <c r="D83" s="1">
+        <v>4</v>
+      </c>
+      <c r="E83" s="8">
+        <v>31</v>
+      </c>
+      <c r="F83" s="9">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9">
+        <v>2055</v>
+      </c>
+      <c r="H83" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="1">
+        <v>679</v>
+      </c>
+      <c r="D84" s="1">
+        <v>4</v>
+      </c>
+      <c r="E84" s="1">
+        <v>31</v>
+      </c>
+      <c r="F84" s="7">
+        <v>1</v>
+      </c>
+      <c r="G84" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H84" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C85" s="1">
+        <v>680</v>
+      </c>
+      <c r="D85" s="1">
+        <v>4</v>
+      </c>
+      <c r="E85" s="1">
+        <v>31</v>
+      </c>
+      <c r="F85" s="7">
+        <v>1</v>
+      </c>
+      <c r="G85" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H85" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C86" s="1">
+        <v>681</v>
+      </c>
+      <c r="D86" s="1">
+        <v>4</v>
+      </c>
+      <c r="E86" s="1">
+        <v>31</v>
+      </c>
+      <c r="F86" s="7">
+        <v>1</v>
+      </c>
+      <c r="G86" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H86" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C87" s="1">
+        <v>682</v>
+      </c>
+      <c r="D87" s="1">
+        <v>4</v>
+      </c>
+      <c r="E87" s="1">
+        <v>31</v>
+      </c>
+      <c r="F87" s="7">
+        <v>2</v>
+      </c>
+      <c r="G87" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H87" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C88" s="1">
+        <v>683</v>
+      </c>
+      <c r="D88" s="1">
+        <v>4</v>
+      </c>
+      <c r="E88" s="1">
+        <v>31</v>
+      </c>
+      <c r="F88" s="7">
+        <v>2</v>
+      </c>
+      <c r="G88" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H88" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C89" s="1">
+        <v>684</v>
+      </c>
+      <c r="D89" s="1">
+        <v>4</v>
+      </c>
+      <c r="E89" s="1">
+        <v>31</v>
+      </c>
+      <c r="F89" s="7">
+        <v>2</v>
+      </c>
+      <c r="G89" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H89" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C90" s="1">
+        <v>685</v>
+      </c>
+      <c r="D90" s="1">
+        <v>4</v>
+      </c>
+      <c r="E90" s="1">
+        <v>31</v>
+      </c>
+      <c r="F90" s="7">
+        <v>2</v>
+      </c>
+      <c r="G90" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H90" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C91" s="1">
+        <v>686</v>
+      </c>
+      <c r="D91" s="1">
+        <v>4</v>
+      </c>
+      <c r="E91" s="1">
+        <v>31</v>
+      </c>
+      <c r="F91" s="7">
+        <v>3</v>
+      </c>
+      <c r="G91" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H91" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C92" s="1">
+        <v>687</v>
+      </c>
+      <c r="D92" s="1">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1">
+        <v>31</v>
+      </c>
+      <c r="F92" s="7">
+        <v>3</v>
+      </c>
+      <c r="G92" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H92" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C93" s="1">
+        <v>688</v>
+      </c>
+      <c r="D93" s="1">
+        <v>4</v>
+      </c>
+      <c r="E93" s="1">
+        <v>31</v>
+      </c>
+      <c r="F93" s="7">
+        <v>3</v>
+      </c>
+      <c r="G93" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H93" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C94" s="1">
+        <v>689</v>
+      </c>
+      <c r="D94" s="1">
+        <v>4</v>
+      </c>
+      <c r="E94" s="1">
+        <v>31</v>
+      </c>
+      <c r="F94" s="7">
+        <v>3</v>
+      </c>
+      <c r="G94" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H94" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C95" s="1">
+        <v>690</v>
+      </c>
+      <c r="D95" s="1">
+        <v>4</v>
+      </c>
+      <c r="E95" s="1">
+        <v>31</v>
+      </c>
+      <c r="F95" s="7">
+        <v>4</v>
+      </c>
+      <c r="G95" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H95" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C96" s="1">
+        <v>691</v>
+      </c>
+      <c r="D96" s="1">
+        <v>4</v>
+      </c>
+      <c r="E96" s="1">
+        <v>31</v>
+      </c>
+      <c r="F96" s="7">
+        <v>4</v>
+      </c>
+      <c r="G96" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H96" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C97" s="1">
+        <v>692</v>
+      </c>
+      <c r="D97" s="1">
+        <v>4</v>
+      </c>
+      <c r="E97" s="1">
+        <v>31</v>
+      </c>
+      <c r="F97" s="7">
+        <v>4</v>
+      </c>
+      <c r="G97" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H97" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C98" s="1">
+        <v>693</v>
+      </c>
+      <c r="D98" s="1">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1">
+        <v>31</v>
+      </c>
+      <c r="F98" s="7">
+        <v>4</v>
+      </c>
+      <c r="G98" s="7">
+        <v>2061</v>
+      </c>
+      <c r="H98" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C99" s="1">
+        <v>694</v>
+      </c>
+      <c r="D99" s="1">
+        <v>4</v>
+      </c>
+      <c r="E99" s="8">
+        <v>32</v>
+      </c>
+      <c r="F99" s="9">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9">
+        <v>2056</v>
+      </c>
+      <c r="H99" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C100" s="1">
+        <v>695</v>
+      </c>
+      <c r="D100" s="1">
+        <v>4</v>
+      </c>
+      <c r="E100" s="1">
+        <v>32</v>
+      </c>
+      <c r="F100" s="7">
+        <v>1</v>
+      </c>
+      <c r="G100" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H100" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C101" s="1">
+        <v>696</v>
+      </c>
+      <c r="D101" s="1">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1">
+        <v>32</v>
+      </c>
+      <c r="F101" s="7">
+        <v>1</v>
+      </c>
+      <c r="G101" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H101" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C102" s="1">
+        <v>697</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1">
+        <v>32</v>
+      </c>
+      <c r="F102" s="7">
+        <v>1</v>
+      </c>
+      <c r="G102" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H102" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C103" s="1">
+        <v>698</v>
+      </c>
+      <c r="D103" s="1">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1">
+        <v>32</v>
+      </c>
+      <c r="F103" s="7">
+        <v>2</v>
+      </c>
+      <c r="G103" s="7">
+        <v>2057</v>
+      </c>
+      <c r="H103" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C104" s="1">
+        <v>699</v>
+      </c>
+      <c r="D104" s="1">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1">
+        <v>32</v>
+      </c>
+      <c r="F104" s="7">
+        <v>2</v>
+      </c>
+      <c r="G104" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H104" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C105" s="1">
+        <v>700</v>
+      </c>
+      <c r="D105" s="1">
+        <v>4</v>
+      </c>
+      <c r="E105" s="1">
+        <v>32</v>
+      </c>
+      <c r="F105" s="7">
+        <v>2</v>
+      </c>
+      <c r="G105" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H105" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C106" s="1">
+        <v>701</v>
+      </c>
+      <c r="D106" s="1">
+        <v>4</v>
+      </c>
+      <c r="E106" s="1">
+        <v>32</v>
+      </c>
+      <c r="F106" s="7">
+        <v>2</v>
+      </c>
+      <c r="G106" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H106" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C107" s="1">
+        <v>702</v>
+      </c>
+      <c r="D107" s="1">
+        <v>4</v>
+      </c>
+      <c r="E107" s="1">
+        <v>32</v>
+      </c>
+      <c r="F107" s="7">
+        <v>3</v>
+      </c>
+      <c r="G107" s="7">
+        <v>2058</v>
+      </c>
+      <c r="H107" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C108" s="1">
+        <v>703</v>
+      </c>
+      <c r="D108" s="1">
+        <v>4</v>
+      </c>
+      <c r="E108" s="1">
+        <v>32</v>
+      </c>
+      <c r="F108" s="7">
+        <v>3</v>
+      </c>
+      <c r="G108" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H108" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C109" s="1">
+        <v>704</v>
+      </c>
+      <c r="D109" s="1">
+        <v>4</v>
+      </c>
+      <c r="E109" s="1">
+        <v>32</v>
+      </c>
+      <c r="F109" s="7">
+        <v>3</v>
+      </c>
+      <c r="G109" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H109" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C110" s="1">
+        <v>705</v>
+      </c>
+      <c r="D110" s="1">
+        <v>4</v>
+      </c>
+      <c r="E110" s="1">
+        <v>32</v>
+      </c>
+      <c r="F110" s="7">
+        <v>3</v>
+      </c>
+      <c r="G110" s="7">
+        <v>2061</v>
+      </c>
+      <c r="H110" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C111" s="1">
+        <v>706</v>
+      </c>
+      <c r="D111" s="1">
+        <v>4</v>
+      </c>
+      <c r="E111" s="1">
+        <v>32</v>
+      </c>
+      <c r="F111" s="7">
+        <v>4</v>
+      </c>
+      <c r="G111" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H111" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C112" s="1">
+        <v>707</v>
+      </c>
+      <c r="D112" s="1">
+        <v>4</v>
+      </c>
+      <c r="E112" s="1">
+        <v>32</v>
+      </c>
+      <c r="F112" s="7">
+        <v>4</v>
+      </c>
+      <c r="G112" s="7">
+        <v>2060</v>
+      </c>
+      <c r="H112" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C113" s="1">
+        <v>708</v>
+      </c>
+      <c r="D113" s="1">
+        <v>4</v>
+      </c>
+      <c r="E113" s="1">
+        <v>32</v>
+      </c>
+      <c r="F113" s="7">
+        <v>4</v>
+      </c>
+      <c r="G113" s="7">
+        <v>2061</v>
+      </c>
+      <c r="H113" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C114" s="1">
+        <v>709</v>
+      </c>
+      <c r="D114" s="1">
+        <v>4</v>
+      </c>
+      <c r="E114" s="1">
+        <v>32</v>
+      </c>
+      <c r="F114" s="7">
+        <v>4</v>
+      </c>
+      <c r="G114" s="7">
+        <v>2062</v>
+      </c>
+      <c r="H114" s="7">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>